--- a/docs/usage/sample_sheets/sheets_polygon.xlsx
+++ b/docs/usage/sample_sheets/sheets_polygon.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DDD943A-8E76-F046-B66C-342D6E3A3C91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{448736C4-E2C8-EB41-827A-888C500BCAB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12240" yWindow="4480" windowWidth="53960" windowHeight="22800" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19900" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="238">
   <si>
     <t>X</t>
   </si>
@@ -305,9 +305,6 @@
     <t>s(f)</t>
   </si>
   <si>
-    <t>Base Values</t>
-  </si>
-  <si>
     <t>Standard Deviations</t>
   </si>
   <si>
@@ -460,9 +457,6 @@
   </si>
   <si>
     <t>XSLOPE Input Template</t>
-  </si>
-  <si>
-    <t>Stress</t>
   </si>
   <si>
     <t>E</t>
@@ -914,6 +908,39 @@
   </si>
   <si>
     <t>Neumann flux - normal Darcy velocity (len/time), + = inflow</t>
+  </si>
+  <si>
+    <t>polygon</t>
+  </si>
+  <si>
+    <t>Polygons describing the slope geometry</t>
+  </si>
+  <si>
+    <t>piles</t>
+  </si>
+  <si>
+    <t>Piles</t>
+  </si>
+  <si>
+    <t>lloads</t>
+  </si>
+  <si>
+    <t>Line loads</t>
+  </si>
+  <si>
+    <t>elastic</t>
+  </si>
+  <si>
+    <t>Elastic / infinite strength (cannot fail). FEM: no yield; LEM: impenetrable</t>
+  </si>
+  <si>
+    <t>t_cut</t>
+  </si>
+  <si>
+    <t>Shear Strength/Stiffness</t>
+  </si>
+  <si>
+    <t>Color legend</t>
   </si>
 </sst>
 </file>
@@ -1063,7 +1090,7 @@
       <name val="Aptos Narrow"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1126,12 +1153,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -1157,6 +1178,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1247,7 +1280,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1304,26 +1337,14 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1342,28 +1363,28 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1376,28 +1397,25 @@
     <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1415,8 +1433,32 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10376,7 +10418,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="32" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="19" x14ac:dyDescent="0.25">
@@ -10386,22 +10428,22 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="C5" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="D5" s="34">
-        <v>15</v>
+        <v>78</v>
+      </c>
+      <c r="D5" s="30">
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="49" t="s">
+      <c r="B7" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
       <c r="F7" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="G7" s="35" t="s">
+      <c r="G7" s="31" t="s">
         <v>16</v>
       </c>
     </row>
@@ -10413,10 +10455,10 @@
         <v>9.81</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
@@ -10450,77 +10492,98 @@
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B11" s="1"/>
       <c r="C11" s="14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D11" s="1">
         <v>0.0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>21</v>
+        <v>227</v>
       </c>
       <c r="G11" t="s">
-        <v>22</v>
+        <v>228</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="F12" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="F13" s="1" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="G13" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="F14" s="1" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G14" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="F15" s="1" t="s">
-        <v>117</v>
+        <v>34</v>
       </c>
       <c r="G15" t="s">
-        <v>119</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="F16" s="1" t="s">
-        <v>36</v>
+        <v>115</v>
       </c>
       <c r="G16" t="s">
-        <v>37</v>
+        <v>117</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B17" s="1"/>
       <c r="F17" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>121</v>
+        <v>36</v>
+      </c>
+      <c r="G17" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
       <c r="F18" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G18" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="F19" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G19" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="F20" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="F21" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G21" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="G18" s="9" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="F20" s="1"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="1"/>
@@ -10556,36 +10619,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="54" t="s">
+        <v>129</v>
+      </c>
+      <c r="C2" s="54"/>
+      <c r="D2" s="54"/>
+      <c r="F2" s="54" t="s">
+        <v>130</v>
+      </c>
+      <c r="G2" s="54"/>
+      <c r="H2" s="54"/>
+      <c r="J2" s="54" t="s">
         <v>131</v>
       </c>
-      <c r="C2" s="59"/>
-      <c r="D2" s="59"/>
-      <c r="F2" s="59" t="s">
+      <c r="K2" s="54"/>
+      <c r="L2" s="54"/>
+      <c r="N2" s="54" t="s">
         <v>132</v>
       </c>
-      <c r="G2" s="59"/>
-      <c r="H2" s="59"/>
-      <c r="J2" s="59" t="s">
+      <c r="O2" s="54"/>
+      <c r="P2" s="54"/>
+      <c r="R2" s="54" t="s">
         <v>133</v>
       </c>
-      <c r="K2" s="59"/>
-      <c r="L2" s="59"/>
-      <c r="N2" s="59" t="s">
+      <c r="S2" s="54"/>
+      <c r="T2" s="54"/>
+      <c r="V2" s="54" t="s">
         <v>134</v>
       </c>
-      <c r="O2" s="59"/>
-      <c r="P2" s="59"/>
-      <c r="R2" s="59" t="s">
-        <v>135</v>
-      </c>
-      <c r="S2" s="59"/>
-      <c r="T2" s="59"/>
-      <c r="V2" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="W2" s="59"/>
-      <c r="X2" s="59"/>
+      <c r="W2" s="54"/>
+      <c r="X2" s="54"/>
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
@@ -11054,64 +11117,64 @@
         <v>25</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C2" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="E2" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="G2" s="40" t="s">
+        <v>192</v>
+      </c>
+      <c r="H2" s="40" t="s">
+        <v>193</v>
+      </c>
+      <c r="I2" s="40" t="s">
+        <v>177</v>
+      </c>
+      <c r="J2" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="K2" s="27" t="s">
+        <v>105</v>
+      </c>
+      <c r="L2" s="27" t="s">
+        <v>106</v>
+      </c>
+      <c r="M2" s="27" t="s">
+        <v>178</v>
+      </c>
+      <c r="N2" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="O2" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="P2" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q2" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="R2" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="F2" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="G2" s="44" t="s">
-        <v>194</v>
-      </c>
-      <c r="H2" s="44" t="s">
-        <v>195</v>
-      </c>
-      <c r="I2" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="J2" s="31" t="s">
-        <v>106</v>
-      </c>
-      <c r="K2" s="31" t="s">
-        <v>107</v>
-      </c>
-      <c r="L2" s="31" t="s">
-        <v>108</v>
-      </c>
-      <c r="M2" s="31" t="s">
+      <c r="Z2" t="s">
         <v>180</v>
       </c>
-      <c r="N2" s="31" t="s">
+      <c r="AA2" t="s">
         <v>181</v>
       </c>
-      <c r="O2" s="31" t="s">
-        <v>196</v>
-      </c>
-      <c r="P2" s="32" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q2" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="R2" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="Z2" t="s">
+      <c r="AB2" t="s">
         <v>182</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>183</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
@@ -11142,13 +11205,13 @@
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
       <c r="Z3" t="s">
+        <v>183</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>184</v>
+      </c>
+      <c r="AB3" t="s">
         <v>185</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>186</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.2">
@@ -11179,7 +11242,7 @@
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
       <c r="Z4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -11210,7 +11273,7 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="Z5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -11297,13 +11360,13 @@
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="Z8" t="s">
+        <v>180</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>181</v>
+      </c>
+      <c r="AB8" t="s">
         <v>182</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>183</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
@@ -11334,13 +11397,13 @@
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
       <c r="Z9" t="s">
+        <v>183</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>184</v>
+      </c>
+      <c r="AB9" t="s">
         <v>185</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>186</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
@@ -11371,13 +11434,13 @@
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
       <c r="Z10" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="AA10" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AB10" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
@@ -11408,13 +11471,13 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="Z11" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="AA11" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="AB11" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -11726,25 +11789,25 @@
       <c r="R22" s="3"/>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="T23" s="46"/>
+      <c r="T23" s="42"/>
       <c r="U23" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.2">
       <c r="K24" s="9"/>
       <c r="L24" s="9"/>
-      <c r="T24" s="30"/>
+      <c r="T24" s="26"/>
       <c r="U24" s="9" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.2">
       <c r="K25" s="9"/>
       <c r="L25" s="9"/>
-      <c r="T25" s="33"/>
+      <c r="T25" s="29"/>
       <c r="U25" s="9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -11782,58 +11845,58 @@
         <v>25</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C2" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="E2" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="G2" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="H2" s="40" t="s">
+        <v>160</v>
+      </c>
+      <c r="I2" s="40" t="s">
+        <v>177</v>
+      </c>
+      <c r="J2" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="K2" s="27" t="s">
+        <v>154</v>
+      </c>
+      <c r="L2" s="41" t="s">
+        <v>157</v>
+      </c>
+      <c r="M2" s="41" t="s">
+        <v>158</v>
+      </c>
+      <c r="N2" s="28" t="s">
+        <v>97</v>
+      </c>
+      <c r="O2" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="P2" s="28" t="s">
         <v>103</v>
       </c>
-      <c r="F2" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="G2" s="44" t="s">
-        <v>154</v>
-      </c>
-      <c r="H2" s="44" t="s">
-        <v>162</v>
-      </c>
-      <c r="I2" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="J2" s="31" t="s">
-        <v>155</v>
-      </c>
-      <c r="K2" s="31" t="s">
-        <v>156</v>
-      </c>
-      <c r="L2" s="45" t="s">
-        <v>159</v>
-      </c>
-      <c r="M2" s="45" t="s">
-        <v>160</v>
-      </c>
-      <c r="N2" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="O2" s="32" t="s">
-        <v>157</v>
-      </c>
-      <c r="P2" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q2" s="32" t="s">
-        <v>166</v>
+      <c r="Q2" s="28" t="s">
+        <v>164</v>
       </c>
       <c r="Z2" t="s">
         <v>40</v>
       </c>
       <c r="AA2" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
@@ -11857,10 +11920,10 @@
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
       <c r="Z3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="AA3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
@@ -12061,21 +12124,21 @@
       <c r="K15" s="9"/>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="S16" s="46"/>
+      <c r="S16" s="42"/>
       <c r="T16" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="17" spans="19:20" x14ac:dyDescent="0.2">
+      <c r="S17" s="26"/>
+      <c r="T17" s="9" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="18" spans="19:20" x14ac:dyDescent="0.2">
+      <c r="S18" s="29"/>
+      <c r="T18" s="9" t="s">
         <v>163</v>
-      </c>
-    </row>
-    <row r="17" spans="19:20" x14ac:dyDescent="0.2">
-      <c r="S17" s="30"/>
-      <c r="T17" s="9" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="18" spans="19:20" x14ac:dyDescent="0.2">
-      <c r="S18" s="33"/>
-      <c r="T18" s="9" t="s">
-        <v>165</v>
       </c>
     </row>
   </sheetData>
@@ -12107,7 +12170,7 @@
         <v>25</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C2" s="12" t="s">
         <v>3</v>
@@ -12116,10 +12179,10 @@
         <v>4</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -12341,108 +12404,108 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B2" s="60" t="s">
-        <v>129</v>
-      </c>
-      <c r="C2" s="60"/>
-      <c r="E2" s="56" t="s">
+      <c r="B2" s="55" t="s">
+        <v>127</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="E2" s="51" t="s">
+        <v>215</v>
+      </c>
+      <c r="F2" s="51"/>
+      <c r="H2" s="51" t="s">
         <v>217</v>
       </c>
-      <c r="F2" s="56"/>
-      <c r="H2" s="56" t="s">
+      <c r="I2" s="51"/>
+      <c r="K2" s="51" t="s">
+        <v>218</v>
+      </c>
+      <c r="L2" s="51"/>
+      <c r="N2" s="51" t="s">
         <v>219</v>
       </c>
-      <c r="I2" s="56"/>
-      <c r="K2" s="56" t="s">
+      <c r="O2" s="51"/>
+      <c r="Q2" s="51" t="s">
         <v>220</v>
       </c>
-      <c r="L2" s="56"/>
-      <c r="N2" s="56" t="s">
-        <v>221</v>
-      </c>
-      <c r="O2" s="56"/>
-      <c r="Q2" s="56" t="s">
-        <v>222</v>
-      </c>
-      <c r="R2" s="56"/>
+      <c r="R2" s="51"/>
     </row>
     <row r="3" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B3" s="60"/>
-      <c r="C3" s="60"/>
-      <c r="E3" s="36" t="inlineStr">
+      <c r="B3" s="55"/>
+      <c r="C3" s="55"/>
+      <c r="E3" s="32" t="inlineStr">
         <is>
           <t>head</t>
         </is>
       </c>
-      <c r="F3" s="37">
+      <c r="F3" s="33">
         <v>14.0</v>
       </c>
-      <c r="H3" s="36" t="inlineStr">
+      <c r="H3" s="32" t="inlineStr">
         <is>
           <t>head</t>
         </is>
       </c>
-      <c r="I3" s="37">
+      <c r="I3" s="33">
         <v>10.0</v>
       </c>
-      <c r="K3" s="36" t="s">
-        <v>215</v>
-      </c>
-      <c r="L3" s="37"/>
-      <c r="N3" s="36" t="s">
-        <v>215</v>
-      </c>
-      <c r="O3" s="37"/>
-      <c r="Q3" s="36" t="s">
-        <v>215</v>
-      </c>
-      <c r="R3" s="37"/>
+      <c r="K3" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="L3" s="33"/>
+      <c r="N3" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="O3" s="33"/>
+      <c r="Q3" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="R3" s="33"/>
       <c r="T3" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="28" t="s">
+      <c r="I4" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="28" t="s">
+      <c r="K4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="L4" s="28" t="s">
+      <c r="L4" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="N4" s="28" t="s">
+      <c r="N4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="O4" s="28" t="s">
+      <c r="O4" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="Q4" s="28" t="s">
+      <c r="Q4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="R4" s="28" t="s">
+      <c r="R4" s="25" t="s">
         <v>4</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="U4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -12471,10 +12534,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="U5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -12793,100 +12856,100 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B2" s="61" t="s">
-        <v>130</v>
-      </c>
-      <c r="C2" s="61"/>
-      <c r="E2" s="57" t="s">
+      <c r="B2" s="56" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2" s="56"/>
+      <c r="E2" s="52" t="s">
+        <v>221</v>
+      </c>
+      <c r="F2" s="52"/>
+      <c r="H2" s="52" t="s">
+        <v>222</v>
+      </c>
+      <c r="I2" s="52"/>
+      <c r="K2" s="52" t="s">
         <v>223</v>
       </c>
-      <c r="F2" s="57"/>
-      <c r="H2" s="57" t="s">
+      <c r="L2" s="52"/>
+      <c r="N2" s="52" t="s">
         <v>224</v>
       </c>
-      <c r="I2" s="57"/>
-      <c r="K2" s="57" t="s">
+      <c r="O2" s="52"/>
+      <c r="Q2" s="52" t="s">
         <v>225</v>
       </c>
-      <c r="L2" s="57"/>
-      <c r="N2" s="57" t="s">
-        <v>226</v>
-      </c>
-      <c r="O2" s="57"/>
-      <c r="Q2" s="57" t="s">
-        <v>227</v>
-      </c>
-      <c r="R2" s="57"/>
+      <c r="R2" s="52"/>
     </row>
     <row r="3" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B3" s="61"/>
-      <c r="C3" s="61"/>
-      <c r="E3" s="38" t="s">
-        <v>215</v>
-      </c>
-      <c r="F3" s="39"/>
-      <c r="H3" s="38" t="s">
-        <v>215</v>
-      </c>
-      <c r="I3" s="39"/>
-      <c r="K3" s="38" t="s">
-        <v>215</v>
-      </c>
-      <c r="L3" s="39"/>
-      <c r="N3" s="38" t="s">
-        <v>215</v>
-      </c>
-      <c r="O3" s="39"/>
-      <c r="Q3" s="38" t="s">
-        <v>215</v>
-      </c>
-      <c r="R3" s="39"/>
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+      <c r="E3" s="34" t="s">
+        <v>213</v>
+      </c>
+      <c r="F3" s="35"/>
+      <c r="H3" s="34" t="s">
+        <v>213</v>
+      </c>
+      <c r="I3" s="35"/>
+      <c r="K3" s="34" t="s">
+        <v>213</v>
+      </c>
+      <c r="L3" s="35"/>
+      <c r="N3" s="34" t="s">
+        <v>213</v>
+      </c>
+      <c r="O3" s="35"/>
+      <c r="Q3" s="34" t="s">
+        <v>213</v>
+      </c>
+      <c r="R3" s="35"/>
       <c r="T3" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="28" t="s">
+      <c r="E4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="I4" s="28" t="s">
+      <c r="I4" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="K4" s="28" t="s">
+      <c r="K4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="L4" s="28" t="s">
+      <c r="L4" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="N4" s="28" t="s">
+      <c r="N4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="O4" s="28" t="s">
+      <c r="O4" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="Q4" s="28" t="s">
+      <c r="Q4" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="R4" s="28" t="s">
+      <c r="R4" s="25" t="s">
         <v>4</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="U4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -12903,10 +12966,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="U5" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -13205,396 +13268,305 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60A900FC-A692-B445-95C9-59E70352B291}">
-  <dimension ref="A2:AK51"/>
+  <dimension ref="A2:AL52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" style="1" customWidth="1"/>
     <col min="3" max="10" width="8.5" style="1" customWidth="1"/>
-    <col min="11" max="35" width="8.5" customWidth="1"/>
-    <col min="36" max="36" width="8.5" style="1" customWidth="1"/>
-    <col min="37" max="37" width="8.5" customWidth="1"/>
+    <col min="11" max="38" width="8.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C2" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E2"/>
       <c r="F2"/>
       <c r="G2"/>
-      <c r="K2" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="Y2" s="6"/>
-      <c r="AE2" s="6" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="L2" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="AB2" s="6"/>
+      <c r="AH2" s="6" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="3" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C3" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F3"/>
       <c r="G3"/>
-      <c r="K3" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="L3" t="s">
-        <v>59</v>
-      </c>
-      <c r="Y3" s="14"/>
-      <c r="AE3" s="1" t="s">
+      <c r="O3" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="P3" t="s">
+        <v>58</v>
+      </c>
+      <c r="AB3" s="14"/>
+      <c r="AH3" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="AI3" t="s">
         <v>168</v>
       </c>
-      <c r="AF3" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D4" t="s">
         <v>70</v>
-      </c>
-      <c r="D4" t="s">
-        <v>71</v>
       </c>
       <c r="F4"/>
       <c r="G4"/>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="42"/>
+      <c r="M4" t="s">
+        <v>161</v>
+      </c>
+      <c r="O4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L4" t="s">
-        <v>60</v>
-      </c>
-      <c r="Y4" s="14"/>
-      <c r="AE4" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="AF4" t="s">
+      <c r="P4" t="s">
+        <v>59</v>
+      </c>
+      <c r="AB4" s="14"/>
+      <c r="AH4" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="C5" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D5" t="s">
+        <v>191</v>
+      </c>
+      <c r="L5" s="26"/>
+      <c r="M5" s="9" t="s">
+        <v>162</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="P5" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB5" s="14"/>
+      <c r="AH5" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="AI5" s="9" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="C6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="L6" s="29"/>
+      <c r="M6" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="P6" t="s">
+        <v>190</v>
+      </c>
+      <c r="AC6" s="1"/>
+      <c r="AD6" s="1"/>
+    </row>
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="C7" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>234</v>
+      </c>
+      <c r="AC7" s="1"/>
+      <c r="AD7" s="1"/>
+    </row>
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="C9" s="45" t="s">
+        <v>236</v>
+      </c>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="45"/>
+      <c r="I9" s="45"/>
+      <c r="J9" s="45"/>
+      <c r="K9" s="45"/>
+      <c r="L9" s="45"/>
+      <c r="M9" s="45"/>
+      <c r="N9" s="45"/>
+      <c r="O9" s="45"/>
+      <c r="P9" s="45"/>
+      <c r="Q9" s="45"/>
+      <c r="R9" s="45"/>
+      <c r="S9" s="45"/>
+      <c r="T9" s="45"/>
+      <c r="U9" s="45"/>
+      <c r="V9" s="45"/>
+      <c r="W9" s="45"/>
+      <c r="X9" s="45"/>
+      <c r="Y9" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z9" s="45"/>
+      <c r="AA9" s="45"/>
+      <c r="AB9" s="45"/>
+      <c r="AC9" s="45"/>
+      <c r="AD9" s="45"/>
+      <c r="AE9" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="AF9" s="45"/>
+      <c r="AG9" s="45"/>
+      <c r="AH9" s="45"/>
+      <c r="AI9" s="45"/>
+      <c r="AJ9" s="45"/>
+      <c r="AK9" s="45"/>
+      <c r="AL9" s="45"/>
+    </row>
+    <row r="10" spans="1:38" ht="18" x14ac:dyDescent="0.25">
+      <c r="A10" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="C10" s="58" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="62" t="s">
+        <v>189</v>
+      </c>
+      <c r="E10" s="57" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="57" t="s">
+        <v>53</v>
+      </c>
+      <c r="G10" s="58" t="s">
+        <v>51</v>
+      </c>
+      <c r="H10" s="57" t="s">
+        <v>72</v>
+      </c>
+      <c r="I10" s="57" t="s">
+        <v>71</v>
+      </c>
+      <c r="J10" s="64" t="s">
+        <v>79</v>
+      </c>
+      <c r="K10" s="64" t="s">
+        <v>135</v>
+      </c>
+      <c r="L10" s="63" t="s">
+        <v>235</v>
+      </c>
+      <c r="M10" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="N10" s="43" t="s">
+        <v>211</v>
+      </c>
+      <c r="O10" s="57" t="s">
+        <v>84</v>
+      </c>
+      <c r="P10" s="57" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q10" s="57" t="s">
+        <v>173</v>
+      </c>
+      <c r="R10" s="57" t="s">
+        <v>174</v>
+      </c>
+      <c r="S10" s="57" t="s">
+        <v>175</v>
+      </c>
+      <c r="T10" s="57" t="s">
+        <v>176</v>
+      </c>
+      <c r="U10" s="57" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="C5" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="D5" t="s">
-        <v>193</v>
-      </c>
-      <c r="K5" s="1" t="s">
+      <c r="V10" s="57" t="s">
+        <v>208</v>
+      </c>
+      <c r="W10" s="57" t="s">
+        <v>209</v>
+      </c>
+      <c r="X10" s="57" t="s">
+        <v>210</v>
+      </c>
+      <c r="Y10" s="59" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z10" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="AA10" s="60" t="s">
+        <v>56</v>
+      </c>
+      <c r="AB10" s="59" t="s">
+        <v>73</v>
+      </c>
+      <c r="AC10" s="59" t="s">
+        <v>80</v>
+      </c>
+      <c r="AD10" s="60" t="s">
+        <v>136</v>
+      </c>
+      <c r="AE10" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="L5" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="Y5" s="14"/>
-      <c r="AE5" s="1" t="s">
-        <v>204</v>
-      </c>
-      <c r="AF5" s="9" t="s">
+      <c r="AF10" s="23" t="s">
+        <v>89</v>
+      </c>
+      <c r="AG10" s="23" t="s">
+        <v>90</v>
+      </c>
+      <c r="AH10" s="23" t="s">
+        <v>165</v>
+      </c>
+      <c r="AI10" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="AJ10" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="AK10" s="23" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="C6" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>209</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="L6" t="s">
-        <v>192</v>
-      </c>
-      <c r="T6" s="1"/>
-      <c r="Z6" s="1"/>
-      <c r="AA6" s="1"/>
-    </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="C8" s="50" t="s">
-        <v>57</v>
-      </c>
-      <c r="D8" s="50"/>
-      <c r="E8" s="50"/>
-      <c r="F8" s="50"/>
-      <c r="G8" s="50"/>
-      <c r="H8" s="50"/>
-      <c r="I8" s="50"/>
-      <c r="J8" s="50"/>
-      <c r="K8" s="50"/>
-      <c r="L8" s="50"/>
-      <c r="M8" s="50"/>
-      <c r="N8" s="50"/>
-      <c r="O8" s="50"/>
-      <c r="P8" s="50"/>
-      <c r="Q8" s="50"/>
-      <c r="R8" s="50"/>
-      <c r="S8" s="50"/>
-      <c r="T8" s="50"/>
-      <c r="U8" s="50"/>
-      <c r="V8" s="50" t="s">
-        <v>58</v>
-      </c>
-      <c r="W8" s="50"/>
-      <c r="X8" s="50"/>
-      <c r="Y8" s="50"/>
-      <c r="Z8" s="50"/>
-      <c r="AA8" s="50"/>
-      <c r="AB8" s="50" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC8" s="50"/>
-      <c r="AD8" s="50"/>
-      <c r="AE8" s="50"/>
-      <c r="AF8" s="50"/>
-      <c r="AG8" s="50"/>
-      <c r="AH8" s="50"/>
-      <c r="AI8" s="50"/>
-      <c r="AJ8" s="50" t="s">
+      <c r="AL10" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="AK8" s="50"/>
-    </row>
-    <row r="9" spans="1:37" ht="18" x14ac:dyDescent="0.25">
-      <c r="A9" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="47" t="s">
-        <v>191</v>
-      </c>
-      <c r="E9" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="F9" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="G9" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="H9" s="21" t="s">
-        <v>73</v>
-      </c>
-      <c r="I9" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="J9" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="K9" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="L9" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="M9" s="21" t="s">
-        <v>176</v>
-      </c>
-      <c r="N9" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="O9" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="P9" s="21" t="s">
-        <v>208</v>
-      </c>
-      <c r="Q9" s="21" t="s">
-        <v>210</v>
-      </c>
-      <c r="R9" s="21" t="s">
-        <v>211</v>
-      </c>
-      <c r="S9" s="21" t="s">
-        <v>212</v>
-      </c>
-      <c r="T9" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="U9" s="21" t="s">
-        <v>174</v>
-      </c>
-      <c r="V9" s="22" t="s">
-        <v>54</v>
-      </c>
-      <c r="W9" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="X9" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="Y9" s="22" t="s">
-        <v>74</v>
-      </c>
-      <c r="Z9" s="22" t="s">
-        <v>81</v>
-      </c>
-      <c r="AA9" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="AB9" s="25" t="s">
-        <v>89</v>
-      </c>
-      <c r="AC9" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="AD9" s="25" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE9" s="25" t="s">
-        <v>167</v>
-      </c>
-      <c r="AF9" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="AG9" s="25" t="s">
-        <v>96</v>
-      </c>
-      <c r="AH9" s="25" t="s">
-        <v>207</v>
-      </c>
-      <c r="AI9" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="AJ9" s="29" t="s">
-        <v>99</v>
-      </c>
-      <c r="AK9" s="48" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="A10" s="3">
+    </row>
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
         <v>1</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>levee</t>
-        </is>
-      </c>
-      <c r="C10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="G10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="K10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="L10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="M10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="N10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="O10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="P10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Q10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="R10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="S10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="T10" s="3" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="U10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="V10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="W10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="X10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Y10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Z10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AA10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AB10" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="AC10" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="AD10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AE10" s="3" t="inlineStr">
-        <is>
-          <t>lf</t>
-        </is>
-      </c>
-      <c r="AF10" s="3">
-        <v>0.001</v>
-      </c>
-      <c r="AG10" s="3">
-        <v>-1.0</v>
-      </c>
-      <c r="AH10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AI10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AJ10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AK10" s="3">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="A11" s="3">
-        <v>2</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t>grout</t>
         </is>
       </c>
       <c r="C11" s="3">
@@ -13620,35 +13592,33 @@
       <c r="K11" s="3">
         <v>0.0</v>
       </c>
-      <c r="L11" s="3">
-        <v>0.0</v>
-      </c>
+      <c r="L11" s="3"/>
       <c r="M11" s="3">
         <v>0.0</v>
       </c>
       <c r="N11" s="3">
         <v>0.0</v>
       </c>
-      <c r="O11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="P11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Q11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="R11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="S11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="T11" s="3" t="inlineStr">
+      <c r="O11" s="3" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
+      <c r="P11" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="R11" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="S11" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="T11" s="3">
+        <v>0.0</v>
+      </c>
       <c r="U11" s="3">
         <v>0.0</v>
       </c>
@@ -13671,45 +13641,48 @@
         <v>0.0</v>
       </c>
       <c r="AB11" s="3">
-        <v>0.2</v>
+        <v>0.0</v>
       </c>
       <c r="AC11" s="3">
-        <v>0.2</v>
+        <v>0.0</v>
       </c>
       <c r="AD11" s="3">
         <v>0.0</v>
       </c>
-      <c r="AE11" s="3" t="inlineStr">
+      <c r="AE11" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="AF11" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="AG11" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AH11" s="3" t="inlineStr">
         <is>
           <t>lf</t>
         </is>
       </c>
-      <c r="AF11" s="3">
+      <c r="AI11" s="3">
         <v>0.001</v>
       </c>
-      <c r="AG11" s="3">
+      <c r="AJ11" s="3">
         <v>-1.0</v>
-      </c>
-      <c r="AH11" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="AI11" s="19">
-        <v>0.0</v>
-      </c>
-      <c r="AJ11" s="3">
-        <v>0.0</v>
       </c>
       <c r="AK11" s="3">
         <v>0.0</v>
       </c>
-    </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL11" s="3">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>foundation</t>
+          <t>grout</t>
         </is>
       </c>
       <c r="C12" s="3">
@@ -13735,35 +13708,33 @@
       <c r="K12" s="3">
         <v>0.0</v>
       </c>
-      <c r="L12" s="3">
-        <v>0.0</v>
-      </c>
+      <c r="L12" s="3"/>
       <c r="M12" s="3">
         <v>0.0</v>
       </c>
       <c r="N12" s="3">
         <v>0.0</v>
       </c>
-      <c r="O12" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="P12" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="R12" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="S12" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="T12" s="3" t="inlineStr">
+      <c r="O12" s="3" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
+      <c r="P12" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="R12" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="S12" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="T12" s="3">
+        <v>0.0</v>
+      </c>
       <c r="U12" s="3">
         <v>0.0</v>
       </c>
@@ -13786,82 +13757,160 @@
         <v>0.0</v>
       </c>
       <c r="AB12" s="3">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="AC12" s="3">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AD12" s="3">
         <v>0.0</v>
       </c>
-      <c r="AE12" s="3" t="inlineStr">
+      <c r="AE12" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="AF12" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="AG12" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AH12" s="3" t="inlineStr">
         <is>
           <t>lf</t>
         </is>
       </c>
-      <c r="AF12" s="3">
+      <c r="AI12" s="3">
         <v>0.001</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AJ12" s="3">
         <v>-1.0</v>
       </c>
-      <c r="AH12" s="18">
+      <c r="AK12" s="18">
         <v>0.0</v>
       </c>
-      <c r="AI12" s="19">
+      <c r="AL12" s="19">
         <v>0.0</v>
       </c>
-      <c r="AJ12" s="3">
+    </row>
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A13" s="3">
+        <v>3</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>foundation</t>
+        </is>
+      </c>
+      <c r="C13" s="3">
         <v>0.0</v>
       </c>
-      <c r="AK12" s="3">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="A13" s="3">
-        <v>4</v>
-      </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
+      <c r="F13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="I13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="K13" s="3">
+        <v>0.0</v>
+      </c>
       <c r="L13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
-      <c r="U13" s="3"/>
-      <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="3"/>
-      <c r="AA13" s="3"/>
-      <c r="AB13" s="3"/>
-      <c r="AC13" s="3"/>
-      <c r="AD13" s="3"/>
-      <c r="AE13" s="3"/>
-      <c r="AF13" s="3"/>
-      <c r="AG13" s="3"/>
-      <c r="AH13" s="3"/>
-      <c r="AI13" s="3"/>
-      <c r="AJ13" s="3"/>
-      <c r="AK13" s="3"/>
-    </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="P13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="T13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="U13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="W13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="X13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Z13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AA13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AB13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AD13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AF13" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AG13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AH13" s="3" t="inlineStr">
+        <is>
+          <t>lf</t>
+        </is>
+      </c>
+      <c r="AI13" s="3">
+        <v>0.001</v>
+      </c>
+      <c r="AJ13" s="3">
+        <v>-1.0</v>
+      </c>
+      <c r="AK13" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="AL13" s="19">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -13899,10 +13948,11 @@
       <c r="AI14" s="3"/>
       <c r="AJ14" s="3"/>
       <c r="AK14" s="3"/>
-    </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL14" s="3"/>
+    </row>
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -13940,10 +13990,11 @@
       <c r="AI15" s="3"/>
       <c r="AJ15" s="3"/>
       <c r="AK15" s="3"/>
-    </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL15" s="3"/>
+    </row>
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -13981,10 +14032,11 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
-    </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL16" s="3"/>
+    </row>
+    <row r="17" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B17" s="3"/>
       <c r="C17" s="3"/>
@@ -14022,10 +14074,11 @@
       <c r="AI17" s="3"/>
       <c r="AJ17" s="3"/>
       <c r="AK17" s="3"/>
-    </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL17" s="3"/>
+    </row>
+    <row r="18" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -14063,10 +14116,11 @@
       <c r="AI18" s="3"/>
       <c r="AJ18" s="3"/>
       <c r="AK18" s="3"/>
-    </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL18" s="3"/>
+    </row>
+    <row r="19" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -14104,10 +14158,11 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
-    </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL19" s="3"/>
+    </row>
+    <row r="20" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -14145,10 +14200,11 @@
       <c r="AI20" s="3"/>
       <c r="AJ20" s="3"/>
       <c r="AK20" s="3"/>
-    </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL20" s="3"/>
+    </row>
+    <row r="21" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -14186,10 +14242,11 @@
       <c r="AI21" s="3"/>
       <c r="AJ21" s="3"/>
       <c r="AK21" s="3"/>
-    </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL21" s="3"/>
+    </row>
+    <row r="22" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -14227,10 +14284,11 @@
       <c r="AI22" s="3"/>
       <c r="AJ22" s="3"/>
       <c r="AK22" s="3"/>
-    </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL22" s="3"/>
+    </row>
+    <row r="23" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -14268,10 +14326,11 @@
       <c r="AI23" s="3"/>
       <c r="AJ23" s="3"/>
       <c r="AK23" s="3"/>
-    </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL23" s="3"/>
+    </row>
+    <row r="24" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -14309,35 +14368,51 @@
       <c r="AI24" s="3"/>
       <c r="AJ24" s="3"/>
       <c r="AK24" s="3"/>
-    </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.2">
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="1"/>
-      <c r="R25" s="1"/>
-      <c r="S25" s="1"/>
-      <c r="T25" s="1"/>
-      <c r="U25" s="1"/>
-      <c r="V25" s="1"/>
-      <c r="W25" s="1"/>
-      <c r="X25" s="1"/>
-      <c r="Y25" s="1"/>
-      <c r="Z25" s="1"/>
-      <c r="AA25" s="1"/>
-      <c r="AB25" s="1"/>
-      <c r="AC25" s="1"/>
-      <c r="AD25" s="1"/>
-      <c r="AE25" s="1"/>
-      <c r="AF25" s="1"/>
-      <c r="AG25" s="1"/>
-      <c r="AH25" s="1"/>
-      <c r="AI25" s="1"/>
-    </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AL24" s="3"/>
+    </row>
+    <row r="25" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="A25" s="3">
+        <v>15</v>
+      </c>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="3"/>
+      <c r="S25" s="3"/>
+      <c r="T25" s="3"/>
+      <c r="U25" s="3"/>
+      <c r="V25" s="3"/>
+      <c r="W25" s="3"/>
+      <c r="X25" s="3"/>
+      <c r="Y25" s="3"/>
+      <c r="Z25" s="3"/>
+      <c r="AA25" s="3"/>
+      <c r="AB25" s="3"/>
+      <c r="AC25" s="3"/>
+      <c r="AD25" s="3"/>
+      <c r="AE25" s="3"/>
+      <c r="AF25" s="3"/>
+      <c r="AG25" s="3"/>
+      <c r="AH25" s="3"/>
+      <c r="AI25" s="3"/>
+      <c r="AJ25" s="3"/>
+      <c r="AK25" s="3"/>
+      <c r="AL25" s="3"/>
+    </row>
+    <row r="26" spans="1:38" x14ac:dyDescent="0.2">
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -14355,8 +14430,19 @@
       <c r="Y26" s="1"/>
       <c r="Z26" s="1"/>
       <c r="AA26" s="1"/>
-    </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AB26" s="1"/>
+      <c r="AC26" s="1"/>
+      <c r="AD26" s="1"/>
+      <c r="AE26" s="1"/>
+      <c r="AF26" s="1"/>
+      <c r="AG26" s="1"/>
+      <c r="AH26" s="1"/>
+      <c r="AI26" s="1"/>
+      <c r="AJ26" s="1"/>
+      <c r="AK26" s="1"/>
+      <c r="AL26" s="1"/>
+    </row>
+    <row r="27" spans="1:38" x14ac:dyDescent="0.2">
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -14374,8 +14460,11 @@
       <c r="Y27" s="1"/>
       <c r="Z27" s="1"/>
       <c r="AA27" s="1"/>
-    </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AB27" s="1"/>
+      <c r="AC27" s="1"/>
+      <c r="AD27" s="1"/>
+    </row>
+    <row r="28" spans="1:38" x14ac:dyDescent="0.2">
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -14393,8 +14482,11 @@
       <c r="Y28" s="1"/>
       <c r="Z28" s="1"/>
       <c r="AA28" s="1"/>
-    </row>
-    <row r="29" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AB28" s="1"/>
+      <c r="AC28" s="1"/>
+      <c r="AD28" s="1"/>
+    </row>
+    <row r="29" spans="1:38" x14ac:dyDescent="0.2">
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -14412,8 +14504,11 @@
       <c r="Y29" s="1"/>
       <c r="Z29" s="1"/>
       <c r="AA29" s="1"/>
-    </row>
-    <row r="30" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AB29" s="1"/>
+      <c r="AC29" s="1"/>
+      <c r="AD29" s="1"/>
+    </row>
+    <row r="30" spans="1:38" x14ac:dyDescent="0.2">
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -14431,8 +14526,11 @@
       <c r="Y30" s="1"/>
       <c r="Z30" s="1"/>
       <c r="AA30" s="1"/>
-    </row>
-    <row r="31" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AB30" s="1"/>
+      <c r="AC30" s="1"/>
+      <c r="AD30" s="1"/>
+    </row>
+    <row r="31" spans="1:38" x14ac:dyDescent="0.2">
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -14450,8 +14548,11 @@
       <c r="Y31" s="1"/>
       <c r="Z31" s="1"/>
       <c r="AA31" s="1"/>
-    </row>
-    <row r="32" spans="1:37" x14ac:dyDescent="0.2">
+      <c r="AB31" s="1"/>
+      <c r="AC31" s="1"/>
+      <c r="AD31" s="1"/>
+    </row>
+    <row r="32" spans="1:38" x14ac:dyDescent="0.2">
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -14469,8 +14570,11 @@
       <c r="Y32" s="1"/>
       <c r="Z32" s="1"/>
       <c r="AA32" s="1"/>
-    </row>
-    <row r="33" spans="11:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="1"/>
+      <c r="AC32" s="1"/>
+      <c r="AD32" s="1"/>
+    </row>
+    <row r="33" spans="11:30" x14ac:dyDescent="0.2">
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -14488,8 +14592,11 @@
       <c r="Y33" s="1"/>
       <c r="Z33" s="1"/>
       <c r="AA33" s="1"/>
-    </row>
-    <row r="34" spans="11:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="1"/>
+      <c r="AC33" s="1"/>
+      <c r="AD33" s="1"/>
+    </row>
+    <row r="34" spans="11:30" x14ac:dyDescent="0.2">
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
@@ -14507,8 +14614,11 @@
       <c r="Y34" s="1"/>
       <c r="Z34" s="1"/>
       <c r="AA34" s="1"/>
-    </row>
-    <row r="35" spans="11:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="1"/>
+      <c r="AC34" s="1"/>
+      <c r="AD34" s="1"/>
+    </row>
+    <row r="35" spans="11:30" x14ac:dyDescent="0.2">
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -14526,8 +14636,11 @@
       <c r="Y35" s="1"/>
       <c r="Z35" s="1"/>
       <c r="AA35" s="1"/>
-    </row>
-    <row r="36" spans="11:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="1"/>
+      <c r="AC35" s="1"/>
+      <c r="AD35" s="1"/>
+    </row>
+    <row r="36" spans="11:30" x14ac:dyDescent="0.2">
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
@@ -14545,8 +14658,11 @@
       <c r="Y36" s="1"/>
       <c r="Z36" s="1"/>
       <c r="AA36" s="1"/>
-    </row>
-    <row r="37" spans="11:27" x14ac:dyDescent="0.2">
+      <c r="AB36" s="1"/>
+      <c r="AC36" s="1"/>
+      <c r="AD36" s="1"/>
+    </row>
+    <row r="37" spans="11:30" x14ac:dyDescent="0.2">
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
@@ -14564,8 +14680,11 @@
       <c r="Y37" s="1"/>
       <c r="Z37" s="1"/>
       <c r="AA37" s="1"/>
-    </row>
-    <row r="38" spans="11:27" x14ac:dyDescent="0.2">
+      <c r="AB37" s="1"/>
+      <c r="AC37" s="1"/>
+      <c r="AD37" s="1"/>
+    </row>
+    <row r="38" spans="11:30" x14ac:dyDescent="0.2">
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -14583,8 +14702,11 @@
       <c r="Y38" s="1"/>
       <c r="Z38" s="1"/>
       <c r="AA38" s="1"/>
-    </row>
-    <row r="39" spans="11:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="1"/>
+      <c r="AC38" s="1"/>
+      <c r="AD38" s="1"/>
+    </row>
+    <row r="39" spans="11:30" x14ac:dyDescent="0.2">
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -14602,8 +14724,11 @@
       <c r="Y39" s="1"/>
       <c r="Z39" s="1"/>
       <c r="AA39" s="1"/>
-    </row>
-    <row r="40" spans="11:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="1"/>
+      <c r="AC39" s="1"/>
+      <c r="AD39" s="1"/>
+    </row>
+    <row r="40" spans="11:30" x14ac:dyDescent="0.2">
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -14621,8 +14746,11 @@
       <c r="Y40" s="1"/>
       <c r="Z40" s="1"/>
       <c r="AA40" s="1"/>
-    </row>
-    <row r="41" spans="11:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="1"/>
+      <c r="AC40" s="1"/>
+      <c r="AD40" s="1"/>
+    </row>
+    <row r="41" spans="11:30" x14ac:dyDescent="0.2">
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
@@ -14640,8 +14768,11 @@
       <c r="Y41" s="1"/>
       <c r="Z41" s="1"/>
       <c r="AA41" s="1"/>
-    </row>
-    <row r="42" spans="11:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="1"/>
+      <c r="AC41" s="1"/>
+      <c r="AD41" s="1"/>
+    </row>
+    <row r="42" spans="11:30" x14ac:dyDescent="0.2">
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
@@ -14659,8 +14790,11 @@
       <c r="Y42" s="1"/>
       <c r="Z42" s="1"/>
       <c r="AA42" s="1"/>
-    </row>
-    <row r="43" spans="11:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="1"/>
+      <c r="AC42" s="1"/>
+      <c r="AD42" s="1"/>
+    </row>
+    <row r="43" spans="11:30" x14ac:dyDescent="0.2">
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
@@ -14678,8 +14812,11 @@
       <c r="Y43" s="1"/>
       <c r="Z43" s="1"/>
       <c r="AA43" s="1"/>
-    </row>
-    <row r="44" spans="11:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="1"/>
+      <c r="AC43" s="1"/>
+      <c r="AD43" s="1"/>
+    </row>
+    <row r="44" spans="11:30" x14ac:dyDescent="0.2">
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
@@ -14697,8 +14834,11 @@
       <c r="Y44" s="1"/>
       <c r="Z44" s="1"/>
       <c r="AA44" s="1"/>
-    </row>
-    <row r="45" spans="11:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="1"/>
+      <c r="AC44" s="1"/>
+      <c r="AD44" s="1"/>
+    </row>
+    <row r="45" spans="11:30" x14ac:dyDescent="0.2">
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
@@ -14716,8 +14856,11 @@
       <c r="Y45" s="1"/>
       <c r="Z45" s="1"/>
       <c r="AA45" s="1"/>
-    </row>
-    <row r="46" spans="11:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="1"/>
+      <c r="AC45" s="1"/>
+      <c r="AD45" s="1"/>
+    </row>
+    <row r="46" spans="11:30" x14ac:dyDescent="0.2">
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
@@ -14735,8 +14878,11 @@
       <c r="Y46" s="1"/>
       <c r="Z46" s="1"/>
       <c r="AA46" s="1"/>
-    </row>
-    <row r="47" spans="11:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="1"/>
+      <c r="AC46" s="1"/>
+      <c r="AD46" s="1"/>
+    </row>
+    <row r="47" spans="11:30" x14ac:dyDescent="0.2">
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
@@ -14754,8 +14900,11 @@
       <c r="Y47" s="1"/>
       <c r="Z47" s="1"/>
       <c r="AA47" s="1"/>
-    </row>
-    <row r="48" spans="11:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="1"/>
+      <c r="AC47" s="1"/>
+      <c r="AD47" s="1"/>
+    </row>
+    <row r="48" spans="11:30" x14ac:dyDescent="0.2">
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
       <c r="M48" s="1"/>
@@ -14773,8 +14922,11 @@
       <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
       <c r="AA48" s="1"/>
-    </row>
-    <row r="49" spans="11:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="1"/>
+      <c r="AC48" s="1"/>
+      <c r="AD48" s="1"/>
+    </row>
+    <row r="49" spans="11:30" x14ac:dyDescent="0.2">
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
       <c r="M49" s="1"/>
@@ -14792,8 +14944,11 @@
       <c r="Y49" s="1"/>
       <c r="Z49" s="1"/>
       <c r="AA49" s="1"/>
-    </row>
-    <row r="50" spans="11:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="1"/>
+      <c r="AC49" s="1"/>
+      <c r="AD49" s="1"/>
+    </row>
+    <row r="50" spans="11:30" x14ac:dyDescent="0.2">
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
       <c r="M50" s="1"/>
@@ -14811,8 +14966,11 @@
       <c r="Y50" s="1"/>
       <c r="Z50" s="1"/>
       <c r="AA50" s="1"/>
-    </row>
-    <row r="51" spans="11:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="1"/>
+      <c r="AC50" s="1"/>
+      <c r="AD50" s="1"/>
+    </row>
+    <row r="51" spans="11:30" x14ac:dyDescent="0.2">
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
       <c r="M51" s="1"/>
@@ -14830,88 +14988,125 @@
       <c r="Y51" s="1"/>
       <c r="Z51" s="1"/>
       <c r="AA51" s="1"/>
+      <c r="AB51" s="1"/>
+      <c r="AC51" s="1"/>
+      <c r="AD51" s="1"/>
+    </row>
+    <row r="52" spans="11:30" x14ac:dyDescent="0.2">
+      <c r="K52" s="1"/>
+      <c r="L52" s="1"/>
+      <c r="M52" s="1"/>
+      <c r="N52" s="1"/>
+      <c r="O52" s="1"/>
+      <c r="P52" s="1"/>
+      <c r="Q52" s="1"/>
+      <c r="R52" s="1"/>
+      <c r="S52" s="1"/>
+      <c r="T52" s="1"/>
+      <c r="U52" s="1"/>
+      <c r="V52" s="1"/>
+      <c r="W52" s="1"/>
+      <c r="X52" s="1"/>
+      <c r="Y52" s="1"/>
+      <c r="Z52" s="1"/>
+      <c r="AA52" s="1"/>
+      <c r="AB52" s="1"/>
+      <c r="AC52" s="1"/>
+      <c r="AD52" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="V8:AA8"/>
-    <mergeCell ref="AJ8:AK8"/>
-    <mergeCell ref="AB8:AI8"/>
-    <mergeCell ref="C8:U8"/>
+  <mergeCells count="3">
+    <mergeCell ref="Y9:AD9"/>
+    <mergeCell ref="AE9:AL9"/>
+    <mergeCell ref="C9:X9"/>
   </mergeCells>
-  <conditionalFormatting sqref="F10:K51 W10:AA51">
-    <cfRule type="expression" dxfId="15" priority="2">
-      <formula>$E10="hb"</formula>
+  <conditionalFormatting sqref="F11:K52 Z11:AD52">
+    <cfRule type="expression" dxfId="5" priority="1">
+      <formula>$E11="hb"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="2">
+      <formula>$E11="pow"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G10:G51">
-    <cfRule type="expression" dxfId="14" priority="7">
-      <formula>$E10="cp"</formula>
+  <conditionalFormatting sqref="G11:G52">
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>$E11="cp"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H10:I51">
-    <cfRule type="expression" dxfId="13" priority="6">
-      <formula>$E10="mc"</formula>
+  <conditionalFormatting sqref="H11:I52">
+    <cfRule type="expression" dxfId="5" priority="4">
+      <formula>$E11="mc"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J10:K51">
-    <cfRule type="expression" dxfId="12" priority="8">
-      <formula>$E10="cp"</formula>
+  <conditionalFormatting sqref="J11:K52">
+    <cfRule type="expression" dxfId="5" priority="5">
+      <formula>$E11="cp"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L10:O51">
-    <cfRule type="expression" dxfId="11" priority="21">
-      <formula>AND($E10&lt;&gt;"",$E10&lt;&gt;"pow")</formula>
+  <conditionalFormatting sqref="Q11:T52">
+    <cfRule type="expression" dxfId="5" priority="6">
+      <formula>AND($E11&lt;&gt;"",$E11&lt;&gt;"pow")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P10:S51">
-    <cfRule type="expression" dxfId="10" priority="1">
-      <formula>AND($E10&lt;&gt;"",$E10&lt;&gt;"hb")</formula>
+  <conditionalFormatting sqref="U11:X52">
+    <cfRule type="expression" dxfId="5" priority="7">
+      <formula>AND($E11&lt;&gt;"",$E11&lt;&gt;"hb")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U10:U51">
-    <cfRule type="expression" dxfId="9" priority="22">
-      <formula>AND($T10&lt;&gt;"",$T10&lt;&gt;"ru")</formula>
+  <conditionalFormatting sqref="P11:P52">
+    <cfRule type="expression" dxfId="5" priority="8">
+      <formula>AND($O11&lt;&gt;"",$O11&lt;&gt;"ru")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W10:AA51 F10:K51">
-    <cfRule type="expression" dxfId="8" priority="18">
-      <formula>$E10="pow"</formula>
+  <conditionalFormatting sqref="AA11:AA52">
+    <cfRule type="expression" dxfId="5" priority="9">
+      <formula>$E11="cp"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="X10:X51">
-    <cfRule type="expression" dxfId="7" priority="10">
-      <formula>$E10="cp"</formula>
+  <conditionalFormatting sqref="AB11:AB52">
+    <cfRule type="expression" dxfId="5" priority="10">
+      <formula>$E11="mc"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Y10:Y51">
-    <cfRule type="expression" dxfId="6" priority="17">
-      <formula>$E10="mc"</formula>
+  <conditionalFormatting sqref="AC11:AD52">
+    <cfRule type="expression" dxfId="5" priority="11">
+      <formula>$E11="cp"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z10:AA51">
+  <conditionalFormatting sqref="AI11:AJ52">
     <cfRule type="expression" dxfId="5" priority="12">
-      <formula>$E10="cp"</formula>
+      <formula>OR($AH11="vg",$AH11="gard")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF10:AG101">
-    <cfRule type="expression" dxfId="4" priority="4">
-      <formula>OR($AE10="vg",$AE10="gard")</formula>
+  <conditionalFormatting sqref="AK11:AL52">
+    <cfRule type="expression" dxfId="5" priority="13">
+      <formula>$AH11="lf"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AH10:AI101">
-    <cfRule type="expression" dxfId="3" priority="3">
-      <formula>$AE10="lf"</formula>
+  <conditionalFormatting sqref="F11:L52">
+    <cfRule type="expression" dxfId="5" priority="14">
+      <formula>$E11="elastic"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O11:P52">
+    <cfRule type="expression" dxfId="5" priority="15">
+      <formula>$E11="elastic"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z11:AD52">
+    <cfRule type="expression" dxfId="5" priority="16">
+      <formula>$E11="elastic"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E10:E51" xr:uid="{374AFD2C-B540-DD4B-A245-8B781F76E64C}">
-      <formula1>$C$3:$C$6</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E11:E52" xr:uid="{374AFD2C-B540-DD4B-A245-8B781F76E64C}">
+      <formula1>$C$3:$C$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="T10:T51" xr:uid="{D770415C-1ECE-F44B-9D8C-08EF1CF31C8E}">
-      <formula1>$K$3:$K$6</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH11:AH102" xr:uid="{E00A94A9-D864-5843-8FBD-E84775B1C100}">
+      <formula1>$AH$3:$AH$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AE10:AE101" xr:uid="{E00A94A9-D864-5843-8FBD-E84775B1C100}">
-      <formula1>$AE$3:$AE$5</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O11:O52" xr:uid="{D770415C-1ECE-F44B-9D8C-08EF1CF31C8E}">
+      <formula1>$O$3:$O$6</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14951,264 +15146,264 @@
       <c r="B2" s="3">
         <v>0</v>
       </c>
-      <c r="D2" s="27" t="s">
-        <v>93</v>
+      <c r="D2" s="24" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A4" s="53" t="s">
+      <c r="A4" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="53"/>
-      <c r="D4" s="53" t="s">
+      <c r="B4" s="48"/>
+      <c r="D4" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="53"/>
-      <c r="G4" s="53" t="s">
+      <c r="E4" s="48"/>
+      <c r="G4" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="53"/>
-      <c r="J4" s="53" t="s">
+      <c r="H4" s="48"/>
+      <c r="J4" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="53"/>
-      <c r="M4" s="53" t="s">
+      <c r="K4" s="48"/>
+      <c r="M4" s="48" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="53"/>
-      <c r="P4" s="53" t="s">
+      <c r="N4" s="48"/>
+      <c r="P4" s="48" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" s="53"/>
+      <c r="Q4" s="48"/>
       <c r="R4" s="1"/>
-      <c r="S4" s="53" t="s">
+      <c r="S4" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="T4" s="53"/>
+      <c r="T4" s="48"/>
       <c r="U4" s="1"/>
-      <c r="V4" s="53" t="s">
+      <c r="V4" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="W4" s="53"/>
+      <c r="W4" s="48"/>
       <c r="X4" s="1"/>
-      <c r="Y4" s="53" t="s">
+      <c r="Y4" s="48" t="s">
         <v>12</v>
       </c>
-      <c r="Z4" s="53"/>
+      <c r="Z4" s="48"/>
       <c r="AA4" s="1"/>
-      <c r="AB4" s="53" t="s">
+      <c r="AB4" s="48" t="s">
         <v>13</v>
       </c>
-      <c r="AC4" s="53"/>
-      <c r="AE4" s="53" t="s">
+      <c r="AC4" s="48"/>
+      <c r="AE4" s="48" t="s">
+        <v>108</v>
+      </c>
+      <c r="AF4" s="48"/>
+      <c r="AG4" s="1"/>
+      <c r="AH4" s="48" t="s">
+        <v>109</v>
+      </c>
+      <c r="AI4" s="48"/>
+      <c r="AJ4" s="1"/>
+      <c r="AK4" s="48" t="s">
         <v>110</v>
       </c>
-      <c r="AF4" s="53"/>
-      <c r="AG4" s="1"/>
-      <c r="AH4" s="53" t="s">
+      <c r="AL4" s="48"/>
+      <c r="AM4" s="1"/>
+      <c r="AN4" s="48" t="s">
         <v>111</v>
       </c>
-      <c r="AI4" s="53"/>
-      <c r="AJ4" s="1"/>
-      <c r="AK4" s="53" t="s">
+      <c r="AO4" s="48"/>
+      <c r="AP4" s="1"/>
+      <c r="AQ4" s="48" t="s">
         <v>112</v>
       </c>
-      <c r="AL4" s="53"/>
-      <c r="AM4" s="1"/>
-      <c r="AN4" s="53" t="s">
-        <v>113</v>
-      </c>
-      <c r="AO4" s="53"/>
-      <c r="AP4" s="1"/>
-      <c r="AQ4" s="53" t="s">
-        <v>114</v>
-      </c>
-      <c r="AR4" s="53"/>
+      <c r="AR4" s="48"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A5" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="B5" s="41">
+      <c r="A5" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" s="37">
         <v>1</v>
       </c>
-      <c r="D5" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="E5" s="41">
+      <c r="D5" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="E5" s="37">
         <v>2</v>
       </c>
-      <c r="G5" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="H5" s="41">
+      <c r="G5" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="H5" s="37">
         <v>3</v>
       </c>
-      <c r="J5" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="K5" s="41">
+      <c r="J5" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="K5" s="37">
         <v>4</v>
       </c>
-      <c r="M5" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="N5" s="41">
+      <c r="M5" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="N5" s="37">
         <v>5</v>
       </c>
-      <c r="P5" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q5" s="41">
+      <c r="P5" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q5" s="37">
         <v>6</v>
       </c>
       <c r="R5" s="1"/>
-      <c r="S5" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="T5" s="41">
+      <c r="S5" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="T5" s="37">
         <v>7</v>
       </c>
       <c r="U5" s="1"/>
-      <c r="V5" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="W5" s="41">
+      <c r="V5" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="W5" s="37">
         <v>8</v>
       </c>
       <c r="X5" s="1"/>
-      <c r="Y5" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="Z5" s="41">
+      <c r="Y5" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="Z5" s="37">
         <v>9</v>
       </c>
       <c r="AA5" s="1"/>
-      <c r="AB5" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="AC5" s="41">
+      <c r="AB5" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="AC5" s="37">
         <v>10</v>
       </c>
-      <c r="AE5" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="AF5" s="41">
+      <c r="AE5" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF5" s="37">
         <v>11</v>
       </c>
       <c r="AG5" s="1"/>
-      <c r="AH5" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="AI5" s="41">
+      <c r="AH5" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="AI5" s="37">
         <v>12</v>
       </c>
       <c r="AJ5" s="1"/>
-      <c r="AK5" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="AL5" s="41">
+      <c r="AK5" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="AL5" s="37">
         <v>13</v>
       </c>
       <c r="AM5" s="1"/>
-      <c r="AN5" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="AO5" s="41">
+      <c r="AN5" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="AO5" s="37">
         <v>14</v>
       </c>
       <c r="AP5" s="1"/>
-      <c r="AQ5" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="AR5" s="41">
+      <c r="AQ5" s="36" t="s">
+        <v>120</v>
+      </c>
+      <c r="AR5" s="37">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A6" s="51" t="str">
+      <c r="A6" s="46" t="str">
         <f>_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="B6" s="52"/>
-      <c r="D6" s="51" t="str">
+      <c r="B6" s="47"/>
+      <c r="D6" s="46" t="str">
         <f>_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="E6" s="52"/>
-      <c r="G6" s="51" t="str">
+      <c r="E6" s="47"/>
+      <c r="G6" s="46" t="str">
         <f>_xlfn.XLOOKUP(H5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="H6" s="52"/>
-      <c r="J6" s="51" t="str">
+      <c r="H6" s="47"/>
+      <c r="J6" s="46" t="str">
         <f>_xlfn.XLOOKUP(K5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="K6" s="52"/>
-      <c r="M6" s="51" t="str">
+      <c r="K6" s="47"/>
+      <c r="M6" s="46" t="str">
         <f>_xlfn.XLOOKUP(N5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="N6" s="52"/>
-      <c r="P6" s="51" t="str">
+      <c r="N6" s="47"/>
+      <c r="P6" s="46" t="str">
         <f>_xlfn.XLOOKUP(Q5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Q6" s="52"/>
+      <c r="Q6" s="47"/>
       <c r="R6" s="1"/>
-      <c r="S6" s="51" t="str">
+      <c r="S6" s="46" t="str">
         <f>_xlfn.XLOOKUP(T5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="T6" s="52"/>
+      <c r="T6" s="47"/>
       <c r="U6" s="1"/>
-      <c r="V6" s="51" t="str">
+      <c r="V6" s="46" t="str">
         <f>_xlfn.XLOOKUP(W5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="W6" s="52"/>
+      <c r="W6" s="47"/>
       <c r="X6" s="1"/>
-      <c r="Y6" s="51" t="str">
+      <c r="Y6" s="46" t="str">
         <f>_xlfn.XLOOKUP(Z5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Z6" s="52"/>
+      <c r="Z6" s="47"/>
       <c r="AA6" s="1"/>
-      <c r="AB6" s="51" t="str">
+      <c r="AB6" s="46" t="str">
         <f>_xlfn.XLOOKUP(AC5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AC6" s="52"/>
-      <c r="AE6" s="51" t="str">
+      <c r="AC6" s="47"/>
+      <c r="AE6" s="46" t="str">
         <f>_xlfn.XLOOKUP(AF5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AF6" s="52"/>
+      <c r="AF6" s="47"/>
       <c r="AG6" s="1"/>
-      <c r="AH6" s="51" t="str">
+      <c r="AH6" s="46" t="str">
         <f>_xlfn.XLOOKUP(AI5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AI6" s="52"/>
+      <c r="AI6" s="47"/>
       <c r="AJ6" s="1"/>
-      <c r="AK6" s="51" t="str">
+      <c r="AK6" s="46" t="str">
         <f>_xlfn.XLOOKUP(AL5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AL6" s="52"/>
+      <c r="AL6" s="47"/>
       <c r="AM6" s="1"/>
-      <c r="AN6" s="51" t="str">
+      <c r="AN6" s="46" t="str">
         <f>_xlfn.XLOOKUP(AO5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AO6" s="52"/>
+      <c r="AO6" s="47"/>
       <c r="AP6" s="1"/>
-      <c r="AQ6" s="51" t="str">
+      <c r="AQ6" s="46" t="str">
         <f>_xlfn.XLOOKUP(AR5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AR6" s="52"/>
+      <c r="AR6" s="47"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -16174,276 +16369,276 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
-        <v>158</v>
+      <c r="A2" s="24" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A4" s="53" t="inlineStr">
+      <c r="A4" s="48" t="inlineStr">
         <is>
           <t>Polygon #1</t>
         </is>
       </c>
-      <c r="B4" s="53"/>
-      <c r="D4" s="53" t="inlineStr">
+      <c r="B4" s="48"/>
+      <c r="D4" s="48" t="inlineStr">
         <is>
           <t>Polygon #2</t>
         </is>
       </c>
-      <c r="E4" s="53"/>
-      <c r="G4" s="53" t="inlineStr">
+      <c r="E4" s="48"/>
+      <c r="G4" s="48" t="inlineStr">
         <is>
           <t>Polygon #3</t>
         </is>
       </c>
-      <c r="H4" s="53"/>
-      <c r="J4" s="53" t="inlineStr">
+      <c r="H4" s="48"/>
+      <c r="J4" s="48" t="inlineStr">
         <is>
           <t>Polygon #4</t>
         </is>
       </c>
-      <c r="K4" s="53"/>
-      <c r="M4" s="53" t="s">
+      <c r="K4" s="48"/>
+      <c r="M4" s="48" t="s">
+        <v>141</v>
+      </c>
+      <c r="N4" s="48"/>
+      <c r="P4" s="48" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q4" s="48"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="48" t="s">
         <v>143</v>
       </c>
-      <c r="N4" s="53"/>
-      <c r="P4" s="53" t="s">
+      <c r="T4" s="48"/>
+      <c r="U4" s="1"/>
+      <c r="V4" s="48" t="s">
         <v>144</v>
       </c>
-      <c r="Q4" s="53"/>
-      <c r="R4" s="1"/>
-      <c r="S4" s="53" t="s">
+      <c r="W4" s="48"/>
+      <c r="X4" s="1"/>
+      <c r="Y4" s="48" t="s">
         <v>145</v>
       </c>
-      <c r="T4" s="53"/>
-      <c r="U4" s="1"/>
-      <c r="V4" s="53" t="s">
+      <c r="Z4" s="48"/>
+      <c r="AA4" s="1"/>
+      <c r="AB4" s="48" t="s">
         <v>146</v>
       </c>
-      <c r="W4" s="53"/>
-      <c r="X4" s="1"/>
-      <c r="Y4" s="53" t="s">
+      <c r="AC4" s="48"/>
+      <c r="AE4" s="48" t="s">
         <v>147</v>
       </c>
-      <c r="Z4" s="53"/>
-      <c r="AA4" s="1"/>
-      <c r="AB4" s="53" t="s">
+      <c r="AF4" s="48"/>
+      <c r="AG4" s="1"/>
+      <c r="AH4" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="AC4" s="53"/>
-      <c r="AE4" s="53" t="s">
+      <c r="AI4" s="48"/>
+      <c r="AJ4" s="1"/>
+      <c r="AK4" s="48" t="s">
         <v>149</v>
       </c>
-      <c r="AF4" s="53"/>
-      <c r="AG4" s="1"/>
-      <c r="AH4" s="53" t="s">
+      <c r="AL4" s="48"/>
+      <c r="AM4" s="1"/>
+      <c r="AN4" s="48" t="s">
         <v>150</v>
       </c>
-      <c r="AI4" s="53"/>
-      <c r="AJ4" s="1"/>
-      <c r="AK4" s="53" t="s">
+      <c r="AO4" s="48"/>
+      <c r="AP4" s="1"/>
+      <c r="AQ4" s="48" t="s">
         <v>151</v>
       </c>
-      <c r="AL4" s="53"/>
-      <c r="AM4" s="1"/>
-      <c r="AN4" s="53" t="s">
-        <v>152</v>
-      </c>
-      <c r="AO4" s="53"/>
-      <c r="AP4" s="1"/>
-      <c r="AQ4" s="53" t="s">
-        <v>153</v>
-      </c>
-      <c r="AR4" s="53"/>
+      <c r="AR4" s="48"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A5" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="B5" s="43">
+      <c r="A5" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" s="39">
         <v>1</v>
       </c>
-      <c r="D5" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="E5" s="43">
+      <c r="D5" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="E5" s="39">
         <v>3</v>
       </c>
-      <c r="G5" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="H5" s="43">
+      <c r="G5" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="H5" s="39">
         <v>2</v>
       </c>
-      <c r="J5" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="K5" s="43">
+      <c r="J5" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="K5" s="39">
         <v>3</v>
       </c>
-      <c r="M5" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="N5" s="43">
+      <c r="M5" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="N5" s="39">
         <v>5</v>
       </c>
-      <c r="P5" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q5" s="43">
+      <c r="P5" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q5" s="39">
         <v>6</v>
       </c>
       <c r="R5" s="1"/>
-      <c r="S5" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="T5" s="43">
+      <c r="S5" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="T5" s="39">
         <v>7</v>
       </c>
       <c r="U5" s="1"/>
-      <c r="V5" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="W5" s="43">
+      <c r="V5" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="W5" s="39">
         <v>8</v>
       </c>
       <c r="X5" s="1"/>
-      <c r="Y5" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="Z5" s="43">
+      <c r="Y5" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="Z5" s="39">
         <v>9</v>
       </c>
       <c r="AA5" s="1"/>
-      <c r="AB5" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="AC5" s="43">
+      <c r="AB5" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="AC5" s="39">
         <v>10</v>
       </c>
-      <c r="AE5" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="AF5" s="43">
+      <c r="AE5" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF5" s="39">
         <v>11</v>
       </c>
       <c r="AG5" s="1"/>
-      <c r="AH5" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="AI5" s="43">
+      <c r="AH5" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="AI5" s="39">
         <v>12</v>
       </c>
       <c r="AJ5" s="1"/>
-      <c r="AK5" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="AL5" s="43">
+      <c r="AK5" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="AL5" s="39">
         <v>13</v>
       </c>
       <c r="AM5" s="1"/>
-      <c r="AN5" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="AO5" s="43">
+      <c r="AN5" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="AO5" s="39">
         <v>14</v>
       </c>
       <c r="AP5" s="1"/>
-      <c r="AQ5" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="AR5" s="43">
+      <c r="AQ5" s="38" t="s">
+        <v>120</v>
+      </c>
+      <c r="AR5" s="39">
         <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A6" s="54" t="inlineStr">
+      <c r="A6" s="49" t="inlineStr">
         <is>
           <t>levee</t>
         </is>
       </c>
-      <c r="B6" s="55"/>
-      <c r="D6" s="54" t="inlineStr">
+      <c r="B6" s="50"/>
+      <c r="D6" s="49" t="inlineStr">
         <is>
           <t>foundation</t>
         </is>
       </c>
-      <c r="E6" s="55"/>
-      <c r="G6" s="54" t="inlineStr">
+      <c r="E6" s="50"/>
+      <c r="G6" s="49" t="inlineStr">
         <is>
           <t>grout</t>
         </is>
       </c>
-      <c r="H6" s="55"/>
-      <c r="J6" s="54" t="inlineStr">
+      <c r="H6" s="50"/>
+      <c r="J6" s="49" t="inlineStr">
         <is>
           <t>foundation</t>
         </is>
       </c>
-      <c r="K6" s="55"/>
-      <c r="M6" s="54" t="str">
+      <c r="K6" s="50"/>
+      <c r="M6" s="49" t="str">
         <f>_xlfn.XLOOKUP(N5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="N6" s="55"/>
-      <c r="P6" s="54" t="str">
+      <c r="N6" s="50"/>
+      <c r="P6" s="49" t="str">
         <f>_xlfn.XLOOKUP(Q5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Q6" s="55"/>
+      <c r="Q6" s="50"/>
       <c r="R6" s="1"/>
-      <c r="S6" s="54" t="str">
+      <c r="S6" s="49" t="str">
         <f>_xlfn.XLOOKUP(T5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="T6" s="55"/>
+      <c r="T6" s="50"/>
       <c r="U6" s="1"/>
-      <c r="V6" s="54" t="str">
+      <c r="V6" s="49" t="str">
         <f>_xlfn.XLOOKUP(W5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="W6" s="55"/>
+      <c r="W6" s="50"/>
       <c r="X6" s="1"/>
-      <c r="Y6" s="54" t="str">
+      <c r="Y6" s="49" t="str">
         <f>_xlfn.XLOOKUP(Z5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Z6" s="55"/>
+      <c r="Z6" s="50"/>
       <c r="AA6" s="1"/>
-      <c r="AB6" s="54" t="str">
+      <c r="AB6" s="49" t="str">
         <f>_xlfn.XLOOKUP(AC5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AC6" s="55"/>
-      <c r="AE6" s="54" t="str">
+      <c r="AC6" s="50"/>
+      <c r="AE6" s="49" t="str">
         <f>_xlfn.XLOOKUP(AF5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AF6" s="55"/>
+      <c r="AF6" s="50"/>
       <c r="AG6" s="1"/>
-      <c r="AH6" s="54" t="str">
+      <c r="AH6" s="49" t="str">
         <f>_xlfn.XLOOKUP(AI5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AI6" s="55"/>
+      <c r="AI6" s="50"/>
       <c r="AJ6" s="1"/>
-      <c r="AK6" s="54" t="str">
+      <c r="AK6" s="49" t="str">
         <f>_xlfn.XLOOKUP(AL5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AL6" s="55"/>
+      <c r="AL6" s="50"/>
       <c r="AM6" s="1"/>
-      <c r="AN6" s="54" t="str">
+      <c r="AN6" s="49" t="str">
         <f>_xlfn.XLOOKUP(AO5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AO6" s="55"/>
+      <c r="AO6" s="50"/>
       <c r="AP6" s="1"/>
-      <c r="AQ6" s="54" t="str">
+      <c r="AQ6" s="49" t="str">
         <f>_xlfn.XLOOKUP(AR5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AR6" s="55"/>
+      <c r="AR6" s="50"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -17476,36 +17671,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="56" t="s">
-        <v>84</v>
-      </c>
-      <c r="B2" s="56"/>
-      <c r="D2" s="57" t="s">
+      <c r="A2" s="51" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" s="51"/>
+      <c r="D2" s="52" t="s">
+        <v>81</v>
+      </c>
+      <c r="E2" s="52"/>
+      <c r="G2" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="E2" s="57"/>
-      <c r="G2" s="24" t="s">
-        <v>83</v>
-      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A3" s="36" t="s">
-        <v>198</v>
-      </c>
-      <c r="B3" s="37" t="inlineStr">
+      <c r="A3" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="B3" s="33" t="inlineStr">
         <is>
           <t>piezo</t>
         </is>
       </c>
-      <c r="D3" s="38" t="s">
-        <v>198</v>
-      </c>
-      <c r="E3" s="39" t="inlineStr">
+      <c r="D3" s="34" t="s">
+        <v>196</v>
+      </c>
+      <c r="E3" s="35" t="inlineStr">
         <is>
           <t>piezo</t>
         </is>
       </c>
-      <c r="G3" s="24"/>
+      <c r="G3" s="22"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
@@ -17521,7 +17716,7 @@
         <v>4</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H4" s="1"/>
     </row>
@@ -17534,7 +17729,7 @@
         <v>21</v>
       </c>
       <c r="H5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -17543,10 +17738,10 @@
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="G6" s="1" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="H6" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -17686,10 +17881,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2" s="13" t="s">
         <v>61</v>
-      </c>
-      <c r="C2" s="13" t="s">
-        <v>62</v>
       </c>
       <c r="D2" s="13" t="s">
         <v>29</v>
@@ -17704,7 +17899,7 @@
         <v>28</v>
       </c>
       <c r="H2" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>30</v>
@@ -17761,10 +17956,10 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="J5" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -17936,10 +18131,10 @@
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="E5" t="s">
+        <v>75</v>
+      </c>
+      <c r="F5" t="s">
         <v>76</v>
-      </c>
-      <c r="F5" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -18062,36 +18257,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="F2" s="53" t="s">
+        <v>122</v>
+      </c>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="J2" s="53" t="s">
         <v>123</v>
       </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="F2" s="58" t="s">
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="N2" s="53" t="s">
         <v>124</v>
       </c>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="J2" s="58" t="s">
+      <c r="O2" s="53"/>
+      <c r="P2" s="53"/>
+      <c r="R2" s="53" t="s">
         <v>125</v>
       </c>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="N2" s="58" t="s">
+      <c r="S2" s="53"/>
+      <c r="T2" s="53"/>
+      <c r="V2" s="53" t="s">
         <v>126</v>
       </c>
-      <c r="O2" s="58"/>
-      <c r="P2" s="58"/>
-      <c r="R2" s="58" t="s">
-        <v>127</v>
-      </c>
-      <c r="S2" s="58"/>
-      <c r="T2" s="58"/>
-      <c r="V2" s="58" t="s">
-        <v>128</v>
-      </c>
-      <c r="W2" s="58"/>
-      <c r="X2" s="58"/>
+      <c r="W2" s="53"/>
+      <c r="X2" s="53"/>
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">

--- a/docs/usage/sample_sheets/sheets_polygon.xlsx
+++ b/docs/usage/sample_sheets/sheets_polygon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{448736C4-E2C8-EB41-827A-888C500BCAB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9AE3CBE-0B2A-ED44-BB50-AACC6A5490D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19900" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="35040" windowHeight="19900" xr2:uid="{BA54C293-CE08-6E4C-9212-B3317DAA148E}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="240">
   <si>
     <t>X</t>
   </si>
@@ -941,6 +941,12 @@
   </si>
   <si>
     <t>Color legend</t>
+  </si>
+  <si>
+    <t>phi_b</t>
+  </si>
+  <si>
+    <t>s_cap</t>
   </si>
 </sst>
 </file>
@@ -1090,7 +1096,7 @@
       <name val="Aptos Narrow"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1187,12 +1193,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="-0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="7">
     <border>
@@ -1280,7 +1280,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1397,19 +1397,37 @@
     <xf numFmtId="0" fontId="20" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1436,35 +1454,11 @@
     <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="16">
+  <dxfs count="19">
     <dxf>
       <fill>
         <patternFill>
@@ -1483,34 +1477,6 @@
       <fill>
         <patternFill>
           <bgColor theme="1" tint="0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1559,7 +1525,56 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="2" tint="-0.499984740745262"/>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -10431,15 +10446,15 @@
         <v>78</v>
       </c>
       <c r="D5" s="30">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B7" s="44" t="s">
+      <c r="B7" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="44"/>
-      <c r="D7" s="44"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
       <c r="F7" s="15" t="s">
         <v>15</v>
       </c>
@@ -10619,36 +10634,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B2" s="54" t="s">
+      <c r="B2" s="60" t="s">
         <v>129</v>
       </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="54"/>
-      <c r="F2" s="54" t="s">
+      <c r="C2" s="60"/>
+      <c r="D2" s="60"/>
+      <c r="F2" s="60" t="s">
         <v>130</v>
       </c>
-      <c r="G2" s="54"/>
-      <c r="H2" s="54"/>
-      <c r="J2" s="54" t="s">
+      <c r="G2" s="60"/>
+      <c r="H2" s="60"/>
+      <c r="J2" s="60" t="s">
         <v>131</v>
       </c>
-      <c r="K2" s="54"/>
-      <c r="L2" s="54"/>
-      <c r="N2" s="54" t="s">
+      <c r="K2" s="60"/>
+      <c r="L2" s="60"/>
+      <c r="N2" s="60" t="s">
         <v>132</v>
       </c>
-      <c r="O2" s="54"/>
-      <c r="P2" s="54"/>
-      <c r="R2" s="54" t="s">
+      <c r="O2" s="60"/>
+      <c r="P2" s="60"/>
+      <c r="R2" s="60" t="s">
         <v>133</v>
       </c>
-      <c r="S2" s="54"/>
-      <c r="T2" s="54"/>
-      <c r="V2" s="54" t="s">
+      <c r="S2" s="60"/>
+      <c r="T2" s="60"/>
+      <c r="V2" s="60" t="s">
         <v>134</v>
       </c>
-      <c r="W2" s="54"/>
-      <c r="X2" s="54"/>
+      <c r="W2" s="60"/>
+      <c r="X2" s="60"/>
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
@@ -12404,34 +12419,34 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B2" s="55" t="s">
+      <c r="B2" s="61" t="s">
         <v>127</v>
       </c>
-      <c r="C2" s="55"/>
-      <c r="E2" s="51" t="s">
+      <c r="C2" s="61"/>
+      <c r="E2" s="57" t="s">
         <v>215</v>
       </c>
-      <c r="F2" s="51"/>
-      <c r="H2" s="51" t="s">
+      <c r="F2" s="57"/>
+      <c r="H2" s="57" t="s">
         <v>217</v>
       </c>
-      <c r="I2" s="51"/>
-      <c r="K2" s="51" t="s">
+      <c r="I2" s="57"/>
+      <c r="K2" s="57" t="s">
         <v>218</v>
       </c>
-      <c r="L2" s="51"/>
-      <c r="N2" s="51" t="s">
+      <c r="L2" s="57"/>
+      <c r="N2" s="57" t="s">
         <v>219</v>
       </c>
-      <c r="O2" s="51"/>
-      <c r="Q2" s="51" t="s">
+      <c r="O2" s="57"/>
+      <c r="Q2" s="57" t="s">
         <v>220</v>
       </c>
-      <c r="R2" s="51"/>
+      <c r="R2" s="57"/>
     </row>
     <row r="3" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B3" s="55"/>
-      <c r="C3" s="55"/>
+      <c r="B3" s="61"/>
+      <c r="C3" s="61"/>
       <c r="E3" s="32" t="inlineStr">
         <is>
           <t>head</t>
@@ -12856,34 +12871,34 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="62" t="s">
         <v>128</v>
       </c>
-      <c r="C2" s="56"/>
-      <c r="E2" s="52" t="s">
+      <c r="C2" s="62"/>
+      <c r="E2" s="58" t="s">
         <v>221</v>
       </c>
-      <c r="F2" s="52"/>
-      <c r="H2" s="52" t="s">
+      <c r="F2" s="58"/>
+      <c r="H2" s="58" t="s">
         <v>222</v>
       </c>
-      <c r="I2" s="52"/>
-      <c r="K2" s="52" t="s">
+      <c r="I2" s="58"/>
+      <c r="K2" s="58" t="s">
         <v>223</v>
       </c>
-      <c r="L2" s="52"/>
-      <c r="N2" s="52" t="s">
+      <c r="L2" s="58"/>
+      <c r="N2" s="58" t="s">
         <v>224</v>
       </c>
-      <c r="O2" s="52"/>
-      <c r="Q2" s="52" t="s">
+      <c r="O2" s="58"/>
+      <c r="Q2" s="58" t="s">
         <v>225</v>
       </c>
-      <c r="R2" s="52"/>
+      <c r="R2" s="58"/>
     </row>
     <row r="3" spans="2:21" x14ac:dyDescent="0.2">
-      <c r="B3" s="56"/>
-      <c r="C3" s="56"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
       <c r="E3" s="34" t="s">
         <v>213</v>
       </c>
@@ -13268,34 +13283,34 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60A900FC-A692-B445-95C9-59E70352B291}">
-  <dimension ref="A2:AL52"/>
+  <dimension ref="A2:AN52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" style="1" customWidth="1"/>
     <col min="3" max="10" width="8.5" style="1" customWidth="1"/>
-    <col min="11" max="38" width="8.5" customWidth="1"/>
+    <col min="11" max="40" width="8.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C2" s="6" t="s">
         <v>67</v>
       </c>
       <c r="E2"/>
       <c r="F2"/>
       <c r="G2"/>
-      <c r="L2" s="6" t="s">
+      <c r="N2" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="Q2" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="AB2" s="6"/>
-      <c r="AH2" s="6" t="s">
+      <c r="AD2" s="6"/>
+      <c r="AJ2" s="6" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="3" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C3" s="1" t="s">
         <v>66</v>
       </c>
@@ -13304,21 +13319,21 @@
       </c>
       <c r="F3"/>
       <c r="G3"/>
-      <c r="O3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="P3" t="s">
+      <c r="R3" t="s">
         <v>58</v>
       </c>
-      <c r="AB3" s="14"/>
-      <c r="AH3" s="1" t="s">
+      <c r="AD3" s="14"/>
+      <c r="AJ3" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="AI3" t="s">
+      <c r="AK3" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="4" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C4" s="1" t="s">
         <v>69</v>
       </c>
@@ -13327,240 +13342,248 @@
       </c>
       <c r="F4"/>
       <c r="G4"/>
-      <c r="L4" s="42"/>
-      <c r="M4" t="s">
+      <c r="N4" s="42"/>
+      <c r="O4" t="s">
         <v>161</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="Q4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="P4" t="s">
+      <c r="R4" t="s">
         <v>59</v>
       </c>
-      <c r="AB4" s="14"/>
-      <c r="AH4" s="1" t="s">
+      <c r="AD4" s="14"/>
+      <c r="AJ4" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="AI4" t="s">
+      <c r="AK4" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C5" s="1" t="s">
         <v>171</v>
       </c>
       <c r="D5" t="s">
         <v>191</v>
       </c>
-      <c r="L5" s="26"/>
-      <c r="M5" s="9" t="s">
+      <c r="N5" s="26"/>
+      <c r="O5" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="Q5" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="P5" s="9" t="s">
+      <c r="R5" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="AB5" s="14"/>
-      <c r="AH5" s="1" t="s">
+      <c r="AD5" s="14"/>
+      <c r="AJ5" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="AI5" s="9" t="s">
+      <c r="AK5" s="9" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C6" s="1" t="s">
         <v>201</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>207</v>
       </c>
-      <c r="L6" s="29"/>
-      <c r="M6" s="9" t="s">
+      <c r="N6" s="29"/>
+      <c r="O6" s="9" t="s">
         <v>163</v>
       </c>
-      <c r="O6" s="1" t="s">
+      <c r="Q6" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="P6" t="s">
+      <c r="R6" t="s">
         <v>190</v>
       </c>
-      <c r="AC6" s="1"/>
-      <c r="AD6" s="1"/>
-    </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AE6" s="1"/>
+      <c r="AF6" s="1"/>
+    </row>
+    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>233</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="AC7" s="1"/>
-      <c r="AD7" s="1"/>
-    </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
-      <c r="C9" s="45" t="s">
+      <c r="AE7" s="1"/>
+      <c r="AF7" s="1"/>
+    </row>
+    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="C9" s="51" t="s">
         <v>236</v>
       </c>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="45"/>
-      <c r="I9" s="45"/>
-      <c r="J9" s="45"/>
-      <c r="K9" s="45"/>
-      <c r="L9" s="45"/>
-      <c r="M9" s="45"/>
-      <c r="N9" s="45"/>
-      <c r="O9" s="45"/>
-      <c r="P9" s="45"/>
-      <c r="Q9" s="45"/>
-      <c r="R9" s="45"/>
-      <c r="S9" s="45"/>
-      <c r="T9" s="45"/>
-      <c r="U9" s="45"/>
-      <c r="V9" s="45"/>
-      <c r="W9" s="45"/>
-      <c r="X9" s="45"/>
-      <c r="Y9" s="45" t="s">
+      <c r="D9" s="51"/>
+      <c r="E9" s="51"/>
+      <c r="F9" s="51"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="51"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="51"/>
+      <c r="K9" s="51"/>
+      <c r="L9" s="51"/>
+      <c r="M9" s="51"/>
+      <c r="N9" s="51"/>
+      <c r="O9" s="51"/>
+      <c r="P9" s="51"/>
+      <c r="Q9" s="51"/>
+      <c r="R9" s="51"/>
+      <c r="S9" s="51"/>
+      <c r="T9" s="51"/>
+      <c r="U9" s="51"/>
+      <c r="V9" s="51"/>
+      <c r="W9" s="51"/>
+      <c r="X9" s="51"/>
+      <c r="Y9" s="51"/>
+      <c r="Z9" s="51"/>
+      <c r="AA9" s="51" t="s">
         <v>57</v>
       </c>
-      <c r="Z9" s="45"/>
-      <c r="AA9" s="45"/>
-      <c r="AB9" s="45"/>
-      <c r="AC9" s="45"/>
-      <c r="AD9" s="45"/>
-      <c r="AE9" s="45" t="s">
+      <c r="AB9" s="51"/>
+      <c r="AC9" s="51"/>
+      <c r="AD9" s="51"/>
+      <c r="AE9" s="51"/>
+      <c r="AF9" s="51"/>
+      <c r="AG9" s="51" t="s">
         <v>91</v>
       </c>
-      <c r="AF9" s="45"/>
-      <c r="AG9" s="45"/>
-      <c r="AH9" s="45"/>
-      <c r="AI9" s="45"/>
-      <c r="AJ9" s="45"/>
-      <c r="AK9" s="45"/>
-      <c r="AL9" s="45"/>
-    </row>
-    <row r="10" spans="1:38" ht="18" x14ac:dyDescent="0.25">
+      <c r="AH9" s="51"/>
+      <c r="AI9" s="51"/>
+      <c r="AJ9" s="51"/>
+      <c r="AK9" s="51"/>
+      <c r="AL9" s="51"/>
+      <c r="AM9" s="51"/>
+      <c r="AN9" s="51"/>
+    </row>
+    <row r="10" spans="1:40" ht="18" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
         <v>19</v>
       </c>
       <c r="B10" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="C10" s="58" t="s">
+      <c r="C10" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="62" t="s">
+      <c r="D10" s="48" t="s">
         <v>189</v>
       </c>
-      <c r="E10" s="57" t="s">
+      <c r="E10" s="44" t="s">
         <v>65</v>
       </c>
-      <c r="F10" s="57" t="s">
+      <c r="F10" s="44" t="s">
         <v>53</v>
       </c>
-      <c r="G10" s="58" t="s">
+      <c r="G10" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="H10" s="57" t="s">
+      <c r="H10" s="44" t="s">
         <v>72</v>
       </c>
-      <c r="I10" s="57" t="s">
+      <c r="I10" s="44" t="s">
         <v>71</v>
       </c>
-      <c r="J10" s="64" t="s">
+      <c r="J10" s="49" t="s">
         <v>79</v>
       </c>
-      <c r="K10" s="64" t="s">
+      <c r="K10" s="49" t="s">
         <v>135</v>
       </c>
-      <c r="L10" s="63" t="s">
+      <c r="L10" s="49" t="s">
+        <v>238</v>
+      </c>
+      <c r="M10" s="49" t="s">
+        <v>239</v>
+      </c>
+      <c r="N10" s="21" t="s">
         <v>235</v>
       </c>
-      <c r="M10" s="21" t="s">
+      <c r="O10" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="N10" s="43" t="s">
+      <c r="P10" s="43" t="s">
         <v>211</v>
       </c>
-      <c r="O10" s="57" t="s">
+      <c r="Q10" s="44" t="s">
         <v>84</v>
       </c>
-      <c r="P10" s="57" t="s">
+      <c r="R10" s="44" t="s">
         <v>172</v>
       </c>
-      <c r="Q10" s="57" t="s">
+      <c r="S10" s="44" t="s">
         <v>173</v>
       </c>
-      <c r="R10" s="57" t="s">
+      <c r="T10" s="44" t="s">
         <v>174</v>
       </c>
-      <c r="S10" s="57" t="s">
+      <c r="U10" s="44" t="s">
         <v>175</v>
       </c>
-      <c r="T10" s="57" t="s">
+      <c r="V10" s="44" t="s">
         <v>176</v>
       </c>
-      <c r="U10" s="57" t="s">
+      <c r="W10" s="44" t="s">
         <v>206</v>
       </c>
-      <c r="V10" s="57" t="s">
+      <c r="X10" s="44" t="s">
         <v>208</v>
       </c>
-      <c r="W10" s="57" t="s">
+      <c r="Y10" s="44" t="s">
         <v>209</v>
       </c>
-      <c r="X10" s="57" t="s">
+      <c r="Z10" s="44" t="s">
         <v>210</v>
       </c>
-      <c r="Y10" s="59" t="s">
+      <c r="AA10" s="46" t="s">
         <v>54</v>
       </c>
-      <c r="Z10" s="59" t="s">
+      <c r="AB10" s="46" t="s">
         <v>55</v>
       </c>
-      <c r="AA10" s="60" t="s">
+      <c r="AC10" s="47" t="s">
         <v>56</v>
       </c>
-      <c r="AB10" s="59" t="s">
+      <c r="AD10" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="AC10" s="59" t="s">
+      <c r="AE10" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="AD10" s="60" t="s">
+      <c r="AF10" s="47" t="s">
         <v>136</v>
       </c>
-      <c r="AE10" s="23" t="s">
+      <c r="AG10" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="AF10" s="23" t="s">
+      <c r="AH10" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="AG10" s="23" t="s">
+      <c r="AI10" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="AH10" s="23" t="s">
+      <c r="AJ10" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="AI10" s="23" t="s">
+      <c r="AK10" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="AJ10" s="23" t="s">
+      <c r="AL10" s="23" t="s">
         <v>95</v>
       </c>
-      <c r="AK10" s="23" t="s">
+      <c r="AM10" s="23" t="s">
         <v>205</v>
       </c>
-      <c r="AL10" s="23" t="s">
+      <c r="AN10" s="23" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>1</v>
       </c>
@@ -13593,23 +13616,19 @@
         <v>0.0</v>
       </c>
       <c r="L11" s="3"/>
-      <c r="M11" s="3">
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3">
         <v>0.0</v>
       </c>
-      <c r="N11" s="3">
+      <c r="P11" s="3">
         <v>0.0</v>
       </c>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="Q11" s="3" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="P11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Q11" s="3">
-        <v>0.0</v>
-      </c>
       <c r="R11" s="3">
         <v>0.0</v>
       </c>
@@ -13650,33 +13669,39 @@
         <v>0.0</v>
       </c>
       <c r="AE11" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AF11" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AG11" s="3">
         <v>0.5</v>
       </c>
-      <c r="AF11" s="3">
+      <c r="AH11" s="3">
         <v>0.2</v>
       </c>
-      <c r="AG11" s="3">
+      <c r="AI11" s="3">
         <v>0.0</v>
       </c>
-      <c r="AH11" s="3" t="inlineStr">
+      <c r="AJ11" s="3" t="inlineStr">
         <is>
           <t>lf</t>
         </is>
       </c>
-      <c r="AI11" s="3">
+      <c r="AK11" s="3">
         <v>0.001</v>
       </c>
-      <c r="AJ11" s="3">
+      <c r="AL11" s="3">
         <v>-1.0</v>
       </c>
-      <c r="AK11" s="3">
+      <c r="AM11" s="3">
         <v>0.0</v>
       </c>
-      <c r="AL11" s="3">
+      <c r="AN11" s="3">
         <v>0.0</v>
       </c>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>2</v>
       </c>
@@ -13709,23 +13734,19 @@
         <v>0.0</v>
       </c>
       <c r="L12" s="3"/>
-      <c r="M12" s="3">
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3">
         <v>0.0</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>0.0</v>
       </c>
-      <c r="O12" s="3" t="inlineStr">
+      <c r="Q12" s="3" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="P12" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Q12" s="3">
-        <v>0.0</v>
-      </c>
       <c r="R12" s="3">
         <v>0.0</v>
       </c>
@@ -13766,33 +13787,39 @@
         <v>0.0</v>
       </c>
       <c r="AE12" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AF12" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AG12" s="3">
         <v>0.2</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AH12" s="3">
         <v>0.2</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AI12" s="3">
         <v>0.0</v>
       </c>
-      <c r="AH12" s="3" t="inlineStr">
+      <c r="AJ12" s="3" t="inlineStr">
         <is>
           <t>lf</t>
         </is>
       </c>
-      <c r="AI12" s="3">
+      <c r="AK12" s="3">
         <v>0.001</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AL12" s="3">
         <v>-1.0</v>
       </c>
-      <c r="AK12" s="18">
+      <c r="AM12" s="18">
         <v>0.0</v>
       </c>
-      <c r="AL12" s="19">
+      <c r="AN12" s="19">
         <v>0.0</v>
       </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>3</v>
       </c>
@@ -13825,23 +13852,19 @@
         <v>0.0</v>
       </c>
       <c r="L13" s="3"/>
-      <c r="M13" s="3">
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3">
         <v>0.0</v>
       </c>
-      <c r="N13" s="3">
+      <c r="P13" s="3">
         <v>0.0</v>
       </c>
-      <c r="O13" s="3" t="inlineStr">
+      <c r="Q13" s="3" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="P13" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Q13" s="3">
-        <v>0.0</v>
-      </c>
       <c r="R13" s="3">
         <v>0.0</v>
       </c>
@@ -13882,33 +13905,39 @@
         <v>0.0</v>
       </c>
       <c r="AE13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AF13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="AG13" s="3">
         <v>2.0</v>
       </c>
-      <c r="AF13" s="3">
+      <c r="AH13" s="3">
         <v>1.0</v>
       </c>
-      <c r="AG13" s="3">
+      <c r="AI13" s="3">
         <v>0.0</v>
       </c>
-      <c r="AH13" s="3" t="inlineStr">
+      <c r="AJ13" s="3" t="inlineStr">
         <is>
           <t>lf</t>
         </is>
       </c>
-      <c r="AI13" s="3">
+      <c r="AK13" s="3">
         <v>0.001</v>
       </c>
-      <c r="AJ13" s="3">
+      <c r="AL13" s="3">
         <v>-1.0</v>
       </c>
-      <c r="AK13" s="18">
+      <c r="AM13" s="18">
         <v>0.0</v>
       </c>
-      <c r="AL13" s="19">
+      <c r="AN13" s="19">
         <v>0.0</v>
       </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>4</v>
       </c>
@@ -13949,8 +13978,10 @@
       <c r="AJ14" s="3"/>
       <c r="AK14" s="3"/>
       <c r="AL14" s="3"/>
-    </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AM14" s="3"/>
+      <c r="AN14" s="3"/>
+    </row>
+    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>5</v>
       </c>
@@ -13991,8 +14022,10 @@
       <c r="AJ15" s="3"/>
       <c r="AK15" s="3"/>
       <c r="AL15" s="3"/>
-    </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AM15" s="3"/>
+      <c r="AN15" s="3"/>
+    </row>
+    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>6</v>
       </c>
@@ -14033,8 +14066,10 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
-    </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AM16" s="3"/>
+      <c r="AN16" s="3"/>
+    </row>
+    <row r="17" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>7</v>
       </c>
@@ -14075,8 +14110,10 @@
       <c r="AJ17" s="3"/>
       <c r="AK17" s="3"/>
       <c r="AL17" s="3"/>
-    </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AM17" s="3"/>
+      <c r="AN17" s="3"/>
+    </row>
+    <row r="18" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>8</v>
       </c>
@@ -14117,8 +14154,10 @@
       <c r="AJ18" s="3"/>
       <c r="AK18" s="3"/>
       <c r="AL18" s="3"/>
-    </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AM18" s="3"/>
+      <c r="AN18" s="3"/>
+    </row>
+    <row r="19" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>9</v>
       </c>
@@ -14159,8 +14198,10 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
-    </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
+    </row>
+    <row r="20" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>10</v>
       </c>
@@ -14201,8 +14242,10 @@
       <c r="AJ20" s="3"/>
       <c r="AK20" s="3"/>
       <c r="AL20" s="3"/>
-    </row>
-    <row r="21" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AM20" s="3"/>
+      <c r="AN20" s="3"/>
+    </row>
+    <row r="21" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>11</v>
       </c>
@@ -14243,8 +14286,10 @@
       <c r="AJ21" s="3"/>
       <c r="AK21" s="3"/>
       <c r="AL21" s="3"/>
-    </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AM21" s="3"/>
+      <c r="AN21" s="3"/>
+    </row>
+    <row r="22" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>12</v>
       </c>
@@ -14285,8 +14330,10 @@
       <c r="AJ22" s="3"/>
       <c r="AK22" s="3"/>
       <c r="AL22" s="3"/>
-    </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AM22" s="3"/>
+      <c r="AN22" s="3"/>
+    </row>
+    <row r="23" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>13</v>
       </c>
@@ -14327,8 +14374,10 @@
       <c r="AJ23" s="3"/>
       <c r="AK23" s="3"/>
       <c r="AL23" s="3"/>
-    </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AM23" s="3"/>
+      <c r="AN23" s="3"/>
+    </row>
+    <row r="24" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>14</v>
       </c>
@@ -14369,8 +14418,10 @@
       <c r="AJ24" s="3"/>
       <c r="AK24" s="3"/>
       <c r="AL24" s="3"/>
-    </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AM24" s="3"/>
+      <c r="AN24" s="3"/>
+    </row>
+    <row r="25" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>15</v>
       </c>
@@ -14411,8 +14462,10 @@
       <c r="AJ25" s="3"/>
       <c r="AK25" s="3"/>
       <c r="AL25" s="3"/>
-    </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AM25" s="3"/>
+      <c r="AN25" s="3"/>
+    </row>
+    <row r="26" spans="1:40" x14ac:dyDescent="0.2">
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -14441,8 +14494,10 @@
       <c r="AJ26" s="1"/>
       <c r="AK26" s="1"/>
       <c r="AL26" s="1"/>
-    </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AM26" s="1"/>
+      <c r="AN26" s="1"/>
+    </row>
+    <row r="27" spans="1:40" x14ac:dyDescent="0.2">
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -14463,8 +14518,10 @@
       <c r="AB27" s="1"/>
       <c r="AC27" s="1"/>
       <c r="AD27" s="1"/>
-    </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AE27" s="1"/>
+      <c r="AF27" s="1"/>
+    </row>
+    <row r="28" spans="1:40" x14ac:dyDescent="0.2">
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -14485,8 +14542,10 @@
       <c r="AB28" s="1"/>
       <c r="AC28" s="1"/>
       <c r="AD28" s="1"/>
-    </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AE28" s="1"/>
+      <c r="AF28" s="1"/>
+    </row>
+    <row r="29" spans="1:40" x14ac:dyDescent="0.2">
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -14507,8 +14566,10 @@
       <c r="AB29" s="1"/>
       <c r="AC29" s="1"/>
       <c r="AD29" s="1"/>
-    </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AE29" s="1"/>
+      <c r="AF29" s="1"/>
+    </row>
+    <row r="30" spans="1:40" x14ac:dyDescent="0.2">
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -14529,8 +14590,10 @@
       <c r="AB30" s="1"/>
       <c r="AC30" s="1"/>
       <c r="AD30" s="1"/>
-    </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AE30" s="1"/>
+      <c r="AF30" s="1"/>
+    </row>
+    <row r="31" spans="1:40" x14ac:dyDescent="0.2">
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -14551,8 +14614,10 @@
       <c r="AB31" s="1"/>
       <c r="AC31" s="1"/>
       <c r="AD31" s="1"/>
-    </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.2">
+      <c r="AE31" s="1"/>
+      <c r="AF31" s="1"/>
+    </row>
+    <row r="32" spans="1:40" x14ac:dyDescent="0.2">
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -14573,8 +14638,10 @@
       <c r="AB32" s="1"/>
       <c r="AC32" s="1"/>
       <c r="AD32" s="1"/>
-    </row>
-    <row r="33" spans="11:30" x14ac:dyDescent="0.2">
+      <c r="AE32" s="1"/>
+      <c r="AF32" s="1"/>
+    </row>
+    <row r="33" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -14595,8 +14662,10 @@
       <c r="AB33" s="1"/>
       <c r="AC33" s="1"/>
       <c r="AD33" s="1"/>
-    </row>
-    <row r="34" spans="11:30" x14ac:dyDescent="0.2">
+      <c r="AE33" s="1"/>
+      <c r="AF33" s="1"/>
+    </row>
+    <row r="34" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
@@ -14617,8 +14686,10 @@
       <c r="AB34" s="1"/>
       <c r="AC34" s="1"/>
       <c r="AD34" s="1"/>
-    </row>
-    <row r="35" spans="11:30" x14ac:dyDescent="0.2">
+      <c r="AE34" s="1"/>
+      <c r="AF34" s="1"/>
+    </row>
+    <row r="35" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -14639,8 +14710,10 @@
       <c r="AB35" s="1"/>
       <c r="AC35" s="1"/>
       <c r="AD35" s="1"/>
-    </row>
-    <row r="36" spans="11:30" x14ac:dyDescent="0.2">
+      <c r="AE35" s="1"/>
+      <c r="AF35" s="1"/>
+    </row>
+    <row r="36" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
@@ -14661,8 +14734,10 @@
       <c r="AB36" s="1"/>
       <c r="AC36" s="1"/>
       <c r="AD36" s="1"/>
-    </row>
-    <row r="37" spans="11:30" x14ac:dyDescent="0.2">
+      <c r="AE36" s="1"/>
+      <c r="AF36" s="1"/>
+    </row>
+    <row r="37" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
@@ -14683,8 +14758,10 @@
       <c r="AB37" s="1"/>
       <c r="AC37" s="1"/>
       <c r="AD37" s="1"/>
-    </row>
-    <row r="38" spans="11:30" x14ac:dyDescent="0.2">
+      <c r="AE37" s="1"/>
+      <c r="AF37" s="1"/>
+    </row>
+    <row r="38" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -14705,8 +14782,10 @@
       <c r="AB38" s="1"/>
       <c r="AC38" s="1"/>
       <c r="AD38" s="1"/>
-    </row>
-    <row r="39" spans="11:30" x14ac:dyDescent="0.2">
+      <c r="AE38" s="1"/>
+      <c r="AF38" s="1"/>
+    </row>
+    <row r="39" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -14727,8 +14806,10 @@
       <c r="AB39" s="1"/>
       <c r="AC39" s="1"/>
       <c r="AD39" s="1"/>
-    </row>
-    <row r="40" spans="11:30" x14ac:dyDescent="0.2">
+      <c r="AE39" s="1"/>
+      <c r="AF39" s="1"/>
+    </row>
+    <row r="40" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -14749,8 +14830,10 @@
       <c r="AB40" s="1"/>
       <c r="AC40" s="1"/>
       <c r="AD40" s="1"/>
-    </row>
-    <row r="41" spans="11:30" x14ac:dyDescent="0.2">
+      <c r="AE40" s="1"/>
+      <c r="AF40" s="1"/>
+    </row>
+    <row r="41" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
@@ -14771,8 +14854,10 @@
       <c r="AB41" s="1"/>
       <c r="AC41" s="1"/>
       <c r="AD41" s="1"/>
-    </row>
-    <row r="42" spans="11:30" x14ac:dyDescent="0.2">
+      <c r="AE41" s="1"/>
+      <c r="AF41" s="1"/>
+    </row>
+    <row r="42" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
@@ -14793,8 +14878,10 @@
       <c r="AB42" s="1"/>
       <c r="AC42" s="1"/>
       <c r="AD42" s="1"/>
-    </row>
-    <row r="43" spans="11:30" x14ac:dyDescent="0.2">
+      <c r="AE42" s="1"/>
+      <c r="AF42" s="1"/>
+    </row>
+    <row r="43" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
@@ -14815,8 +14902,10 @@
       <c r="AB43" s="1"/>
       <c r="AC43" s="1"/>
       <c r="AD43" s="1"/>
-    </row>
-    <row r="44" spans="11:30" x14ac:dyDescent="0.2">
+      <c r="AE43" s="1"/>
+      <c r="AF43" s="1"/>
+    </row>
+    <row r="44" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
@@ -14837,8 +14926,10 @@
       <c r="AB44" s="1"/>
       <c r="AC44" s="1"/>
       <c r="AD44" s="1"/>
-    </row>
-    <row r="45" spans="11:30" x14ac:dyDescent="0.2">
+      <c r="AE44" s="1"/>
+      <c r="AF44" s="1"/>
+    </row>
+    <row r="45" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
@@ -14859,8 +14950,10 @@
       <c r="AB45" s="1"/>
       <c r="AC45" s="1"/>
       <c r="AD45" s="1"/>
-    </row>
-    <row r="46" spans="11:30" x14ac:dyDescent="0.2">
+      <c r="AE45" s="1"/>
+      <c r="AF45" s="1"/>
+    </row>
+    <row r="46" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
@@ -14881,8 +14974,10 @@
       <c r="AB46" s="1"/>
       <c r="AC46" s="1"/>
       <c r="AD46" s="1"/>
-    </row>
-    <row r="47" spans="11:30" x14ac:dyDescent="0.2">
+      <c r="AE46" s="1"/>
+      <c r="AF46" s="1"/>
+    </row>
+    <row r="47" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
@@ -14903,8 +14998,10 @@
       <c r="AB47" s="1"/>
       <c r="AC47" s="1"/>
       <c r="AD47" s="1"/>
-    </row>
-    <row r="48" spans="11:30" x14ac:dyDescent="0.2">
+      <c r="AE47" s="1"/>
+      <c r="AF47" s="1"/>
+    </row>
+    <row r="48" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
       <c r="M48" s="1"/>
@@ -14925,8 +15022,10 @@
       <c r="AB48" s="1"/>
       <c r="AC48" s="1"/>
       <c r="AD48" s="1"/>
-    </row>
-    <row r="49" spans="11:30" x14ac:dyDescent="0.2">
+      <c r="AE48" s="1"/>
+      <c r="AF48" s="1"/>
+    </row>
+    <row r="49" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
       <c r="M49" s="1"/>
@@ -14947,8 +15046,10 @@
       <c r="AB49" s="1"/>
       <c r="AC49" s="1"/>
       <c r="AD49" s="1"/>
-    </row>
-    <row r="50" spans="11:30" x14ac:dyDescent="0.2">
+      <c r="AE49" s="1"/>
+      <c r="AF49" s="1"/>
+    </row>
+    <row r="50" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
       <c r="M50" s="1"/>
@@ -14969,8 +15070,10 @@
       <c r="AB50" s="1"/>
       <c r="AC50" s="1"/>
       <c r="AD50" s="1"/>
-    </row>
-    <row r="51" spans="11:30" x14ac:dyDescent="0.2">
+      <c r="AE50" s="1"/>
+      <c r="AF50" s="1"/>
+    </row>
+    <row r="51" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
       <c r="M51" s="1"/>
@@ -14991,8 +15094,10 @@
       <c r="AB51" s="1"/>
       <c r="AC51" s="1"/>
       <c r="AD51" s="1"/>
-    </row>
-    <row r="52" spans="11:30" x14ac:dyDescent="0.2">
+      <c r="AE51" s="1"/>
+      <c r="AF51" s="1"/>
+    </row>
+    <row r="52" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="1"/>
@@ -15013,100 +15118,107 @@
       <c r="AB52" s="1"/>
       <c r="AC52" s="1"/>
       <c r="AD52" s="1"/>
+      <c r="AE52" s="1"/>
+      <c r="AF52" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="Y9:AD9"/>
-    <mergeCell ref="AE9:AL9"/>
-    <mergeCell ref="C9:X9"/>
+    <mergeCell ref="AA9:AF9"/>
+    <mergeCell ref="AG9:AN9"/>
+    <mergeCell ref="C9:Z9"/>
   </mergeCells>
-  <conditionalFormatting sqref="F11:K52 Z11:AD52">
-    <cfRule type="expression" dxfId="5" priority="1">
+  <conditionalFormatting sqref="L11:M52">
+    <cfRule type="expression" dxfId="5" priority="17">
+      <formula>AND($Q11&lt;&gt;"",$Q11&lt;&gt;"piezo",$Q11&lt;&gt;"seep")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F11:K52 AB11:AF52">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>$E11="hb"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="5" priority="2">
+    <cfRule type="expression" dxfId="17" priority="2">
       <formula>$E11="pow"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F11:N52">
+    <cfRule type="expression" dxfId="16" priority="14">
+      <formula>$E11="elastic"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="G11:G52">
-    <cfRule type="expression" dxfId="5" priority="3">
+    <cfRule type="expression" dxfId="15" priority="3">
       <formula>$E11="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11:I52">
-    <cfRule type="expression" dxfId="5" priority="4">
+    <cfRule type="expression" dxfId="14" priority="4">
       <formula>$E11="mc"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J11:K52">
-    <cfRule type="expression" dxfId="5" priority="5">
+  <conditionalFormatting sqref="J11:M52">
+    <cfRule type="expression" dxfId="13" priority="5">
       <formula>$E11="cp"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q11:T52">
-    <cfRule type="expression" dxfId="5" priority="6">
+  <conditionalFormatting sqref="Q11:R52">
+    <cfRule type="expression" dxfId="12" priority="15">
+      <formula>$E11="elastic"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R11:R52">
+    <cfRule type="expression" dxfId="11" priority="8">
+      <formula>AND($Q11&lt;&gt;"",$Q11&lt;&gt;"ru")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S11:V52">
+    <cfRule type="expression" dxfId="10" priority="6">
       <formula>AND($E11&lt;&gt;"",$E11&lt;&gt;"pow")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U11:X52">
-    <cfRule type="expression" dxfId="5" priority="7">
+  <conditionalFormatting sqref="W11:Z52">
+    <cfRule type="expression" dxfId="9" priority="7">
       <formula>AND($E11&lt;&gt;"",$E11&lt;&gt;"hb")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P11:P52">
-    <cfRule type="expression" dxfId="5" priority="8">
-      <formula>AND($O11&lt;&gt;"",$O11&lt;&gt;"ru")</formula>
+  <conditionalFormatting sqref="AB11:AF52">
+    <cfRule type="expression" dxfId="8" priority="16">
+      <formula>$E11="elastic"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA11:AA52">
-    <cfRule type="expression" dxfId="5" priority="9">
+  <conditionalFormatting sqref="AC11:AC52">
+    <cfRule type="expression" dxfId="7" priority="9">
       <formula>$E11="cp"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AB11:AB52">
-    <cfRule type="expression" dxfId="5" priority="10">
+  <conditionalFormatting sqref="AD11:AD52">
+    <cfRule type="expression" dxfId="6" priority="10">
       <formula>$E11="mc"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC11:AD52">
+  <conditionalFormatting sqref="AE11:AF52">
     <cfRule type="expression" dxfId="5" priority="11">
       <formula>$E11="cp"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AI11:AJ52">
-    <cfRule type="expression" dxfId="5" priority="12">
-      <formula>OR($AH11="vg",$AH11="gard")</formula>
+  <conditionalFormatting sqref="AK11:AL52">
+    <cfRule type="expression" dxfId="4" priority="12">
+      <formula>OR($AJ11="vg",$AJ11="gard")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AK11:AL52">
-    <cfRule type="expression" dxfId="5" priority="13">
-      <formula>$AH11="lf"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F11:L52">
-    <cfRule type="expression" dxfId="5" priority="14">
-      <formula>$E11="elastic"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O11:P52">
-    <cfRule type="expression" dxfId="5" priority="15">
-      <formula>$E11="elastic"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z11:AD52">
-    <cfRule type="expression" dxfId="5" priority="16">
-      <formula>$E11="elastic"</formula>
+  <conditionalFormatting sqref="AM11:AN52">
+    <cfRule type="expression" dxfId="3" priority="13">
+      <formula>$AJ11="lf"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E11:E52" xr:uid="{374AFD2C-B540-DD4B-A245-8B781F76E64C}">
       <formula1>$C$3:$C$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AH11:AH102" xr:uid="{E00A94A9-D864-5843-8FBD-E84775B1C100}">
-      <formula1>$AH$3:$AH$5</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AJ11:AJ102" xr:uid="{E00A94A9-D864-5843-8FBD-E84775B1C100}">
+      <formula1>$AJ$3:$AJ$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O11:O52" xr:uid="{D770415C-1ECE-F44B-9D8C-08EF1CF31C8E}">
-      <formula1>$O$3:$O$6</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q11:Q52" xr:uid="{D770415C-1ECE-F44B-9D8C-08EF1CF31C8E}">
+      <formula1>$Q$3:$Q$6</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -15151,74 +15263,74 @@
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A4" s="48" t="s">
+      <c r="A4" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="48"/>
-      <c r="D4" s="48" t="s">
+      <c r="B4" s="52"/>
+      <c r="D4" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="48"/>
-      <c r="G4" s="48" t="s">
+      <c r="E4" s="52"/>
+      <c r="G4" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="48"/>
-      <c r="J4" s="48" t="s">
+      <c r="H4" s="52"/>
+      <c r="J4" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="48"/>
-      <c r="M4" s="48" t="s">
+      <c r="K4" s="52"/>
+      <c r="M4" s="52" t="s">
         <v>8</v>
       </c>
-      <c r="N4" s="48"/>
-      <c r="P4" s="48" t="s">
+      <c r="N4" s="52"/>
+      <c r="P4" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="Q4" s="48"/>
+      <c r="Q4" s="52"/>
       <c r="R4" s="1"/>
-      <c r="S4" s="48" t="s">
+      <c r="S4" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="T4" s="48"/>
+      <c r="T4" s="52"/>
       <c r="U4" s="1"/>
-      <c r="V4" s="48" t="s">
+      <c r="V4" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="W4" s="48"/>
+      <c r="W4" s="52"/>
       <c r="X4" s="1"/>
-      <c r="Y4" s="48" t="s">
+      <c r="Y4" s="52" t="s">
         <v>12</v>
       </c>
-      <c r="Z4" s="48"/>
+      <c r="Z4" s="52"/>
       <c r="AA4" s="1"/>
-      <c r="AB4" s="48" t="s">
+      <c r="AB4" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="AC4" s="48"/>
-      <c r="AE4" s="48" t="s">
+      <c r="AC4" s="52"/>
+      <c r="AE4" s="52" t="s">
         <v>108</v>
       </c>
-      <c r="AF4" s="48"/>
+      <c r="AF4" s="52"/>
       <c r="AG4" s="1"/>
-      <c r="AH4" s="48" t="s">
+      <c r="AH4" s="52" t="s">
         <v>109</v>
       </c>
-      <c r="AI4" s="48"/>
+      <c r="AI4" s="52"/>
       <c r="AJ4" s="1"/>
-      <c r="AK4" s="48" t="s">
+      <c r="AK4" s="52" t="s">
         <v>110</v>
       </c>
-      <c r="AL4" s="48"/>
+      <c r="AL4" s="52"/>
       <c r="AM4" s="1"/>
-      <c r="AN4" s="48" t="s">
+      <c r="AN4" s="52" t="s">
         <v>111</v>
       </c>
-      <c r="AO4" s="48"/>
+      <c r="AO4" s="52"/>
       <c r="AP4" s="1"/>
-      <c r="AQ4" s="48" t="s">
+      <c r="AQ4" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="AR4" s="48"/>
+      <c r="AR4" s="52"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="36" t="s">
@@ -15321,89 +15433,89 @@
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A6" s="46" t="str">
+      <c r="A6" s="53" t="str">
         <f>_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="B6" s="47"/>
-      <c r="D6" s="46" t="str">
+      <c r="B6" s="54"/>
+      <c r="D6" s="53" t="str">
         <f>_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="E6" s="47"/>
-      <c r="G6" s="46" t="str">
+      <c r="E6" s="54"/>
+      <c r="G6" s="53" t="str">
         <f>_xlfn.XLOOKUP(H5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="H6" s="47"/>
-      <c r="J6" s="46" t="str">
+      <c r="H6" s="54"/>
+      <c r="J6" s="53" t="str">
         <f>_xlfn.XLOOKUP(K5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="K6" s="47"/>
-      <c r="M6" s="46" t="str">
+      <c r="K6" s="54"/>
+      <c r="M6" s="53" t="str">
         <f>_xlfn.XLOOKUP(N5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="N6" s="47"/>
-      <c r="P6" s="46" t="str">
+      <c r="N6" s="54"/>
+      <c r="P6" s="53" t="str">
         <f>_xlfn.XLOOKUP(Q5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Q6" s="47"/>
+      <c r="Q6" s="54"/>
       <c r="R6" s="1"/>
-      <c r="S6" s="46" t="str">
+      <c r="S6" s="53" t="str">
         <f>_xlfn.XLOOKUP(T5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="T6" s="47"/>
+      <c r="T6" s="54"/>
       <c r="U6" s="1"/>
-      <c r="V6" s="46" t="str">
+      <c r="V6" s="53" t="str">
         <f>_xlfn.XLOOKUP(W5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="W6" s="47"/>
+      <c r="W6" s="54"/>
       <c r="X6" s="1"/>
-      <c r="Y6" s="46" t="str">
+      <c r="Y6" s="53" t="str">
         <f>_xlfn.XLOOKUP(Z5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Z6" s="47"/>
+      <c r="Z6" s="54"/>
       <c r="AA6" s="1"/>
-      <c r="AB6" s="46" t="str">
+      <c r="AB6" s="53" t="str">
         <f>_xlfn.XLOOKUP(AC5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AC6" s="47"/>
-      <c r="AE6" s="46" t="str">
+      <c r="AC6" s="54"/>
+      <c r="AE6" s="53" t="str">
         <f>_xlfn.XLOOKUP(AF5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AF6" s="47"/>
+      <c r="AF6" s="54"/>
       <c r="AG6" s="1"/>
-      <c r="AH6" s="46" t="str">
+      <c r="AH6" s="53" t="str">
         <f>_xlfn.XLOOKUP(AI5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AI6" s="47"/>
+      <c r="AI6" s="54"/>
       <c r="AJ6" s="1"/>
-      <c r="AK6" s="46" t="str">
+      <c r="AK6" s="53" t="str">
         <f>_xlfn.XLOOKUP(AL5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AL6" s="47"/>
+      <c r="AL6" s="54"/>
       <c r="AM6" s="1"/>
-      <c r="AN6" s="46" t="str">
+      <c r="AN6" s="53" t="str">
         <f>_xlfn.XLOOKUP(AO5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AO6" s="47"/>
+      <c r="AO6" s="54"/>
       <c r="AP6" s="1"/>
-      <c r="AQ6" s="46" t="str">
+      <c r="AQ6" s="53" t="str">
         <f>_xlfn.XLOOKUP(AR5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AR6" s="47"/>
+      <c r="AR6" s="54"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -16307,36 +16419,36 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="AE6:AF6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AK6:AL6"/>
+    <mergeCell ref="AN6:AO6"/>
+    <mergeCell ref="AQ6:AR6"/>
+    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="J6:K6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AQ4:AR4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="S4:T4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AB4:AC4"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="J4:K4"/>
     <mergeCell ref="M4:N4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AK4:AL4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AQ4:AR4"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AE6:AF6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AK6:AL6"/>
-    <mergeCell ref="AN6:AO6"/>
-    <mergeCell ref="AQ6:AR6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16374,82 +16486,82 @@
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A4" s="48" t="inlineStr">
+      <c r="A4" s="52" t="inlineStr">
         <is>
           <t>Polygon #1</t>
         </is>
       </c>
-      <c r="B4" s="48"/>
-      <c r="D4" s="48" t="inlineStr">
+      <c r="B4" s="52"/>
+      <c r="D4" s="52" t="inlineStr">
         <is>
           <t>Polygon #2</t>
         </is>
       </c>
-      <c r="E4" s="48"/>
-      <c r="G4" s="48" t="inlineStr">
+      <c r="E4" s="52"/>
+      <c r="G4" s="52" t="inlineStr">
         <is>
           <t>Polygon #3</t>
         </is>
       </c>
-      <c r="H4" s="48"/>
-      <c r="J4" s="48" t="inlineStr">
+      <c r="H4" s="52"/>
+      <c r="J4" s="52" t="inlineStr">
         <is>
           <t>Polygon #4</t>
         </is>
       </c>
-      <c r="K4" s="48"/>
-      <c r="M4" s="48" t="s">
+      <c r="K4" s="52"/>
+      <c r="M4" s="52" t="s">
         <v>141</v>
       </c>
-      <c r="N4" s="48"/>
-      <c r="P4" s="48" t="s">
+      <c r="N4" s="52"/>
+      <c r="P4" s="52" t="s">
         <v>142</v>
       </c>
-      <c r="Q4" s="48"/>
+      <c r="Q4" s="52"/>
       <c r="R4" s="1"/>
-      <c r="S4" s="48" t="s">
+      <c r="S4" s="52" t="s">
         <v>143</v>
       </c>
-      <c r="T4" s="48"/>
+      <c r="T4" s="52"/>
       <c r="U4" s="1"/>
-      <c r="V4" s="48" t="s">
+      <c r="V4" s="52" t="s">
         <v>144</v>
       </c>
-      <c r="W4" s="48"/>
+      <c r="W4" s="52"/>
       <c r="X4" s="1"/>
-      <c r="Y4" s="48" t="s">
+      <c r="Y4" s="52" t="s">
         <v>145</v>
       </c>
-      <c r="Z4" s="48"/>
+      <c r="Z4" s="52"/>
       <c r="AA4" s="1"/>
-      <c r="AB4" s="48" t="s">
+      <c r="AB4" s="52" t="s">
         <v>146</v>
       </c>
-      <c r="AC4" s="48"/>
-      <c r="AE4" s="48" t="s">
+      <c r="AC4" s="52"/>
+      <c r="AE4" s="52" t="s">
         <v>147</v>
       </c>
-      <c r="AF4" s="48"/>
+      <c r="AF4" s="52"/>
       <c r="AG4" s="1"/>
-      <c r="AH4" s="48" t="s">
+      <c r="AH4" s="52" t="s">
         <v>148</v>
       </c>
-      <c r="AI4" s="48"/>
+      <c r="AI4" s="52"/>
       <c r="AJ4" s="1"/>
-      <c r="AK4" s="48" t="s">
+      <c r="AK4" s="52" t="s">
         <v>149</v>
       </c>
-      <c r="AL4" s="48"/>
+      <c r="AL4" s="52"/>
       <c r="AM4" s="1"/>
-      <c r="AN4" s="48" t="s">
+      <c r="AN4" s="52" t="s">
         <v>150</v>
       </c>
-      <c r="AO4" s="48"/>
+      <c r="AO4" s="52"/>
       <c r="AP4" s="1"/>
-      <c r="AQ4" s="48" t="s">
+      <c r="AQ4" s="52" t="s">
         <v>151</v>
       </c>
-      <c r="AR4" s="48"/>
+      <c r="AR4" s="52"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="38" t="s">
@@ -16552,93 +16664,93 @@
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A6" s="49" t="inlineStr">
+      <c r="A6" s="55" t="inlineStr">
         <is>
           <t>levee</t>
         </is>
       </c>
-      <c r="B6" s="50"/>
-      <c r="D6" s="49" t="inlineStr">
+      <c r="B6" s="56"/>
+      <c r="D6" s="55" t="inlineStr">
         <is>
           <t>foundation</t>
         </is>
       </c>
-      <c r="E6" s="50"/>
-      <c r="G6" s="49" t="inlineStr">
+      <c r="E6" s="56"/>
+      <c r="G6" s="55" t="inlineStr">
         <is>
           <t>grout</t>
         </is>
       </c>
-      <c r="H6" s="50"/>
-      <c r="J6" s="49" t="inlineStr">
+      <c r="H6" s="56"/>
+      <c r="J6" s="55" t="inlineStr">
         <is>
           <t>foundation</t>
         </is>
       </c>
-      <c r="K6" s="50"/>
-      <c r="M6" s="49" t="str">
+      <c r="K6" s="56"/>
+      <c r="M6" s="55" t="str">
         <f>_xlfn.XLOOKUP(N5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="N6" s="50"/>
-      <c r="P6" s="49" t="str">
+      <c r="N6" s="56"/>
+      <c r="P6" s="55" t="str">
         <f>_xlfn.XLOOKUP(Q5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Q6" s="50"/>
+      <c r="Q6" s="56"/>
       <c r="R6" s="1"/>
-      <c r="S6" s="49" t="str">
+      <c r="S6" s="55" t="str">
         <f>_xlfn.XLOOKUP(T5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="T6" s="50"/>
+      <c r="T6" s="56"/>
       <c r="U6" s="1"/>
-      <c r="V6" s="49" t="str">
+      <c r="V6" s="55" t="str">
         <f>_xlfn.XLOOKUP(W5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="W6" s="50"/>
+      <c r="W6" s="56"/>
       <c r="X6" s="1"/>
-      <c r="Y6" s="49" t="str">
+      <c r="Y6" s="55" t="str">
         <f>_xlfn.XLOOKUP(Z5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="Z6" s="50"/>
+      <c r="Z6" s="56"/>
       <c r="AA6" s="1"/>
-      <c r="AB6" s="49" t="str">
+      <c r="AB6" s="55" t="str">
         <f>_xlfn.XLOOKUP(AC5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AC6" s="50"/>
-      <c r="AE6" s="49" t="str">
+      <c r="AC6" s="56"/>
+      <c r="AE6" s="55" t="str">
         <f>_xlfn.XLOOKUP(AF5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AF6" s="50"/>
+      <c r="AF6" s="56"/>
       <c r="AG6" s="1"/>
-      <c r="AH6" s="49" t="str">
+      <c r="AH6" s="55" t="str">
         <f>_xlfn.XLOOKUP(AI5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AI6" s="50"/>
+      <c r="AI6" s="56"/>
       <c r="AJ6" s="1"/>
-      <c r="AK6" s="49" t="str">
+      <c r="AK6" s="55" t="str">
         <f>_xlfn.XLOOKUP(AL5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AL6" s="50"/>
+      <c r="AL6" s="56"/>
       <c r="AM6" s="1"/>
-      <c r="AN6" s="49" t="str">
+      <c r="AN6" s="55" t="str">
         <f>_xlfn.XLOOKUP(AO5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AO6" s="50"/>
+      <c r="AO6" s="56"/>
       <c r="AP6" s="1"/>
-      <c r="AQ6" s="49" t="str">
+      <c r="AQ6" s="55" t="str">
         <f>_xlfn.XLOOKUP(AR5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
         <v/>
       </c>
-      <c r="AR6" s="50"/>
+      <c r="AR6" s="56"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
@@ -17626,12 +17738,14 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="AN6:AO6"/>
+    <mergeCell ref="AQ6:AR6"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="AE6:AF6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="AK6:AL6"/>
     <mergeCell ref="AK4:AL4"/>
     <mergeCell ref="AN4:AO4"/>
     <mergeCell ref="AQ4:AR4"/>
@@ -17648,14 +17762,12 @@
     <mergeCell ref="AB4:AC4"/>
     <mergeCell ref="AE4:AF4"/>
     <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="AN6:AO6"/>
-    <mergeCell ref="AQ6:AR6"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AE6:AF6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="AK6:AL6"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="M4:N4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -17671,14 +17783,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="57" t="s">
         <v>83</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="D2" s="52" t="s">
+      <c r="B2" s="57"/>
+      <c r="D2" s="58" t="s">
         <v>81</v>
       </c>
-      <c r="E2" s="52"/>
+      <c r="E2" s="58"/>
       <c r="G2" s="22" t="s">
         <v>82</v>
       </c>
@@ -18257,36 +18369,36 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="59" t="s">
         <v>121</v>
       </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="F2" s="53" t="s">
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="F2" s="59" t="s">
         <v>122</v>
       </c>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="J2" s="53" t="s">
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="J2" s="59" t="s">
         <v>123</v>
       </c>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-      <c r="N2" s="53" t="s">
+      <c r="K2" s="59"/>
+      <c r="L2" s="59"/>
+      <c r="N2" s="59" t="s">
         <v>124</v>
       </c>
-      <c r="O2" s="53"/>
-      <c r="P2" s="53"/>
-      <c r="R2" s="53" t="s">
+      <c r="O2" s="59"/>
+      <c r="P2" s="59"/>
+      <c r="R2" s="59" t="s">
         <v>125</v>
       </c>
-      <c r="S2" s="53"/>
-      <c r="T2" s="53"/>
-      <c r="V2" s="53" t="s">
+      <c r="S2" s="59"/>
+      <c r="T2" s="59"/>
+      <c r="V2" s="59" t="s">
         <v>126</v>
       </c>
-      <c r="W2" s="53"/>
-      <c r="X2" s="53"/>
+      <c r="W2" s="59"/>
+      <c r="X2" s="59"/>
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">

--- a/docs/usage/sample_sheets/sheets_polygon.xlsx
+++ b/docs/usage/sample_sheets/sheets_polygon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{807E244B-733A-DD48-859C-6A1D7FF99A48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA8D9778-BA48-644C-980F-473DF9F954B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="34200" windowHeight="19900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -458,9 +458,6 @@
     <t>nu</t>
   </si>
   <si>
-    <t>ssr_zone</t>
-  </si>
-  <si>
     <t>u</t>
   </si>
   <si>
@@ -972,6 +969,9 @@
   </si>
   <si>
     <t>corps</t>
+  </si>
+  <si>
+    <t>Mat ID = -1 --&gt; SSR reduce, Mat ID = -2 --&gt; SSR hold, Mat ID = -3 --&gt; SSR elastic</t>
   </si>
 </sst>
 </file>
@@ -1479,11 +1479,18 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="20">
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="1" tint="0.499984740745262"/>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1504,21 +1511,7 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
+          <bgColor theme="1" tint="0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -8972,7 +8965,7 @@
         <v>13</v>
       </c>
       <c r="D5" s="30">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -9261,7 +9254,7 @@
     </row>
     <row r="67" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D67" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="68" spans="4:4" x14ac:dyDescent="0.2">
@@ -9360,90 +9353,90 @@
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B2" s="63" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
       <c r="F2" s="63" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G2" s="62"/>
       <c r="H2" s="62"/>
       <c r="J2" s="63" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K2" s="62"/>
       <c r="L2" s="62"/>
       <c r="N2" s="63" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
       <c r="R2" s="63" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="S2" s="62"/>
       <c r="T2" s="62"/>
       <c r="V2" s="63" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="W2" s="62"/>
       <c r="X2" s="62"/>
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="H3" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="L3" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="N3" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="O3" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="P3" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="R3" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="S3" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="S3" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="T3" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V3" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="W3" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="W3" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="X3" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.2">
@@ -9828,12 +9821,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B2:D2"/>
     <mergeCell ref="V2:X2"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="R2:T2"/>
     <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9854,67 +9847,67 @@
   <sheetData>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="40" t="s">
         <v>255</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="H2" s="40" t="s">
         <v>256</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="I2" s="40" t="s">
         <v>257</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="J2" s="27" t="s">
         <v>258</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="K2" s="27" t="s">
         <v>259</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="L2" s="27" t="s">
         <v>260</v>
       </c>
-      <c r="L2" s="27" t="s">
+      <c r="M2" s="27" t="s">
         <v>261</v>
       </c>
-      <c r="M2" s="27" t="s">
+      <c r="N2" s="27" t="s">
         <v>262</v>
       </c>
-      <c r="N2" s="27" t="s">
+      <c r="O2" s="27" t="s">
         <v>263</v>
       </c>
-      <c r="O2" s="27" t="s">
+      <c r="P2" s="28" t="s">
         <v>264</v>
-      </c>
-      <c r="P2" s="28" t="s">
-        <v>265</v>
       </c>
       <c r="Q2" s="28" t="s">
         <v>130</v>
       </c>
       <c r="R2" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="Z2" t="s">
         <v>266</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
         <v>267</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AB2" t="s">
         <v>268</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
@@ -9945,13 +9938,13 @@
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
       <c r="Z3" t="s">
+        <v>269</v>
+      </c>
+      <c r="AA3" t="s">
         <v>270</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AB3" t="s">
         <v>271</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.2">
@@ -9982,7 +9975,7 @@
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
       <c r="Z4" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -10013,7 +10006,7 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="Z5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -10100,13 +10093,13 @@
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="Z8" t="s">
+        <v>266</v>
+      </c>
+      <c r="AA8" t="s">
         <v>267</v>
       </c>
-      <c r="AA8" t="s">
+      <c r="AB8" t="s">
         <v>268</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
@@ -10137,13 +10130,13 @@
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
       <c r="Z9" t="s">
+        <v>269</v>
+      </c>
+      <c r="AA9" t="s">
         <v>270</v>
       </c>
-      <c r="AA9" t="s">
+      <c r="AB9" t="s">
         <v>271</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
@@ -10174,13 +10167,13 @@
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
       <c r="Z10" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AA10" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AB10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
@@ -10211,13 +10204,13 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="Z11" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AA11" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AB11" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -10581,61 +10574,61 @@
   <sheetData>
     <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>250</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>251</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="12" t="s">
         <v>252</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>253</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>254</v>
       </c>
-      <c r="F2" s="12" t="s">
-        <v>255</v>
-      </c>
       <c r="G2" s="40" t="s">
+        <v>274</v>
+      </c>
+      <c r="H2" s="40" t="s">
         <v>275</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="I2" s="40" t="s">
+        <v>257</v>
+      </c>
+      <c r="J2" s="27" t="s">
         <v>276</v>
       </c>
-      <c r="I2" s="40" t="s">
-        <v>258</v>
-      </c>
-      <c r="J2" s="27" t="s">
+      <c r="K2" s="27" t="s">
         <v>277</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="L2" s="41" t="s">
         <v>278</v>
       </c>
-      <c r="L2" s="41" t="s">
+      <c r="M2" s="41" t="s">
         <v>279</v>
-      </c>
-      <c r="M2" s="41" t="s">
-        <v>280</v>
       </c>
       <c r="N2" s="28" t="s">
         <v>130</v>
       </c>
       <c r="O2" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="P2" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="Q2" s="28" t="s">
         <v>281</v>
       </c>
-      <c r="P2" s="28" t="s">
-        <v>266</v>
-      </c>
-      <c r="Q2" s="28" t="s">
-        <v>282</v>
-      </c>
       <c r="Z2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AA2" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
@@ -10659,10 +10652,10 @@
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
       <c r="Z3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AA3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
@@ -10905,22 +10898,22 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C2" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="D2" s="12" t="s">
-        <v>179</v>
-      </c>
       <c r="E2" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="F2" s="12" t="s">
         <v>283</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -11143,27 +11136,27 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="64" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="59" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F2" s="54"/>
       <c r="H2" s="59" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I2" s="54"/>
       <c r="K2" s="59" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="L2" s="54"/>
       <c r="N2" s="59" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="O2" s="54"/>
       <c r="Q2" s="59" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="R2" s="54"/>
     </row>
@@ -11187,63 +11180,63 @@
         <v>10.0</v>
       </c>
       <c r="K3" s="32" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L3" s="33"/>
       <c r="N3" s="32" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O3" s="33"/>
       <c r="Q3" s="32" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="R3" s="33"/>
       <c r="T3" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B4" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="C4" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="C4" s="25" t="s">
-        <v>179</v>
-      </c>
       <c r="E4" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="F4" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="F4" s="25" t="s">
-        <v>179</v>
-      </c>
       <c r="H4" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="I4" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="I4" s="25" t="s">
-        <v>179</v>
-      </c>
       <c r="K4" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="L4" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="L4" s="25" t="s">
-        <v>179</v>
-      </c>
       <c r="N4" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="O4" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="O4" s="25" t="s">
-        <v>179</v>
-      </c>
       <c r="Q4" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="R4" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="R4" s="25" t="s">
-        <v>179</v>
-      </c>
       <c r="T4" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="U4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -11272,10 +11265,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="U5" t="s">
         <v>294</v>
-      </c>
-      <c r="U5" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -11304,7 +11297,7 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="T6" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="U6" s="9"/>
     </row>
@@ -11597,27 +11590,27 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="68" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="60" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F2" s="54"/>
       <c r="H2" s="60" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="I2" s="54"/>
       <c r="K2" s="60" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L2" s="54"/>
       <c r="N2" s="60" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O2" s="54"/>
       <c r="Q2" s="60" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="R2" s="54"/>
     </row>
@@ -11625,71 +11618,71 @@
       <c r="B3" s="66"/>
       <c r="C3" s="67"/>
       <c r="E3" s="34" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F3" s="35"/>
       <c r="H3" s="34" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I3" s="35"/>
       <c r="K3" s="34" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L3" s="35"/>
       <c r="N3" s="34" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="O3" s="35"/>
       <c r="Q3" s="34" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="R3" s="35"/>
       <c r="T3" s="6" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B4" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="C4" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="C4" s="25" t="s">
-        <v>179</v>
-      </c>
       <c r="E4" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="F4" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="F4" s="25" t="s">
-        <v>179</v>
-      </c>
       <c r="H4" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="I4" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="I4" s="25" t="s">
-        <v>179</v>
-      </c>
       <c r="K4" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="L4" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="L4" s="25" t="s">
-        <v>179</v>
-      </c>
       <c r="N4" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="O4" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="O4" s="25" t="s">
-        <v>179</v>
-      </c>
       <c r="Q4" s="25" t="s">
+        <v>177</v>
+      </c>
+      <c r="R4" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="R4" s="25" t="s">
-        <v>179</v>
-      </c>
       <c r="T4" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="U4" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -11706,10 +11699,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="U5" t="s">
         <v>294</v>
-      </c>
-      <c r="U5" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -12941,52 +12934,52 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A2:AQ52"/>
+  <dimension ref="A2:AP52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" style="1" customWidth="1"/>
     <col min="3" max="10" width="8.5" style="1" customWidth="1"/>
-    <col min="11" max="42" width="8.5" customWidth="1"/>
+    <col min="11" max="41" width="8.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C2" s="6" t="s">
         <v>86</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="O2" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="AE2" s="6"/>
-      <c r="AK2" s="6" t="s">
+      <c r="AD2" s="6"/>
+      <c r="AJ2" s="6" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C3" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D3" t="s">
         <v>91</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="P3" t="s">
         <v>93</v>
       </c>
-      <c r="AE3" s="14"/>
-      <c r="AK3" s="1" t="s">
+      <c r="AD3" s="14"/>
+      <c r="AJ3" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="AL3" t="s">
+      <c r="AK3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C4" s="1" t="s">
         <v>96</v>
       </c>
@@ -12997,21 +12990,21 @@
       <c r="M4" t="s">
         <v>98</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="O4" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="P4" t="s">
         <v>99</v>
       </c>
-      <c r="AE4" s="14"/>
-      <c r="AK4" s="1" t="s">
+      <c r="AD4" s="14"/>
+      <c r="AJ4" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="AL4" t="s">
+      <c r="AK4" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C5" s="1" t="s">
         <v>102</v>
       </c>
@@ -13022,21 +13015,21 @@
       <c r="M5" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="P5" s="1" t="s">
+      <c r="O5" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="Q5" s="9" t="s">
+      <c r="P5" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="AE5" s="14"/>
-      <c r="AK5" s="1" t="s">
+      <c r="AD5" s="14"/>
+      <c r="AJ5" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="AL5" s="9" t="s">
+      <c r="AK5" s="9" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C6" s="1" t="s">
         <v>109</v>
       </c>
@@ -13047,26 +13040,26 @@
       <c r="M6" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="P6" s="1" t="s">
+      <c r="O6" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="P6" t="s">
         <v>113</v>
       </c>
+      <c r="AE6" s="1"/>
       <c r="AF6" s="1"/>
-      <c r="AG6" s="1"/>
-    </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>114</v>
       </c>
       <c r="D7" s="9" t="s">
         <v>115</v>
       </c>
+      <c r="AE7" s="1"/>
       <c r="AF7" s="1"/>
-      <c r="AG7" s="1"/>
-    </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="53" t="s">
         <v>116</v>
       </c>
@@ -13093,18 +13086,18 @@
       <c r="X9" s="54"/>
       <c r="Y9" s="54"/>
       <c r="Z9" s="54"/>
-      <c r="AA9" s="54"/>
-      <c r="AB9" s="53" t="s">
+      <c r="AA9" s="53" t="s">
         <v>117</v>
       </c>
+      <c r="AB9" s="54"/>
       <c r="AC9" s="54"/>
       <c r="AD9" s="54"/>
       <c r="AE9" s="54"/>
       <c r="AF9" s="54"/>
-      <c r="AG9" s="54"/>
-      <c r="AH9" s="53" t="s">
+      <c r="AG9" s="53" t="s">
         <v>118</v>
       </c>
+      <c r="AH9" s="54"/>
       <c r="AI9" s="54"/>
       <c r="AJ9" s="54"/>
       <c r="AK9" s="54"/>
@@ -13113,9 +13106,8 @@
       <c r="AN9" s="54"/>
       <c r="AO9" s="54"/>
       <c r="AP9" s="54"/>
-      <c r="AQ9" s="54"/>
-    </row>
-    <row r="10" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:42" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="20" t="s">
         <v>23</v>
       </c>
@@ -13158,14 +13150,14 @@
       <c r="N10" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="O10" s="43" t="s">
+      <c r="O10" s="44" t="s">
         <v>132</v>
       </c>
       <c r="P10" s="44" t="s">
+        <v>112</v>
+      </c>
+      <c r="Q10" s="44" t="s">
         <v>133</v>
-      </c>
-      <c r="Q10" s="44" t="s">
-        <v>112</v>
       </c>
       <c r="R10" s="44" t="s">
         <v>134</v>
@@ -13194,25 +13186,25 @@
       <c r="Z10" s="44" t="s">
         <v>142</v>
       </c>
-      <c r="AA10" s="44" t="s">
+      <c r="AA10" s="46" t="s">
         <v>143</v>
       </c>
       <c r="AB10" s="46" t="s">
         <v>144</v>
       </c>
-      <c r="AC10" s="46" t="s">
+      <c r="AC10" s="47" t="s">
         <v>145</v>
       </c>
-      <c r="AD10" s="47" t="s">
+      <c r="AD10" s="46" t="s">
         <v>146</v>
       </c>
       <c r="AE10" s="46" t="s">
         <v>147</v>
       </c>
-      <c r="AF10" s="46" t="s">
+      <c r="AF10" s="47" t="s">
         <v>148</v>
       </c>
-      <c r="AG10" s="47" t="s">
+      <c r="AG10" s="23" t="s">
         <v>149</v>
       </c>
       <c r="AH10" s="23" t="s">
@@ -13242,11 +13234,8 @@
       <c r="AP10" s="23" t="s">
         <v>158</v>
       </c>
-      <c r="AQ10" s="23" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>1</v>
       </c>
@@ -13285,17 +13274,19 @@
       <c r="N11" s="3">
         <v>0.0</v>
       </c>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3" t="inlineStr">
+      <c r="O11" s="3" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="Q11" s="3">
+      <c r="P11" s="3">
         <v>0.0</v>
       </c>
+      <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-      <c r="S11" s="3"/>
+      <c r="S11" s="3">
+        <v>0.0</v>
+      </c>
       <c r="T11" s="3">
         <v>0.0</v>
       </c>
@@ -13336,38 +13327,35 @@
         <v>0.0</v>
       </c>
       <c r="AG11" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="AH11" s="3">
+        <v>0.2</v>
+      </c>
+      <c r="AI11" s="3">
         <v>0.0</v>
       </c>
-      <c r="AH11" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="AI11" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="AJ11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AK11" s="3" t="inlineStr">
+      <c r="AJ11" s="3" t="inlineStr">
         <is>
           <t>lf</t>
         </is>
       </c>
+      <c r="AK11" s="3">
+        <v>0.001</v>
+      </c>
       <c r="AL11" s="3">
-        <v>0.001</v>
+        <v>-1.0</v>
       </c>
       <c r="AM11" s="3">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="AN11" s="3">
         <v>0.0</v>
       </c>
-      <c r="AO11" s="3">
-        <v>0.0</v>
-      </c>
+      <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
-      <c r="AQ11" s="3"/>
-    </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>2</v>
       </c>
@@ -13406,17 +13394,19 @@
       <c r="N12" s="3">
         <v>0.0</v>
       </c>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3" t="inlineStr">
+      <c r="O12" s="3" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="Q12" s="3">
+      <c r="P12" s="3">
         <v>0.0</v>
       </c>
+      <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
-      <c r="S12" s="3"/>
+      <c r="S12" s="3">
+        <v>0.0</v>
+      </c>
       <c r="T12" s="3">
         <v>0.0</v>
       </c>
@@ -13457,38 +13447,35 @@
         <v>0.0</v>
       </c>
       <c r="AG12" s="3">
-        <v>0.0</v>
+        <v>0.2</v>
       </c>
       <c r="AH12" s="3">
         <v>0.2</v>
       </c>
       <c r="AI12" s="3">
-        <v>0.2</v>
-      </c>
-      <c r="AJ12" s="3">
         <v>0.0</v>
       </c>
-      <c r="AK12" s="3" t="inlineStr">
+      <c r="AJ12" s="3" t="inlineStr">
         <is>
           <t>lf</t>
         </is>
       </c>
+      <c r="AK12" s="3">
+        <v>0.001</v>
+      </c>
       <c r="AL12" s="3">
-        <v>0.001</v>
-      </c>
-      <c r="AM12" s="3">
         <v>-1.0</v>
       </c>
-      <c r="AN12" s="18">
+      <c r="AM12" s="18">
         <v>0.0</v>
       </c>
-      <c r="AO12" s="19">
+      <c r="AN12" s="19">
         <v>0.0</v>
       </c>
+      <c r="AO12" s="19"/>
       <c r="AP12" s="19"/>
-      <c r="AQ12" s="19"/>
-    </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>3</v>
       </c>
@@ -13527,17 +13514,19 @@
       <c r="N13" s="3">
         <v>0.0</v>
       </c>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3" t="inlineStr">
+      <c r="O13" s="3" t="inlineStr">
         <is>
           <t>none</t>
         </is>
       </c>
-      <c r="Q13" s="3">
+      <c r="P13" s="3">
         <v>0.0</v>
       </c>
+      <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
-      <c r="S13" s="3"/>
+      <c r="S13" s="3">
+        <v>0.0</v>
+      </c>
       <c r="T13" s="3">
         <v>0.0</v>
       </c>
@@ -13578,38 +13567,35 @@
         <v>0.0</v>
       </c>
       <c r="AG13" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="AH13" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="AI13" s="3">
         <v>0.0</v>
       </c>
-      <c r="AH13" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="AI13" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="AJ13" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="AK13" s="3" t="inlineStr">
+      <c r="AJ13" s="3" t="inlineStr">
         <is>
           <t>lf</t>
         </is>
       </c>
+      <c r="AK13" s="3">
+        <v>0.001</v>
+      </c>
       <c r="AL13" s="3">
-        <v>0.001</v>
-      </c>
-      <c r="AM13" s="3">
         <v>-1.0</v>
       </c>
-      <c r="AN13" s="18">
+      <c r="AM13" s="18">
         <v>0.0</v>
       </c>
-      <c r="AO13" s="19">
+      <c r="AN13" s="19">
         <v>0.0</v>
       </c>
+      <c r="AO13" s="19"/>
       <c r="AP13" s="19"/>
-      <c r="AQ13" s="19"/>
-    </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>4</v>
       </c>
@@ -13654,9 +13640,8 @@
       <c r="AN14" s="3"/>
       <c r="AO14" s="3"/>
       <c r="AP14" s="3"/>
-      <c r="AQ14" s="3"/>
-    </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>5</v>
       </c>
@@ -13701,9 +13686,8 @@
       <c r="AN15" s="3"/>
       <c r="AO15" s="3"/>
       <c r="AP15" s="3"/>
-      <c r="AQ15" s="3"/>
-    </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>6</v>
       </c>
@@ -13748,9 +13732,8 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
-      <c r="AQ16" s="3"/>
-    </row>
-    <row r="17" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="17" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>7</v>
       </c>
@@ -13795,9 +13778,8 @@
       <c r="AN17" s="3"/>
       <c r="AO17" s="3"/>
       <c r="AP17" s="3"/>
-      <c r="AQ17" s="3"/>
-    </row>
-    <row r="18" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="18" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>8</v>
       </c>
@@ -13842,9 +13824,8 @@
       <c r="AN18" s="3"/>
       <c r="AO18" s="3"/>
       <c r="AP18" s="3"/>
-      <c r="AQ18" s="3"/>
-    </row>
-    <row r="19" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>9</v>
       </c>
@@ -13889,9 +13870,8 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
-      <c r="AQ19" s="3"/>
-    </row>
-    <row r="20" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>10</v>
       </c>
@@ -13936,9 +13916,8 @@
       <c r="AN20" s="3"/>
       <c r="AO20" s="3"/>
       <c r="AP20" s="3"/>
-      <c r="AQ20" s="3"/>
-    </row>
-    <row r="21" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>11</v>
       </c>
@@ -13983,9 +13962,8 @@
       <c r="AN21" s="3"/>
       <c r="AO21" s="3"/>
       <c r="AP21" s="3"/>
-      <c r="AQ21" s="3"/>
-    </row>
-    <row r="22" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="22" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>12</v>
       </c>
@@ -14030,9 +14008,8 @@
       <c r="AN22" s="3"/>
       <c r="AO22" s="3"/>
       <c r="AP22" s="3"/>
-      <c r="AQ22" s="3"/>
-    </row>
-    <row r="23" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>13</v>
       </c>
@@ -14077,9 +14054,8 @@
       <c r="AN23" s="3"/>
       <c r="AO23" s="3"/>
       <c r="AP23" s="3"/>
-      <c r="AQ23" s="3"/>
-    </row>
-    <row r="24" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="24" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>14</v>
       </c>
@@ -14124,9 +14100,8 @@
       <c r="AN24" s="3"/>
       <c r="AO24" s="3"/>
       <c r="AP24" s="3"/>
-      <c r="AQ24" s="3"/>
-    </row>
-    <row r="25" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>15</v>
       </c>
@@ -14171,9 +14146,8 @@
       <c r="AN25" s="3"/>
       <c r="AO25" s="3"/>
       <c r="AP25" s="3"/>
-      <c r="AQ25" s="3"/>
-    </row>
-    <row r="26" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="26" spans="1:42" x14ac:dyDescent="0.2">
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -14206,9 +14180,8 @@
       <c r="AN26" s="1"/>
       <c r="AO26" s="1"/>
       <c r="AP26" s="1"/>
-      <c r="AQ26" s="1"/>
-    </row>
-    <row r="27" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:42" x14ac:dyDescent="0.2">
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -14231,9 +14204,8 @@
       <c r="AD27" s="1"/>
       <c r="AE27" s="1"/>
       <c r="AF27" s="1"/>
-      <c r="AG27" s="1"/>
-    </row>
-    <row r="28" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:42" x14ac:dyDescent="0.2">
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -14256,9 +14228,8 @@
       <c r="AD28" s="1"/>
       <c r="AE28" s="1"/>
       <c r="AF28" s="1"/>
-      <c r="AG28" s="1"/>
-    </row>
-    <row r="29" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:42" x14ac:dyDescent="0.2">
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -14281,9 +14252,8 @@
       <c r="AD29" s="1"/>
       <c r="AE29" s="1"/>
       <c r="AF29" s="1"/>
-      <c r="AG29" s="1"/>
-    </row>
-    <row r="30" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:42" x14ac:dyDescent="0.2">
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -14306,9 +14276,8 @@
       <c r="AD30" s="1"/>
       <c r="AE30" s="1"/>
       <c r="AF30" s="1"/>
-      <c r="AG30" s="1"/>
-    </row>
-    <row r="31" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:42" x14ac:dyDescent="0.2">
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -14331,9 +14300,8 @@
       <c r="AD31" s="1"/>
       <c r="AE31" s="1"/>
       <c r="AF31" s="1"/>
-      <c r="AG31" s="1"/>
-    </row>
-    <row r="32" spans="1:43" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:42" x14ac:dyDescent="0.2">
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -14356,9 +14324,8 @@
       <c r="AD32" s="1"/>
       <c r="AE32" s="1"/>
       <c r="AF32" s="1"/>
-      <c r="AG32" s="1"/>
-    </row>
-    <row r="33" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
@@ -14381,9 +14348,8 @@
       <c r="AD33" s="1"/>
       <c r="AE33" s="1"/>
       <c r="AF33" s="1"/>
-      <c r="AG33" s="1"/>
-    </row>
-    <row r="34" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
@@ -14406,9 +14372,8 @@
       <c r="AD34" s="1"/>
       <c r="AE34" s="1"/>
       <c r="AF34" s="1"/>
-      <c r="AG34" s="1"/>
-    </row>
-    <row r="35" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
@@ -14431,9 +14396,8 @@
       <c r="AD35" s="1"/>
       <c r="AE35" s="1"/>
       <c r="AF35" s="1"/>
-      <c r="AG35" s="1"/>
-    </row>
-    <row r="36" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="36" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
@@ -14456,9 +14420,8 @@
       <c r="AD36" s="1"/>
       <c r="AE36" s="1"/>
       <c r="AF36" s="1"/>
-      <c r="AG36" s="1"/>
-    </row>
-    <row r="37" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="37" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
@@ -14481,9 +14444,8 @@
       <c r="AD37" s="1"/>
       <c r="AE37" s="1"/>
       <c r="AF37" s="1"/>
-      <c r="AG37" s="1"/>
-    </row>
-    <row r="38" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="38" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
@@ -14506,9 +14468,8 @@
       <c r="AD38" s="1"/>
       <c r="AE38" s="1"/>
       <c r="AF38" s="1"/>
-      <c r="AG38" s="1"/>
-    </row>
-    <row r="39" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="39" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
@@ -14531,9 +14492,8 @@
       <c r="AD39" s="1"/>
       <c r="AE39" s="1"/>
       <c r="AF39" s="1"/>
-      <c r="AG39" s="1"/>
-    </row>
-    <row r="40" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="40" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K40" s="1"/>
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
@@ -14556,9 +14516,8 @@
       <c r="AD40" s="1"/>
       <c r="AE40" s="1"/>
       <c r="AF40" s="1"/>
-      <c r="AG40" s="1"/>
-    </row>
-    <row r="41" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="41" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
@@ -14581,9 +14540,8 @@
       <c r="AD41" s="1"/>
       <c r="AE41" s="1"/>
       <c r="AF41" s="1"/>
-      <c r="AG41" s="1"/>
-    </row>
-    <row r="42" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="1"/>
@@ -14606,9 +14564,8 @@
       <c r="AD42" s="1"/>
       <c r="AE42" s="1"/>
       <c r="AF42" s="1"/>
-      <c r="AG42" s="1"/>
-    </row>
-    <row r="43" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="43" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K43" s="1"/>
       <c r="L43" s="1"/>
       <c r="M43" s="1"/>
@@ -14631,9 +14588,8 @@
       <c r="AD43" s="1"/>
       <c r="AE43" s="1"/>
       <c r="AF43" s="1"/>
-      <c r="AG43" s="1"/>
-    </row>
-    <row r="44" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="44" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K44" s="1"/>
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
@@ -14656,9 +14612,8 @@
       <c r="AD44" s="1"/>
       <c r="AE44" s="1"/>
       <c r="AF44" s="1"/>
-      <c r="AG44" s="1"/>
-    </row>
-    <row r="45" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="45" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
@@ -14681,9 +14636,8 @@
       <c r="AD45" s="1"/>
       <c r="AE45" s="1"/>
       <c r="AF45" s="1"/>
-      <c r="AG45" s="1"/>
-    </row>
-    <row r="46" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="46" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K46" s="1"/>
       <c r="L46" s="1"/>
       <c r="M46" s="1"/>
@@ -14706,9 +14660,8 @@
       <c r="AD46" s="1"/>
       <c r="AE46" s="1"/>
       <c r="AF46" s="1"/>
-      <c r="AG46" s="1"/>
-    </row>
-    <row r="47" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="47" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K47" s="1"/>
       <c r="L47" s="1"/>
       <c r="M47" s="1"/>
@@ -14731,9 +14684,8 @@
       <c r="AD47" s="1"/>
       <c r="AE47" s="1"/>
       <c r="AF47" s="1"/>
-      <c r="AG47" s="1"/>
-    </row>
-    <row r="48" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="48" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K48" s="1"/>
       <c r="L48" s="1"/>
       <c r="M48" s="1"/>
@@ -14756,9 +14708,8 @@
       <c r="AD48" s="1"/>
       <c r="AE48" s="1"/>
       <c r="AF48" s="1"/>
-      <c r="AG48" s="1"/>
-    </row>
-    <row r="49" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="49" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
       <c r="M49" s="1"/>
@@ -14781,9 +14732,8 @@
       <c r="AD49" s="1"/>
       <c r="AE49" s="1"/>
       <c r="AF49" s="1"/>
-      <c r="AG49" s="1"/>
-    </row>
-    <row r="50" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="50" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K50" s="1"/>
       <c r="L50" s="1"/>
       <c r="M50" s="1"/>
@@ -14806,9 +14756,8 @@
       <c r="AD50" s="1"/>
       <c r="AE50" s="1"/>
       <c r="AF50" s="1"/>
-      <c r="AG50" s="1"/>
-    </row>
-    <row r="51" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
       <c r="M51" s="1"/>
@@ -14831,9 +14780,8 @@
       <c r="AD51" s="1"/>
       <c r="AE51" s="1"/>
       <c r="AF51" s="1"/>
-      <c r="AG51" s="1"/>
-    </row>
-    <row r="52" spans="11:33" x14ac:dyDescent="0.2">
+    </row>
+    <row r="52" spans="11:32" x14ac:dyDescent="0.2">
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="1"/>
@@ -14856,109 +14804,103 @@
       <c r="AD52" s="1"/>
       <c r="AE52" s="1"/>
       <c r="AF52" s="1"/>
-      <c r="AG52" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="C9:AA9"/>
-    <mergeCell ref="AB9:AG9"/>
-    <mergeCell ref="AH9:AQ9"/>
+    <mergeCell ref="C9:Z9"/>
+    <mergeCell ref="AA9:AF9"/>
+    <mergeCell ref="AG9:AP9"/>
   </mergeCells>
-  <conditionalFormatting sqref="F11:K52 AC11:AG52">
-    <cfRule type="expression" dxfId="20" priority="6">
+  <conditionalFormatting sqref="F11:K52 AB11:AF52">
+    <cfRule type="expression" dxfId="19" priority="6">
       <formula>$E11="hb"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="19" priority="7">
+    <cfRule type="expression" dxfId="18" priority="7">
       <formula>$E11="pow"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F11:L52">
-    <cfRule type="expression" dxfId="18" priority="19">
+  <conditionalFormatting sqref="F11:L52 O11:R52">
+    <cfRule type="expression" dxfId="17" priority="19">
       <formula>$E11="elastic"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11:G52">
-    <cfRule type="expression" dxfId="17" priority="8">
+    <cfRule type="expression" dxfId="16" priority="8">
       <formula>$E11="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11:I52">
-    <cfRule type="expression" dxfId="16" priority="9">
+    <cfRule type="expression" dxfId="15" priority="9">
       <formula>$E11="mc"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J11:K52">
-    <cfRule type="expression" dxfId="15" priority="10">
+    <cfRule type="expression" dxfId="14" priority="10">
       <formula>$E11="cp"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O11:S52">
-    <cfRule type="expression" dxfId="14" priority="4">
+  <conditionalFormatting sqref="P11:P52">
+    <cfRule type="expression" dxfId="13" priority="13">
+      <formula>AND($O11&lt;&gt;"",$O11&lt;&gt;"ru")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="S11:V52">
+    <cfRule type="expression" dxfId="12" priority="11">
+      <formula>AND($E11&lt;&gt;"",$E11&lt;&gt;"pow")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W11:Z52">
+    <cfRule type="expression" dxfId="11" priority="12">
+      <formula>AND($E11&lt;&gt;"",$E11&lt;&gt;"hb")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB11:AF52">
+    <cfRule type="expression" dxfId="10" priority="21">
       <formula>$E11="elastic"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q11:Q52">
-    <cfRule type="expression" dxfId="13" priority="13">
-      <formula>AND($P11&lt;&gt;"",$P11&lt;&gt;"ru")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R11:S52">
-    <cfRule type="expression" dxfId="12" priority="3">
+  <conditionalFormatting sqref="AC11:AC52">
+    <cfRule type="expression" dxfId="9" priority="14">
       <formula>$E11="cp"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="11" priority="5">
-      <formula>AND($P11&lt;&gt;"",$P11&lt;&gt;"piezo",$P11&lt;&gt;"seep")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="T11:W52">
-    <cfRule type="expression" dxfId="10" priority="11">
-      <formula>AND($E11&lt;&gt;"",$E11&lt;&gt;"pow")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X11:AA52">
-    <cfRule type="expression" dxfId="9" priority="12">
-      <formula>AND($E11&lt;&gt;"",$E11&lt;&gt;"hb")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AC11:AG52">
-    <cfRule type="expression" dxfId="8" priority="21">
-      <formula>$E11="elastic"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD11:AD52">
-    <cfRule type="expression" dxfId="7" priority="14">
+    <cfRule type="expression" dxfId="8" priority="15">
+      <formula>$E11="mc"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AE11:AF52">
+    <cfRule type="expression" dxfId="7" priority="16">
       <formula>$E11="cp"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AE11:AE52">
-    <cfRule type="expression" dxfId="6" priority="15">
-      <formula>$E11="mc"</formula>
+  <conditionalFormatting sqref="AK11:AL52">
+    <cfRule type="expression" dxfId="6" priority="17">
+      <formula>OR($AJ11="vg",$AJ11="gard")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AF11:AG52">
-    <cfRule type="expression" dxfId="5" priority="16">
+  <conditionalFormatting sqref="AM11:AN52">
+    <cfRule type="expression" dxfId="5" priority="1">
+      <formula>$AJ11="lf"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q11:R52">
+    <cfRule type="expression" dxfId="1" priority="23">
       <formula>$E11="cp"</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AL11:AM52">
-    <cfRule type="expression" dxfId="4" priority="17">
-      <formula>OR($AK11="vg",$AK11="gard")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AN11:AO52">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>$AK11="lf"</formula>
+    <cfRule type="expression" dxfId="0" priority="24">
+      <formula>AND($O11&lt;&gt;"",$O11&lt;&gt;"piezo",$O11&lt;&gt;"seep")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="E11:E52" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>$C$3:$C$7</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="AK11:AK102" xr:uid="{00000000-0002-0000-0200-000001000000}">
-      <formula1>$AK$3:$AK$5</formula1>
+    <dataValidation type="list" allowBlank="1" sqref="AJ11:AJ102" xr:uid="{00000000-0002-0000-0200-000001000000}">
+      <formula1>$AJ$3:$AJ$5</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="P11:P52" xr:uid="{00000000-0002-0000-0200-000002000000}">
-      <formula1>$P$3:$P$6</formula1>
+    <dataValidation type="list" allowBlank="1" sqref="O11:O52" xr:uid="{00000000-0002-0000-0200-000002000000}">
+      <formula1>$O$3:$O$6</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14993,180 +14935,180 @@
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="D2" s="24" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A4" s="55" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B4" s="52"/>
       <c r="D4" s="55" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E4" s="52"/>
       <c r="G4" s="55" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H4" s="52"/>
       <c r="J4" s="55" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K4" s="52"/>
       <c r="M4" s="55" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="N4" s="52"/>
       <c r="P4" s="55" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="Q4" s="54"/>
       <c r="R4" s="1"/>
       <c r="S4" s="55" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="T4" s="54"/>
       <c r="U4" s="1"/>
       <c r="V4" s="55" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="W4" s="54"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="55" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="Z4" s="54"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="55" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="AC4" s="54"/>
       <c r="AE4" s="55" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AF4" s="54"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="55" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AI4" s="54"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="55" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="AL4" s="54"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="55" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="AO4" s="54"/>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="55" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="AR4" s="54"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B5" s="37">
         <v>1</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E5" s="37">
         <v>2</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H5" s="37">
         <v>3</v>
       </c>
       <c r="J5" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K5" s="37">
         <v>4</v>
       </c>
       <c r="M5" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N5" s="37">
         <v>5</v>
       </c>
       <c r="P5" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q5" s="37">
         <v>6</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="T5" s="37">
         <v>7</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="W5" s="37">
         <v>8</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Z5" s="37">
         <v>9</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AC5" s="37">
         <v>10</v>
       </c>
       <c r="AE5" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AF5" s="37">
         <v>11</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AI5" s="37">
         <v>12</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AL5" s="37">
         <v>13</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AO5" s="37">
         <v>14</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="36" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AR5" s="37">
         <v>15</v>
@@ -15259,102 +15201,102 @@
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="D7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="G7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="J7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="M7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="N7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="P7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="R7" s="1"/>
       <c r="S7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="T7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="U7" s="1"/>
       <c r="V7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="W7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="W7" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="X7" s="1"/>
       <c r="Y7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="Z7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="Z7" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="AA7" s="1"/>
       <c r="AB7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="AC7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="AE7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="AF7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="AF7" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="AG7" s="1"/>
       <c r="AH7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="AI7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="AI7" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="AJ7" s="1"/>
       <c r="AK7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="AL7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="AL7" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="AM7" s="1"/>
       <c r="AN7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="AO7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="AO7" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="AP7" s="1"/>
       <c r="AQ7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="AR7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="AR7" s="2" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.2">
@@ -16159,6 +16101,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="AN6:AO6"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="Y6:Z6"/>
     <mergeCell ref="AQ4:AR4"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
@@ -16175,20 +16131,6 @@
     <mergeCell ref="AH4:AI4"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AN6:AO6"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="AN4:AO4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16222,7 +16164,10 @@
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
-        <v>180</v>
+        <v>179</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
@@ -16250,154 +16195,160 @@
         </is>
       </c>
       <c r="K4" s="52"/>
-      <c r="M4" s="55" t="s">
-        <v>185</v>
+      <c r="M4" s="55" t="inlineStr">
+        <is>
+          <t>Polygon #5</t>
+        </is>
       </c>
       <c r="N4" s="52"/>
-      <c r="P4" s="55" t="s">
-        <v>186</v>
+      <c r="P4" s="55" t="inlineStr">
+        <is>
+          <t>Polygon #6</t>
+        </is>
       </c>
       <c r="Q4" s="54"/>
       <c r="R4" s="1"/>
-      <c r="S4" s="55" t="s">
-        <v>187</v>
+      <c r="S4" s="55" t="inlineStr">
+        <is>
+          <t>Polygon #7</t>
+        </is>
       </c>
       <c r="T4" s="54"/>
       <c r="U4" s="1"/>
       <c r="V4" s="55" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="W4" s="54"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="55" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="Z4" s="54"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="55" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AC4" s="54"/>
       <c r="AE4" s="55" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="AF4" s="54"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="55" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AI4" s="54"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="55" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="AL4" s="54"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="55" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AO4" s="54"/>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="55" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AR4" s="54"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B5" s="39">
         <v>1</v>
       </c>
       <c r="D5" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E5" s="39">
         <v>3</v>
       </c>
       <c r="G5" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H5" s="39">
         <v>2</v>
       </c>
       <c r="J5" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="K5" s="39">
         <v>3</v>
       </c>
       <c r="M5" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="N5" s="39">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="P5" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Q5" s="39">
-        <v>6</v>
+        <v>-2</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="T5" s="39">
-        <v>7</v>
+        <v>-3</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="W5" s="39">
         <v>8</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Z5" s="39">
         <v>9</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AC5" s="39">
         <v>10</v>
       </c>
       <c r="AE5" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AF5" s="39">
         <v>11</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AI5" s="39">
         <v>12</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AL5" s="39">
         <v>13</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AO5" s="39">
         <v>14</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AR5" s="39">
         <v>15</v>
@@ -16428,168 +16379,171 @@
         </is>
       </c>
       <c r="K6" s="57"/>
-      <c r="M6" s="58" t="str">
-        <f>_xlfn.XLOOKUP(N5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
-        <v/>
+      <c r="M6" s="58" t="inlineStr">
+        <is>
+          <t>SSR reduce</t>
+        </is>
       </c>
       <c r="N6" s="57"/>
-      <c r="P6" s="58" t="str">
-        <f>_xlfn.XLOOKUP(Q5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
-        <v/>
+      <c r="P6" s="58" t="inlineStr">
+        <is>
+          <t>SSR hold</t>
+        </is>
       </c>
       <c r="Q6" s="57"/>
       <c r="R6" s="1"/>
-      <c r="S6" s="58" t="str">
-        <f>_xlfn.XLOOKUP(T5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
-        <v/>
+      <c r="S6" s="58" t="inlineStr">
+        <is>
+          <t>SSR elastic</t>
+        </is>
       </c>
       <c r="T6" s="57"/>
       <c r="U6" s="1"/>
       <c r="V6" s="58" t="str">
-        <f>_xlfn.XLOOKUP(W5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
+        <f>IF(W5=-1,"SSR reduce",IF(W5=-2,"SSR hold",IF(W5=-3,"SSR elastic",_xlfn.XLOOKUP(W5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
         <v/>
       </c>
       <c r="W6" s="57"/>
       <c r="X6" s="1"/>
       <c r="Y6" s="58" t="str">
-        <f>_xlfn.XLOOKUP(Z5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
+        <f>IF(Z5=-1,"SSR reduce",IF(Z5=-2,"SSR hold",IF(Z5=-3,"SSR elastic",_xlfn.XLOOKUP(Z5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
         <v/>
       </c>
       <c r="Z6" s="57"/>
       <c r="AA6" s="1"/>
       <c r="AB6" s="58" t="str">
-        <f>_xlfn.XLOOKUP(AC5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
+        <f>IF(AC5=-1,"SSR reduce",IF(AC5=-2,"SSR hold",IF(AC5=-3,"SSR elastic",_xlfn.XLOOKUP(AC5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
         <v/>
       </c>
       <c r="AC6" s="57"/>
       <c r="AE6" s="58" t="str">
-        <f>_xlfn.XLOOKUP(AF5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
+        <f>IF(AF5=-1,"SSR reduce",IF(AF5=-2,"SSR hold",IF(AF5=-3,"SSR elastic",_xlfn.XLOOKUP(AF5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
         <v/>
       </c>
       <c r="AF6" s="57"/>
       <c r="AG6" s="1"/>
       <c r="AH6" s="58" t="str">
-        <f>_xlfn.XLOOKUP(AI5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
+        <f>IF(AI5=-1,"SSR reduce",IF(AI5=-2,"SSR hold",IF(AI5=-3,"SSR elastic",_xlfn.XLOOKUP(AI5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
         <v/>
       </c>
       <c r="AI6" s="57"/>
       <c r="AJ6" s="1"/>
       <c r="AK6" s="58" t="str">
-        <f>_xlfn.XLOOKUP(AL5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
+        <f>IF(AL5=-1,"SSR reduce",IF(AL5=-2,"SSR hold",IF(AL5=-3,"SSR elastic",_xlfn.XLOOKUP(AL5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
         <v/>
       </c>
       <c r="AL6" s="57"/>
       <c r="AM6" s="1"/>
       <c r="AN6" s="58" t="str">
-        <f>_xlfn.XLOOKUP(AO5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
+        <f>IF(AO5=-1,"SSR reduce",IF(AO5=-2,"SSR hold",IF(AO5=-3,"SSR elastic",_xlfn.XLOOKUP(AO5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
         <v/>
       </c>
       <c r="AO6" s="57"/>
       <c r="AP6" s="1"/>
       <c r="AQ6" s="58" t="str">
-        <f>_xlfn.XLOOKUP(AR5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
+        <f>IF(AR5=-1,"SSR reduce",IF(AR5=-2,"SSR hold",IF(AR5=-3,"SSR elastic",_xlfn.XLOOKUP(AR5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
         <v/>
       </c>
       <c r="AR6" s="57"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="D7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="G7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="H7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="J7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="K7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="M7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="N7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="P7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="Q7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="R7" s="1"/>
       <c r="S7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="T7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="U7" s="1"/>
       <c r="V7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="W7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="W7" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="X7" s="1"/>
       <c r="Y7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="Z7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="Z7" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="AA7" s="1"/>
       <c r="AB7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="AC7" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AC7" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="AE7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="AF7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="AF7" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="AG7" s="1"/>
       <c r="AH7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="AI7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="AI7" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="AJ7" s="1"/>
       <c r="AK7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="AL7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="AL7" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="AM7" s="1"/>
       <c r="AN7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="AO7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="AO7" s="2" t="s">
-        <v>179</v>
       </c>
       <c r="AP7" s="1"/>
       <c r="AQ7" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="AR7" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="AR7" s="2" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.2">
@@ -16617,13 +16571,25 @@
       <c r="K8" s="3">
         <v>10.0</v>
       </c>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
+      <c r="M8" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="N8" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="P8" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>0.0</v>
+      </c>
       <c r="R8" s="1"/>
-      <c r="S8" s="3"/>
-      <c r="T8" s="3"/>
+      <c r="S8" s="3">
+        <v>110.0</v>
+      </c>
+      <c r="T8" s="3">
+        <v>0.0</v>
+      </c>
       <c r="U8" s="1"/>
       <c r="V8" s="3"/>
       <c r="W8" s="3"/>
@@ -16673,13 +16639,25 @@
       <c r="K9" s="3">
         <v>10.0</v>
       </c>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
+      <c r="M9" s="3">
+        <v>110.0</v>
+      </c>
+      <c r="N9" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="P9" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>0.0</v>
+      </c>
       <c r="R9" s="1"/>
-      <c r="S9" s="3"/>
-      <c r="T9" s="3"/>
+      <c r="S9" s="3">
+        <v>140.0</v>
+      </c>
+      <c r="T9" s="3">
+        <v>0.0</v>
+      </c>
       <c r="U9" s="1"/>
       <c r="V9" s="3"/>
       <c r="W9" s="3"/>
@@ -16729,13 +16707,25 @@
       <c r="K10" s="3">
         <v>10.0</v>
       </c>
-      <c r="M10" s="3"/>
-      <c r="N10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
+      <c r="M10" s="3">
+        <v>110.0</v>
+      </c>
+      <c r="N10" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="P10" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>12.0</v>
+      </c>
       <c r="R10" s="1"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="3"/>
+      <c r="S10" s="3">
+        <v>140.0</v>
+      </c>
+      <c r="T10" s="3">
+        <v>12.0</v>
+      </c>
       <c r="U10" s="1"/>
       <c r="V10" s="3"/>
       <c r="W10" s="3"/>
@@ -16785,13 +16775,25 @@
       <c r="K11" s="3">
         <v>0.0</v>
       </c>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
+      <c r="M11" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="N11" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="P11" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>12.0</v>
+      </c>
       <c r="R11" s="1"/>
-      <c r="S11" s="3"/>
-      <c r="T11" s="3"/>
+      <c r="S11" s="3">
+        <v>110.0</v>
+      </c>
+      <c r="T11" s="3">
+        <v>12.0</v>
+      </c>
       <c r="U11" s="1"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
@@ -17478,6 +17480,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="AN6:AO6"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="Y6:Z6"/>
     <mergeCell ref="AQ4:AR4"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
@@ -17494,20 +17510,6 @@
     <mergeCell ref="AH4:AI4"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="Y6:Z6"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AN6:AO6"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="AN4:AO4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -17524,20 +17526,20 @@
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="59" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B2" s="54"/>
       <c r="D2" s="60" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="E2" s="54"/>
       <c r="G2" s="22" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="32" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B3" s="33" t="inlineStr">
         <is>
@@ -17545,7 +17547,7 @@
         </is>
       </c>
       <c r="D3" s="34" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E3" s="35" t="inlineStr">
         <is>
@@ -17556,19 +17558,19 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="D4" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="G4" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H4" s="1"/>
     </row>
@@ -17581,7 +17583,7 @@
         <v>32</v>
       </c>
       <c r="H5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -17590,10 +17592,10 @@
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="G6" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="H6" t="s">
         <v>202</v>
-      </c>
-      <c r="H6" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -17730,31 +17732,31 @@
   <sheetData>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="C2" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="D2" s="13" t="s">
         <v>206</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="E2" s="13" t="s">
         <v>207</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="F2" s="13" t="s">
         <v>208</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="G2" s="13" t="s">
         <v>209</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="H2" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="J2" s="5" t="s">
         <v>211</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>212</v>
       </c>
       <c r="K2" s="10" t="s">
         <v>16</v>
@@ -17772,10 +17774,10 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="J3" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -17790,10 +17792,10 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="J4" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="K4" s="9" t="s">
         <v>214</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -17808,10 +17810,10 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="J5" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="K5" t="s">
         <v>216</v>
-      </c>
-      <c r="K5" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -17838,7 +17840,7 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="J7" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -17853,7 +17855,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="J8" s="14" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K8"/>
     </row>
@@ -17869,7 +17871,7 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="J9" s="14" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="K9"/>
     </row>
@@ -17885,7 +17887,7 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="J10" s="14" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="K10"/>
     </row>
@@ -17901,7 +17903,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="J11" s="14" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="K11"/>
     </row>
@@ -17917,31 +17919,31 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="J12" s="14" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="K12"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J13" s="14" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="K13"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J14" s="14" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="K14"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J15" s="14" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="K15"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J16" s="14" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -17950,23 +17952,23 @@
     </row>
     <row r="17" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J17" s="14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K17"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E3:E42">
-    <cfRule type="expression" dxfId="2" priority="3">
+    <cfRule type="expression" dxfId="4" priority="3">
       <formula>OR($D3="Intercept", $D3="Radius")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:G42">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="3" priority="2">
       <formula>OR($D3="Depth",$D3="Radius")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H42">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>OR($D3="Depth",$D3="Intercept")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17991,16 +17993,16 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>229</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="C2" s="12" t="s">
         <v>230</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>231</v>
-      </c>
       <c r="E2" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>16</v>
@@ -18011,10 +18013,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" t="s">
+        <v>231</v>
+      </c>
+      <c r="F3" t="s">
         <v>232</v>
-      </c>
-      <c r="F3" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -18022,10 +18024,10 @@
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="E4" t="s">
+        <v>233</v>
+      </c>
+      <c r="F4" t="s">
         <v>234</v>
-      </c>
-      <c r="F4" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -18033,10 +18035,10 @@
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="E5" t="s">
+        <v>235</v>
+      </c>
+      <c r="F5" t="s">
         <v>236</v>
-      </c>
-      <c r="F5" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -18160,90 +18162,90 @@
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B2" s="61" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C2" s="62"/>
       <c r="D2" s="62"/>
       <c r="F2" s="61" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G2" s="62"/>
       <c r="H2" s="62"/>
       <c r="J2" s="61" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K2" s="62"/>
       <c r="L2" s="62"/>
       <c r="N2" s="61" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="O2" s="62"/>
       <c r="P2" s="62"/>
       <c r="R2" s="61" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="S2" s="62"/>
       <c r="T2" s="62"/>
       <c r="V2" s="61" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="W2" s="62"/>
       <c r="X2" s="62"/>
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="D3" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="H3" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="L3" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="N3" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="O3" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="P3" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="R3" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="S3" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="S3" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="T3" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="V3" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="W3" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="W3" s="2" t="s">
-        <v>230</v>
-      </c>
       <c r="X3" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.2">
@@ -18628,12 +18630,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="B2:D2"/>
     <mergeCell ref="V2:X2"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="R2:T2"/>
     <mergeCell ref="F2:H2"/>
-    <mergeCell ref="B2:D2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docs/usage/sample_sheets/sheets_polygon.xlsx
+++ b/docs/usage/sample_sheets/sheets_polygon.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA8D9778-BA48-644C-980F-473DF9F954B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EEB53F3-5E86-5B42-A7B6-55B20E1E8D9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="34200" windowHeight="19900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="310">
   <si>
     <t>time</t>
   </si>
@@ -971,7 +971,25 @@
     <t>corps</t>
   </si>
   <si>
-    <t>Mat ID = -1 --&gt; SSR reduce, Mat ID = -2 --&gt; SSR hold, Mat ID = -3 --&gt; SSR elastic</t>
+    <t>Size:</t>
+  </si>
+  <si>
+    <t>Direction:</t>
+  </si>
+  <si>
+    <t>material</t>
+  </si>
+  <si>
+    <t>Type: material zone (default), an SSR analysis overlay, or a mesh refinement region.   Size: optional target mesh element size inside the polygon (blank = global size).</t>
+  </si>
+  <si>
+    <t>Side BC:</t>
+  </si>
+  <si>
+    <t>rollers</t>
+  </si>
+  <si>
+    <t>Size: optional target mesh element size inside this line's material zone (blank = global size).</t>
   </si>
 </sst>
 </file>
@@ -1479,18 +1497,11 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="35">
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.499984740745262"/>
+          <bgColor theme="1" tint="0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1511,7 +1522,119 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor theme="1" tint="0.499984740745262"/>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="0" tint="-0.499984740745262"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1686,7 +1809,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$A$8:$A$27</c:f>
+              <c:f>profile!$A$9:$A$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -1695,7 +1818,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$B$8:$B$27</c:f>
+              <c:f>profile!$B$9:$B$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -1749,7 +1872,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$D$8:$D$27</c:f>
+              <c:f>profile!$D$9:$D$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -1758,7 +1881,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$E$8:$E$27</c:f>
+              <c:f>profile!$E$9:$E$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -1812,7 +1935,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$G$8:$G$27</c:f>
+              <c:f>profile!$G$9:$G$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -1821,7 +1944,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$H$8:$H$27</c:f>
+              <c:f>profile!$H$9:$H$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -1875,7 +1998,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$J$8:$J$27</c:f>
+              <c:f>profile!$J$9:$J$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -1884,7 +2007,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$K$8:$K$27</c:f>
+              <c:f>profile!$K$9:$K$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -1938,7 +2061,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$M$8:$M$27</c:f>
+              <c:f>profile!$M$9:$M$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -1947,7 +2070,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$N$8:$N$27</c:f>
+              <c:f>profile!$N$9:$N$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2001,7 +2124,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$P$8:$P$27</c:f>
+              <c:f>profile!$P$9:$P$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2010,7 +2133,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$Q$8:$Q$27</c:f>
+              <c:f>profile!$Q$9:$Q$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2070,7 +2193,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$S$8:$S$27</c:f>
+              <c:f>profile!$S$9:$S$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2079,7 +2202,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$T$8:$T$27</c:f>
+              <c:f>profile!$T$9:$T$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2139,7 +2262,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$V$8:$V$27</c:f>
+              <c:f>profile!$V$9:$V$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2148,7 +2271,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$W$8:$W$27</c:f>
+              <c:f>profile!$W$9:$W$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2208,7 +2331,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$Y$8:$Y$27</c:f>
+              <c:f>profile!$Y$9:$Y$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2217,7 +2340,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$Z$8:$Z$27</c:f>
+              <c:f>profile!$Z$9:$Z$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2277,7 +2400,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$AB$8:$AB$27</c:f>
+              <c:f>profile!$AB$9:$AB$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2286,7 +2409,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$AC$8:$AC$27</c:f>
+              <c:f>profile!$AC$9:$AC$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2346,7 +2469,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$AE$8:$AE$27</c:f>
+              <c:f>profile!$AE$9:$AE$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2355,7 +2478,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$AF$8:$AF$27</c:f>
+              <c:f>profile!$AF$9:$AF$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2415,7 +2538,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$AH$8:$AH$27</c:f>
+              <c:f>profile!$AH$9:$AH$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2424,7 +2547,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$AI$8:$AI$27</c:f>
+              <c:f>profile!$AI$9:$AI$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2484,7 +2607,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$AK$8:$AK$27</c:f>
+              <c:f>profile!$AK$9:$AK$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2493,7 +2616,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$AL$8:$AL$27</c:f>
+              <c:f>profile!$AL$9:$AL$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2556,7 +2679,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$AN$8:$AN$27</c:f>
+              <c:f>profile!$AN$9:$AN$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2565,7 +2688,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$AO$8:$AO$27</c:f>
+              <c:f>profile!$AO$9:$AO$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2628,7 +2751,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>profile!$AQ$8:$AQ$27</c:f>
+              <c:f>profile!$AQ$9:$AQ$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2637,7 +2760,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>profile!$AR$8:$AR$27</c:f>
+              <c:f>profile!$AR$9:$AR$28</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -2879,7 +3002,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>dloads!$B$4:$B$13</c:f>
+              <c:f>dloads!$B$5:$B$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -2888,7 +3011,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>dloads!$C$4:$C$13</c:f>
+              <c:f>dloads!$C$5:$C$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -2951,7 +3074,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>dloads!$F$4:$F$13</c:f>
+              <c:f>dloads!$F$5:$F$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -2960,7 +3083,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>dloads!$G$4:$G$13</c:f>
+              <c:f>dloads!$G$5:$G$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -3023,7 +3146,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>dloads!$J$4:$J$13</c:f>
+              <c:f>dloads!$J$5:$J$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -3032,7 +3155,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>dloads!$K$4:$K$13</c:f>
+              <c:f>dloads!$K$5:$K$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -3095,7 +3218,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>dloads!$N$4:$N$13</c:f>
+              <c:f>dloads!$N$5:$N$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -3104,7 +3227,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>dloads!$O$4:$O$13</c:f>
+              <c:f>dloads!$O$5:$O$14</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
@@ -3167,7 +3290,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>dloads!$R$4:$R$22</c:f>
+              <c:f>dloads!$R$5:$R$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3176,7 +3299,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>dloads!$S$4:$S$22</c:f>
+              <c:f>dloads!$S$5:$S$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3239,7 +3362,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>dloads!$V$4:$V$22</c:f>
+              <c:f>dloads!$V$5:$V$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3248,7 +3371,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>dloads!$W$4:$W$22</c:f>
+              <c:f>dloads!$W$5:$W$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3496,7 +3619,7 @@
           </c:dPt>
           <c:xVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$B$4:$B$22</c:f>
+              <c:f>'dloads (2)'!$B$5:$B$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3505,7 +3628,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$C$4:$C$22</c:f>
+              <c:f>'dloads (2)'!$C$5:$C$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3565,7 +3688,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$F$4:$F$22</c:f>
+              <c:f>'dloads (2)'!$F$5:$F$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3574,7 +3697,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$G$4:$G$22</c:f>
+              <c:f>'dloads (2)'!$G$5:$G$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3628,7 +3751,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$J$4:$J$22</c:f>
+              <c:f>'dloads (2)'!$J$5:$J$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3637,7 +3760,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$K$4:$K$22</c:f>
+              <c:f>'dloads (2)'!$K$5:$K$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3691,7 +3814,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$N$4:$N$22</c:f>
+              <c:f>'dloads (2)'!$N$5:$N$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3700,7 +3823,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$O$4:$O$22</c:f>
+              <c:f>'dloads (2)'!$O$5:$O$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3754,7 +3877,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$R$4:$R$22</c:f>
+              <c:f>'dloads (2)'!$R$5:$R$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3763,7 +3886,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$S$4:$S$22</c:f>
+              <c:f>'dloads (2)'!$S$5:$S$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3817,7 +3940,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$V$4:$V$22</c:f>
+              <c:f>'dloads (2)'!$V$5:$V$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -3826,7 +3949,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'dloads (2)'!$W$4:$W$22</c:f>
+              <c:f>'dloads (2)'!$W$5:$W$23</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
@@ -6241,7 +6364,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$A$8:$A$27</c:f>
+              <c:f>polygon!$A$10:$A$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6250,7 +6373,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$B$8:$B$27</c:f>
+              <c:f>polygon!$B$10:$B$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6310,7 +6433,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$D$8:$D$27</c:f>
+              <c:f>polygon!$D$10:$D$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6319,7 +6442,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$E$8:$E$27</c:f>
+              <c:f>polygon!$E$10:$E$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6379,7 +6502,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$G$8:$G$27</c:f>
+              <c:f>polygon!$G$10:$G$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6388,7 +6511,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$H$8:$H$27</c:f>
+              <c:f>polygon!$H$10:$H$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6448,7 +6571,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$J$8:$J$27</c:f>
+              <c:f>polygon!$J$10:$J$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6457,7 +6580,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$K$8:$K$27</c:f>
+              <c:f>polygon!$K$10:$K$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6520,7 +6643,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$M$8:$M$27</c:f>
+              <c:f>polygon!$M$10:$M$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6529,7 +6652,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$N$8:$N$27</c:f>
+              <c:f>polygon!$N$10:$N$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6592,7 +6715,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$P$8:$P$27</c:f>
+              <c:f>polygon!$P$10:$P$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6601,7 +6724,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$Q$8:$Q$27</c:f>
+              <c:f>polygon!$Q$10:$Q$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6664,7 +6787,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$S$8:$S$27</c:f>
+              <c:f>polygon!$S$10:$S$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6673,7 +6796,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$T$8:$T$27</c:f>
+              <c:f>polygon!$T$10:$T$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6736,7 +6859,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$V$8:$V$27</c:f>
+              <c:f>polygon!$V$10:$V$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6745,7 +6868,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$W$8:$W$27</c:f>
+              <c:f>polygon!$W$10:$W$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6808,7 +6931,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$Y$8:$Y$27</c:f>
+              <c:f>polygon!$Y$10:$Y$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6817,7 +6940,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$Z$8:$Z$27</c:f>
+              <c:f>polygon!$Z$10:$Z$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6880,7 +7003,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$AB$8:$AB$27</c:f>
+              <c:f>polygon!$AB$10:$AB$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6889,7 +7012,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$AC$8:$AC$27</c:f>
+              <c:f>polygon!$AC$10:$AC$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6949,7 +7072,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$AE$8:$AE$27</c:f>
+              <c:f>polygon!$AE$10:$AE$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -6958,7 +7081,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$AF$8:$AF$27</c:f>
+              <c:f>polygon!$AF$10:$AF$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -7018,7 +7141,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$AH$8:$AH$27</c:f>
+              <c:f>polygon!$AH$10:$AH$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -7027,7 +7150,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$AI$8:$AI$27</c:f>
+              <c:f>polygon!$AI$10:$AI$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -7087,7 +7210,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$AK$8:$AK$27</c:f>
+              <c:f>polygon!$AK$10:$AK$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -7096,7 +7219,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$AL$8:$AL$27</c:f>
+              <c:f>polygon!$AL$10:$AL$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -7156,7 +7279,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$AN$8:$AN$27</c:f>
+              <c:f>polygon!$AN$10:$AN$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -7165,7 +7288,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$AO$8:$AO$27</c:f>
+              <c:f>polygon!$AO$10:$AO$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -7225,7 +7348,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>polygon!$AQ$8:$AQ$27</c:f>
+              <c:f>polygon!$AQ$10:$AQ$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -7234,7 +7357,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>polygon!$AR$8:$AR$27</c:f>
+              <c:f>polygon!$AR$10:$AR$29</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="20"/>
@@ -8965,7 +9088,7 @@
         <v>13</v>
       </c>
       <c r="D5" s="30">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -9164,6 +9287,10 @@
       <c r="D21"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="C22" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="D22" s="1"/>
       <c r="F22" s="1" t="s">
         <v>62</v>
       </c>
@@ -9311,20 +9438,23 @@
   <mergeCells count="1">
     <mergeCell ref="B7:D7"/>
   </mergeCells>
-  <dataValidations count="5">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D8" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D22" xr:uid="{4E2B12C7-FE67-3B4F-885D-33F99F4A0D82}">
+      <formula1>"rollers,fixed"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D8" xr:uid="{0D3EDF25-93C5-C944-8126-8CC9B17A21FC}">
       <formula1>$D$50:$D$51</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D9" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D9" xr:uid="{4694A1A0-8B80-B646-8FBE-EF2E498B980D}">
       <formula1>$D$54:$D$57</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D17" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D17" xr:uid="{0356D3C6-ECF7-2D4C-8DB0-E3BFC9D663DB}">
       <formula1>$D$60:$D$61</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D14" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D14" xr:uid="{BDB1B4FF-9C3D-5F43-BB1B-429406E4C3E1}">
       <formula1>$D$64:$D$71</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D18" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D18" xr:uid="{8A75E61B-C3DC-0F4A-869A-1DA1855E5B34}">
       <formula1>$D$74:$D$78</formula1>
     </dataValidation>
   </dataValidations>
@@ -9334,7 +9464,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="B2:X22"/>
+  <dimension ref="B2:X23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -9384,80 +9514,92 @@
       <c r="X2" s="62"/>
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="C3" s="58"/>
+      <c r="D3" s="39"/>
+      <c r="F3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="G3" s="58"/>
+      <c r="H3" s="39"/>
+      <c r="J3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="K3" s="58"/>
+      <c r="L3" s="39"/>
+      <c r="N3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="O3" s="58"/>
+      <c r="P3" s="39"/>
+      <c r="R3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="S3" s="58"/>
+      <c r="T3" s="39"/>
+      <c r="V3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="W3" s="58"/>
+      <c r="X3" s="39"/>
+    </row>
+    <row r="4" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="R4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="T4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="V3" s="2" t="s">
+      <c r="V4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="W4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="X3" s="2" t="s">
+      <c r="X4" s="2" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="4" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-      <c r="V4" s="3"/>
-      <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B5" s="3"/>
@@ -9819,15 +9961,46 @@
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
     </row>
+    <row r="23" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="R23" s="3"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="3"/>
+      <c r="V23" s="3"/>
+      <c r="W23" s="3"/>
+      <c r="X23" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="12">
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="V2:X2"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="R2:T2"/>
     <mergeCell ref="F2:H2"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="R3:S3"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3 H3 L3 P3 T3 X3" xr:uid="{00000000-0002-0000-0900-000000000000}">
+      <formula1>"normal,vertical"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -14812,84 +14985,84 @@
     <mergeCell ref="AG9:AP9"/>
   </mergeCells>
   <conditionalFormatting sqref="F11:K52 AB11:AF52">
-    <cfRule type="expression" dxfId="19" priority="6">
+    <cfRule type="expression" dxfId="34" priority="6">
       <formula>$E11="hb"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="18" priority="7">
+    <cfRule type="expression" dxfId="33" priority="7">
       <formula>$E11="pow"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11:L52 O11:R52">
-    <cfRule type="expression" dxfId="17" priority="19">
+    <cfRule type="expression" dxfId="32" priority="19">
       <formula>$E11="elastic"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G11:G52">
-    <cfRule type="expression" dxfId="16" priority="8">
+    <cfRule type="expression" dxfId="31" priority="8">
       <formula>$E11="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H11:I52">
-    <cfRule type="expression" dxfId="15" priority="9">
+    <cfRule type="expression" dxfId="30" priority="9">
       <formula>$E11="mc"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J11:K52">
-    <cfRule type="expression" dxfId="14" priority="10">
+    <cfRule type="expression" dxfId="29" priority="10">
       <formula>$E11="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P11:P52">
-    <cfRule type="expression" dxfId="13" priority="13">
+    <cfRule type="expression" dxfId="28" priority="13">
       <formula>AND($O11&lt;&gt;"",$O11&lt;&gt;"ru")</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="Q11:R52">
+    <cfRule type="expression" dxfId="27" priority="23">
+      <formula>$E11="cp"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="24">
+      <formula>AND($O11&lt;&gt;"",$O11&lt;&gt;"piezo",$O11&lt;&gt;"seep")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="S11:V52">
-    <cfRule type="expression" dxfId="12" priority="11">
+    <cfRule type="expression" dxfId="25" priority="11">
       <formula>AND($E11&lt;&gt;"",$E11&lt;&gt;"pow")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W11:Z52">
-    <cfRule type="expression" dxfId="11" priority="12">
+    <cfRule type="expression" dxfId="24" priority="12">
       <formula>AND($E11&lt;&gt;"",$E11&lt;&gt;"hb")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB11:AF52">
-    <cfRule type="expression" dxfId="10" priority="21">
+    <cfRule type="expression" dxfId="23" priority="21">
       <formula>$E11="elastic"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AC11:AC52">
-    <cfRule type="expression" dxfId="9" priority="14">
+    <cfRule type="expression" dxfId="22" priority="14">
       <formula>$E11="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD11:AD52">
-    <cfRule type="expression" dxfId="8" priority="15">
+    <cfRule type="expression" dxfId="21" priority="15">
       <formula>$E11="mc"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AE11:AF52">
-    <cfRule type="expression" dxfId="7" priority="16">
+    <cfRule type="expression" dxfId="20" priority="16">
       <formula>$E11="cp"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK11:AL52">
-    <cfRule type="expression" dxfId="6" priority="17">
+    <cfRule type="expression" dxfId="19" priority="17">
       <formula>OR($AJ11="vg",$AJ11="gard")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AM11:AN52">
-    <cfRule type="expression" dxfId="5" priority="1">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>$AJ11="lf"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Q11:R52">
-    <cfRule type="expression" dxfId="1" priority="23">
-      <formula>$E11="cp"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="24">
-      <formula>AND($O11&lt;&gt;"",$O11&lt;&gt;"piezo",$O11&lt;&gt;"seep")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
@@ -14909,7 +15082,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A2:AR27"/>
+  <dimension ref="A2:AR28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="10.83203125" style="1" customWidth="1"/>
@@ -14943,6 +15116,9 @@
       <c r="D2" s="24" t="s">
         <v>160</v>
       </c>
+      <c r="N2" s="24" t="s">
+        <v>309</v>
+      </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A4" s="55" t="s">
@@ -15200,144 +15376,174 @@
       <c r="AR6" s="57"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="B7" s="37"/>
+      <c r="D7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="E7" s="37"/>
+      <c r="G7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="H7" s="37"/>
+      <c r="J7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="K7" s="37"/>
+      <c r="M7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="N7" s="37"/>
+      <c r="P7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q7" s="37"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="T7" s="37"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="W7" s="37"/>
+      <c r="X7" s="1"/>
+      <c r="Y7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="Z7" s="37"/>
+      <c r="AA7" s="1"/>
+      <c r="AB7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="AC7" s="37"/>
+      <c r="AE7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="AF7" s="37"/>
+      <c r="AG7" s="1"/>
+      <c r="AH7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="AI7" s="37"/>
+      <c r="AJ7" s="1"/>
+      <c r="AK7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="AL7" s="37"/>
+      <c r="AM7" s="1"/>
+      <c r="AN7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="AO7" s="37"/>
+      <c r="AP7" s="1"/>
+      <c r="AQ7" s="36" t="s">
+        <v>303</v>
+      </c>
+      <c r="AR7" s="37"/>
+    </row>
+    <row r="8" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="N8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="P8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="Q8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="R7" s="1"/>
-      <c r="S7" s="2" t="s">
+      <c r="R8" s="1"/>
+      <c r="S8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="T8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="U7" s="1"/>
-      <c r="V7" s="2" t="s">
+      <c r="U8" s="1"/>
+      <c r="V8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="W7" s="2" t="s">
+      <c r="W8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="X7" s="1"/>
-      <c r="Y7" s="2" t="s">
+      <c r="X8" s="1"/>
+      <c r="Y8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="Z7" s="2" t="s">
+      <c r="Z8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AA7" s="1"/>
-      <c r="AB7" s="2" t="s">
+      <c r="AA8" s="1"/>
+      <c r="AB8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AC7" s="2" t="s">
+      <c r="AC8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AE7" s="2" t="s">
+      <c r="AE8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AF7" s="2" t="s">
+      <c r="AF8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AG7" s="1"/>
-      <c r="AH7" s="2" t="s">
+      <c r="AG8" s="1"/>
+      <c r="AH8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AI7" s="2" t="s">
+      <c r="AI8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AJ7" s="1"/>
-      <c r="AK7" s="2" t="s">
+      <c r="AJ8" s="1"/>
+      <c r="AK8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AL7" s="2" t="s">
+      <c r="AL8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AM7" s="1"/>
-      <c r="AN7" s="2" t="s">
+      <c r="AM8" s="1"/>
+      <c r="AN8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AO7" s="2" t="s">
+      <c r="AO8" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AP7" s="1"/>
-      <c r="AQ7" s="2" t="s">
+      <c r="AP8" s="1"/>
+      <c r="AQ8" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AR7" s="2" t="s">
+      <c r="AR8" s="2" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="J8" s="3"/>
-      <c r="K8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="N8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="16"/>
-      <c r="T8" s="17"/>
-      <c r="U8" s="1"/>
-      <c r="V8" s="16"/>
-      <c r="W8" s="17"/>
-      <c r="X8" s="1"/>
-      <c r="Y8" s="16"/>
-      <c r="Z8" s="17"/>
-      <c r="AA8" s="1"/>
-      <c r="AB8" s="16"/>
-      <c r="AC8" s="17"/>
-      <c r="AE8" s="3"/>
-      <c r="AF8" s="3"/>
-      <c r="AG8" s="1"/>
-      <c r="AH8" s="16"/>
-      <c r="AI8" s="17"/>
-      <c r="AJ8" s="1"/>
-      <c r="AK8" s="16"/>
-      <c r="AL8" s="17"/>
-      <c r="AM8" s="1"/>
-      <c r="AN8" s="16"/>
-      <c r="AO8" s="17"/>
-      <c r="AP8" s="1"/>
-      <c r="AQ8" s="16"/>
-      <c r="AR8" s="17"/>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A9" s="3"/>
@@ -15353,31 +15559,31 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="1"/>
-      <c r="S9" s="18"/>
-      <c r="T9" s="19"/>
+      <c r="S9" s="16"/>
+      <c r="T9" s="17"/>
       <c r="U9" s="1"/>
-      <c r="V9" s="18"/>
-      <c r="W9" s="19"/>
+      <c r="V9" s="16"/>
+      <c r="W9" s="17"/>
       <c r="X9" s="1"/>
-      <c r="Y9" s="18"/>
-      <c r="Z9" s="19"/>
+      <c r="Y9" s="16"/>
+      <c r="Z9" s="17"/>
       <c r="AA9" s="1"/>
-      <c r="AB9" s="18"/>
-      <c r="AC9" s="19"/>
+      <c r="AB9" s="16"/>
+      <c r="AC9" s="17"/>
       <c r="AE9" s="3"/>
       <c r="AF9" s="3"/>
       <c r="AG9" s="1"/>
-      <c r="AH9" s="18"/>
-      <c r="AI9" s="19"/>
+      <c r="AH9" s="16"/>
+      <c r="AI9" s="17"/>
       <c r="AJ9" s="1"/>
-      <c r="AK9" s="18"/>
-      <c r="AL9" s="19"/>
+      <c r="AK9" s="16"/>
+      <c r="AL9" s="17"/>
       <c r="AM9" s="1"/>
-      <c r="AN9" s="18"/>
-      <c r="AO9" s="19"/>
+      <c r="AN9" s="16"/>
+      <c r="AO9" s="17"/>
       <c r="AP9" s="1"/>
-      <c r="AQ9" s="18"/>
-      <c r="AR9" s="19"/>
+      <c r="AQ9" s="16"/>
+      <c r="AR9" s="17"/>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A10" s="3"/>
@@ -15436,8 +15642,8 @@
       <c r="S11" s="18"/>
       <c r="T11" s="19"/>
       <c r="U11" s="1"/>
-      <c r="V11" s="16"/>
-      <c r="W11" s="17"/>
+      <c r="V11" s="18"/>
+      <c r="W11" s="19"/>
       <c r="X11" s="1"/>
       <c r="Y11" s="18"/>
       <c r="Z11" s="19"/>
@@ -15473,31 +15679,31 @@
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="1"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
+      <c r="S12" s="18"/>
+      <c r="T12" s="19"/>
       <c r="U12" s="1"/>
-      <c r="V12" s="3"/>
-      <c r="W12" s="3"/>
+      <c r="V12" s="16"/>
+      <c r="W12" s="17"/>
       <c r="X12" s="1"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="3"/>
+      <c r="Y12" s="18"/>
+      <c r="Z12" s="19"/>
       <c r="AA12" s="1"/>
-      <c r="AB12" s="3"/>
-      <c r="AC12" s="3"/>
+      <c r="AB12" s="18"/>
+      <c r="AC12" s="19"/>
       <c r="AE12" s="3"/>
       <c r="AF12" s="3"/>
       <c r="AG12" s="1"/>
-      <c r="AH12" s="3"/>
-      <c r="AI12" s="3"/>
+      <c r="AH12" s="18"/>
+      <c r="AI12" s="19"/>
       <c r="AJ12" s="1"/>
-      <c r="AK12" s="3"/>
-      <c r="AL12" s="3"/>
+      <c r="AK12" s="18"/>
+      <c r="AL12" s="19"/>
       <c r="AM12" s="1"/>
-      <c r="AN12" s="3"/>
-      <c r="AO12" s="3"/>
+      <c r="AN12" s="18"/>
+      <c r="AO12" s="19"/>
       <c r="AP12" s="1"/>
-      <c r="AQ12" s="3"/>
-      <c r="AR12" s="3"/>
+      <c r="AQ12" s="18"/>
+      <c r="AR12" s="19"/>
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A13" s="3"/>
@@ -16099,6 +16305,46 @@
       <c r="AQ27" s="3"/>
       <c r="AR27" s="3"/>
     </row>
+    <row r="28" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="3"/>
+      <c r="T28" s="3"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="3"/>
+      <c r="W28" s="3"/>
+      <c r="X28" s="1"/>
+      <c r="Y28" s="3"/>
+      <c r="Z28" s="3"/>
+      <c r="AA28" s="1"/>
+      <c r="AB28" s="3"/>
+      <c r="AC28" s="3"/>
+      <c r="AE28" s="3"/>
+      <c r="AF28" s="3"/>
+      <c r="AG28" s="1"/>
+      <c r="AH28" s="3"/>
+      <c r="AI28" s="3"/>
+      <c r="AJ28" s="1"/>
+      <c r="AK28" s="3"/>
+      <c r="AL28" s="3"/>
+      <c r="AM28" s="1"/>
+      <c r="AN28" s="3"/>
+      <c r="AO28" s="3"/>
+      <c r="AP28" s="1"/>
+      <c r="AQ28" s="3"/>
+      <c r="AR28" s="3"/>
+    </row>
   </sheetData>
   <mergeCells count="30">
     <mergeCell ref="D4:E4"/>
@@ -16138,7 +16384,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A2:AR27"/>
+  <dimension ref="A2:AR29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="10.83203125" style="1" customWidth="1"/>
@@ -16167,7 +16413,7 @@
         <v>179</v>
       </c>
       <c r="G2" s="9" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
@@ -16215,8 +16461,10 @@
       </c>
       <c r="T4" s="54"/>
       <c r="U4" s="1"/>
-      <c r="V4" s="55" t="s">
-        <v>187</v>
+      <c r="V4" s="55" t="inlineStr">
+        <is>
+          <t>Polygon #8</t>
+        </is>
       </c>
       <c r="W4" s="54"/>
       <c r="X4" s="1"/>
@@ -16256,479 +16504,528 @@
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="B5" s="39">
-        <v>1</v>
+        <v>198</v>
+      </c>
+      <c r="B5" s="39" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
       </c>
       <c r="D5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="E5" s="39">
-        <v>3</v>
+        <v>198</v>
+      </c>
+      <c r="E5" s="39" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
       </c>
       <c r="G5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="H5" s="39">
-        <v>2</v>
+        <v>198</v>
+      </c>
+      <c r="H5" s="39" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
       </c>
       <c r="J5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="K5" s="39">
-        <v>3</v>
+        <v>198</v>
+      </c>
+      <c r="K5" s="39" t="inlineStr">
+        <is>
+          <t>material</t>
+        </is>
       </c>
       <c r="M5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="N5" s="39">
-        <v>-1</v>
+        <v>198</v>
+      </c>
+      <c r="N5" s="39" t="inlineStr">
+        <is>
+          <t>ssr reduce</t>
+        </is>
       </c>
       <c r="P5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="Q5" s="39">
-        <v>-2</v>
+        <v>198</v>
+      </c>
+      <c r="Q5" s="39" t="inlineStr">
+        <is>
+          <t>ssr hold</t>
+        </is>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="T5" s="39">
-        <v>-3</v>
+        <v>198</v>
+      </c>
+      <c r="T5" s="39" t="inlineStr">
+        <is>
+          <t>ssr elastic</t>
+        </is>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="W5" s="39">
-        <v>8</v>
+        <v>198</v>
+      </c>
+      <c r="W5" s="39" t="inlineStr">
+        <is>
+          <t>refine</t>
+        </is>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="Z5" s="39">
-        <v>9</v>
+        <v>198</v>
+      </c>
+      <c r="Z5" s="39" t="s">
+        <v>305</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="AC5" s="39">
-        <v>10</v>
+        <v>198</v>
+      </c>
+      <c r="AC5" s="39" t="s">
+        <v>305</v>
       </c>
       <c r="AE5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="AF5" s="39">
-        <v>11</v>
+        <v>198</v>
+      </c>
+      <c r="AF5" s="39" t="s">
+        <v>305</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="AI5" s="39">
-        <v>12</v>
+        <v>198</v>
+      </c>
+      <c r="AI5" s="39" t="s">
+        <v>305</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="AL5" s="39">
-        <v>13</v>
+        <v>198</v>
+      </c>
+      <c r="AL5" s="39" t="s">
+        <v>305</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="38" t="s">
-        <v>176</v>
-      </c>
-      <c r="AO5" s="39">
-        <v>14</v>
+        <v>198</v>
+      </c>
+      <c r="AO5" s="39" t="s">
+        <v>305</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="AR5" s="39" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="6" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A6" s="38" t="s">
         <v>176</v>
       </c>
-      <c r="AR5" s="39">
+      <c r="B6" s="39">
+        <v>1</v>
+      </c>
+      <c r="D6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="E6" s="39">
+        <v>3</v>
+      </c>
+      <c r="G6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="H6" s="39">
+        <v>2</v>
+      </c>
+      <c r="J6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="K6" s="39">
+        <v>3</v>
+      </c>
+      <c r="M6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="N6" s="39"/>
+      <c r="P6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q6" s="39"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="T6" s="39"/>
+      <c r="U6" s="1"/>
+      <c r="V6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="W6" s="39"/>
+      <c r="X6" s="1"/>
+      <c r="Y6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="Z6" s="39">
+        <v>9</v>
+      </c>
+      <c r="AA6" s="1"/>
+      <c r="AB6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="AC6" s="39">
+        <v>10</v>
+      </c>
+      <c r="AE6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="AF6" s="39">
+        <v>11</v>
+      </c>
+      <c r="AG6" s="1"/>
+      <c r="AH6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="AI6" s="39">
+        <v>12</v>
+      </c>
+      <c r="AJ6" s="1"/>
+      <c r="AK6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="AL6" s="39">
+        <v>13</v>
+      </c>
+      <c r="AM6" s="1"/>
+      <c r="AN6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="AO6" s="39">
+        <v>14</v>
+      </c>
+      <c r="AP6" s="1"/>
+      <c r="AQ6" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="AR6" s="39">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A6" s="58" t="inlineStr">
+    <row r="7" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A7" s="58" t="inlineStr">
         <is>
           <t>levee</t>
         </is>
       </c>
-      <c r="B6" s="57"/>
-      <c r="D6" s="58" t="inlineStr">
+      <c r="B7" s="57"/>
+      <c r="D7" s="58" t="inlineStr">
         <is>
           <t>foundation</t>
         </is>
       </c>
-      <c r="E6" s="57"/>
-      <c r="G6" s="58" t="inlineStr">
+      <c r="E7" s="57"/>
+      <c r="G7" s="58" t="inlineStr">
         <is>
           <t>grout</t>
         </is>
       </c>
-      <c r="H6" s="57"/>
-      <c r="J6" s="58" t="inlineStr">
+      <c r="H7" s="57"/>
+      <c r="J7" s="58" t="inlineStr">
         <is>
           <t>foundation</t>
         </is>
       </c>
-      <c r="K6" s="57"/>
-      <c r="M6" s="58" t="inlineStr">
-        <is>
-          <t>SSR reduce</t>
-        </is>
-      </c>
-      <c r="N6" s="57"/>
-      <c r="P6" s="58" t="inlineStr">
-        <is>
-          <t>SSR hold</t>
-        </is>
-      </c>
-      <c r="Q6" s="57"/>
-      <c r="R6" s="1"/>
-      <c r="S6" s="58" t="inlineStr">
-        <is>
-          <t>SSR elastic</t>
-        </is>
-      </c>
-      <c r="T6" s="57"/>
-      <c r="U6" s="1"/>
-      <c r="V6" s="58" t="str">
-        <f>IF(W5=-1,"SSR reduce",IF(W5=-2,"SSR hold",IF(W5=-3,"SSR elastic",_xlfn.XLOOKUP(W5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
+      <c r="K7" s="57"/>
+      <c r="M7" s="58" t="str">
+        <f>IF(OR(N5="",N5="material"),_xlfn.XLOOKUP(N6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
         <v/>
       </c>
-      <c r="W6" s="57"/>
-      <c r="X6" s="1"/>
-      <c r="Y6" s="58" t="str">
-        <f>IF(Z5=-1,"SSR reduce",IF(Z5=-2,"SSR hold",IF(Z5=-3,"SSR elastic",_xlfn.XLOOKUP(Z5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
+      <c r="N7" s="57"/>
+      <c r="P7" s="58" t="str">
+        <f>IF(OR(Q5="",Q5="material"),_xlfn.XLOOKUP(Q6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
         <v/>
       </c>
-      <c r="Z6" s="57"/>
-      <c r="AA6" s="1"/>
-      <c r="AB6" s="58" t="str">
-        <f>IF(AC5=-1,"SSR reduce",IF(AC5=-2,"SSR hold",IF(AC5=-3,"SSR elastic",_xlfn.XLOOKUP(AC5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
+      <c r="Q7" s="57"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="58" t="str">
+        <f>IF(OR(T5="",T5="material"),_xlfn.XLOOKUP(T6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
         <v/>
       </c>
-      <c r="AC6" s="57"/>
-      <c r="AE6" s="58" t="str">
-        <f>IF(AF5=-1,"SSR reduce",IF(AF5=-2,"SSR hold",IF(AF5=-3,"SSR elastic",_xlfn.XLOOKUP(AF5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
+      <c r="T7" s="57"/>
+      <c r="U7" s="1"/>
+      <c r="V7" s="58" t="str">
+        <f>IF(OR(W5="",W5="material"),_xlfn.XLOOKUP(W6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
         <v/>
       </c>
-      <c r="AF6" s="57"/>
-      <c r="AG6" s="1"/>
-      <c r="AH6" s="58" t="str">
-        <f>IF(AI5=-1,"SSR reduce",IF(AI5=-2,"SSR hold",IF(AI5=-3,"SSR elastic",_xlfn.XLOOKUP(AI5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
+      <c r="W7" s="57"/>
+      <c r="X7" s="1"/>
+      <c r="Y7" s="58" t="str">
+        <f>IF(OR(Z5="",Z5="material"),_xlfn.XLOOKUP(Z6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
         <v/>
       </c>
-      <c r="AI6" s="57"/>
-      <c r="AJ6" s="1"/>
-      <c r="AK6" s="58" t="str">
-        <f>IF(AL5=-1,"SSR reduce",IF(AL5=-2,"SSR hold",IF(AL5=-3,"SSR elastic",_xlfn.XLOOKUP(AL5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
+      <c r="Z7" s="57"/>
+      <c r="AA7" s="1"/>
+      <c r="AB7" s="58" t="str">
+        <f>IF(OR(AC5="",AC5="material"),_xlfn.XLOOKUP(AC6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
         <v/>
       </c>
-      <c r="AL6" s="57"/>
-      <c r="AM6" s="1"/>
-      <c r="AN6" s="58" t="str">
-        <f>IF(AO5=-1,"SSR reduce",IF(AO5=-2,"SSR hold",IF(AO5=-3,"SSR elastic",_xlfn.XLOOKUP(AO5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
+      <c r="AC7" s="57"/>
+      <c r="AE7" s="58" t="str">
+        <f>IF(OR(AF5="",AF5="material"),_xlfn.XLOOKUP(AF6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
         <v/>
       </c>
-      <c r="AO6" s="57"/>
-      <c r="AP6" s="1"/>
-      <c r="AQ6" s="58" t="str">
-        <f>IF(AR5=-1,"SSR reduce",IF(AR5=-2,"SSR hold",IF(AR5=-3,"SSR elastic",_xlfn.XLOOKUP(AR5,mat!$A:$A, mat!$B:$B,"") &amp; "")))</f>
+      <c r="AF7" s="57"/>
+      <c r="AG7" s="1"/>
+      <c r="AH7" s="58" t="str">
+        <f>IF(OR(AI5="",AI5="material"),_xlfn.XLOOKUP(AI6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
         <v/>
       </c>
-      <c r="AR6" s="57"/>
-    </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+      <c r="AI7" s="57"/>
+      <c r="AJ7" s="1"/>
+      <c r="AK7" s="58" t="str">
+        <f>IF(OR(AL5="",AL5="material"),_xlfn.XLOOKUP(AL6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
+        <v/>
+      </c>
+      <c r="AL7" s="57"/>
+      <c r="AM7" s="1"/>
+      <c r="AN7" s="58" t="str">
+        <f>IF(OR(AO5="",AO5="material"),_xlfn.XLOOKUP(AO6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
+        <v/>
+      </c>
+      <c r="AO7" s="57"/>
+      <c r="AP7" s="1"/>
+      <c r="AQ7" s="58" t="str">
+        <f>IF(OR(AR5="",AR5="material"),_xlfn.XLOOKUP(AR6,mat!$A:$A, mat!$B:$B,"") &amp; "","")</f>
+        <v/>
+      </c>
+      <c r="AR7" s="57"/>
+    </row>
+    <row r="8" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="B8" s="39">
+        <v>1.5</v>
+      </c>
+      <c r="D8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="E8" s="39"/>
+      <c r="G8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="H8" s="39"/>
+      <c r="J8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="K8" s="39"/>
+      <c r="M8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="N8" s="39">
+        <v>0.75</v>
+      </c>
+      <c r="P8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q8" s="39"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="T8" s="39"/>
+      <c r="U8" s="1"/>
+      <c r="V8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="W8" s="39">
+        <v>0.5</v>
+      </c>
+      <c r="X8" s="1"/>
+      <c r="Y8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="Z8" s="39"/>
+      <c r="AA8" s="1"/>
+      <c r="AB8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="AC8" s="39"/>
+      <c r="AE8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="AF8" s="39"/>
+      <c r="AG8" s="1"/>
+      <c r="AH8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="AI8" s="39"/>
+      <c r="AJ8" s="1"/>
+      <c r="AK8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="AL8" s="39"/>
+      <c r="AM8" s="1"/>
+      <c r="AN8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="AO8" s="39"/>
+      <c r="AP8" s="1"/>
+      <c r="AQ8" s="38" t="s">
+        <v>303</v>
+      </c>
+      <c r="AR8" s="39"/>
+    </row>
+    <row r="9" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B9" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="H9" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="K7" s="2" t="s">
+      <c r="K9" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="M9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="N9" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="P9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="Q9" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="R7" s="1"/>
-      <c r="S7" s="2" t="s">
+      <c r="R9" s="1"/>
+      <c r="S9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="T9" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="U7" s="1"/>
-      <c r="V7" s="2" t="s">
+      <c r="U9" s="1"/>
+      <c r="V9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="W7" s="2" t="s">
+      <c r="W9" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="X7" s="1"/>
-      <c r="Y7" s="2" t="s">
+      <c r="X9" s="1"/>
+      <c r="Y9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="Z7" s="2" t="s">
+      <c r="Z9" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AA7" s="1"/>
-      <c r="AB7" s="2" t="s">
+      <c r="AA9" s="1"/>
+      <c r="AB9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AC7" s="2" t="s">
+      <c r="AC9" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AE7" s="2" t="s">
+      <c r="AE9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AF7" s="2" t="s">
+      <c r="AF9" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AG7" s="1"/>
-      <c r="AH7" s="2" t="s">
+      <c r="AG9" s="1"/>
+      <c r="AH9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AI7" s="2" t="s">
+      <c r="AI9" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AJ7" s="1"/>
-      <c r="AK7" s="2" t="s">
+      <c r="AJ9" s="1"/>
+      <c r="AK9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AL7" s="2" t="s">
+      <c r="AL9" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AM7" s="1"/>
-      <c r="AN7" s="2" t="s">
+      <c r="AM9" s="1"/>
+      <c r="AN9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AO7" s="2" t="s">
+      <c r="AO9" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="AP7" s="1"/>
-      <c r="AQ7" s="2" t="s">
+      <c r="AP9" s="1"/>
+      <c r="AQ9" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="AR7" s="2" t="s">
+      <c r="AR9" s="2" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="B8" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="D8" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="E8" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>26.0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>32.0</v>
-      </c>
-      <c r="K8" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="M8" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="N8" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="P8" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="R8" s="1"/>
-      <c r="S8" s="3">
-        <v>110.0</v>
-      </c>
-      <c r="T8" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="U8" s="1"/>
-      <c r="V8" s="3"/>
-      <c r="W8" s="3"/>
-      <c r="X8" s="1"/>
-      <c r="Y8" s="3"/>
-      <c r="Z8" s="3"/>
-      <c r="AA8" s="1"/>
-      <c r="AB8" s="3"/>
-      <c r="AC8" s="3"/>
-      <c r="AE8" s="3"/>
-      <c r="AF8" s="3"/>
-      <c r="AG8" s="1"/>
-      <c r="AH8" s="3"/>
-      <c r="AI8" s="3"/>
-      <c r="AJ8" s="1"/>
-      <c r="AK8" s="3"/>
-      <c r="AL8" s="3"/>
-      <c r="AM8" s="1"/>
-      <c r="AN8" s="3"/>
-      <c r="AO8" s="3"/>
-      <c r="AP8" s="1"/>
-      <c r="AQ8" s="3"/>
-      <c r="AR8" s="3"/>
-    </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A9" s="3">
-        <v>26.4</v>
-      </c>
-      <c r="B9" s="3">
-        <v>14.0</v>
-      </c>
-      <c r="D9" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="E9" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="G9" s="3">
-        <v>32.0</v>
-      </c>
-      <c r="H9" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="J9" s="3">
-        <v>38.0</v>
-      </c>
-      <c r="K9" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="M9" s="3">
-        <v>110.0</v>
-      </c>
-      <c r="N9" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="P9" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="Q9" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="R9" s="1"/>
-      <c r="S9" s="3">
-        <v>140.0</v>
-      </c>
-      <c r="T9" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="U9" s="1"/>
-      <c r="V9" s="3"/>
-      <c r="W9" s="3"/>
-      <c r="X9" s="1"/>
-      <c r="Y9" s="3"/>
-      <c r="Z9" s="3"/>
-      <c r="AA9" s="1"/>
-      <c r="AB9" s="3"/>
-      <c r="AC9" s="3"/>
-      <c r="AE9" s="3"/>
-      <c r="AF9" s="3"/>
-      <c r="AG9" s="1"/>
-      <c r="AH9" s="3"/>
-      <c r="AI9" s="3"/>
-      <c r="AJ9" s="1"/>
-      <c r="AK9" s="3"/>
-      <c r="AL9" s="3"/>
-      <c r="AM9" s="1"/>
-      <c r="AN9" s="3"/>
-      <c r="AO9" s="3"/>
-      <c r="AP9" s="1"/>
-      <c r="AQ9" s="3"/>
-      <c r="AR9" s="3"/>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
-        <v>27.2</v>
+        <v>20.0</v>
       </c>
       <c r="B10" s="3">
-        <v>14.5</v>
+        <v>10.0</v>
       </c>
       <c r="D10" s="3">
-        <v>26.0</v>
+        <v>0.0</v>
       </c>
       <c r="E10" s="3">
         <v>10.0</v>
       </c>
       <c r="G10" s="3">
+        <v>26.0</v>
+      </c>
+      <c r="H10" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="J10" s="3">
         <v>32.0</v>
-      </c>
-      <c r="H10" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="J10" s="3">
-        <v>58.0</v>
       </c>
       <c r="K10" s="3">
         <v>10.0</v>
       </c>
       <c r="M10" s="3">
-        <v>110.0</v>
+        <v>30.0</v>
       </c>
       <c r="N10" s="3">
-        <v>30.0</v>
+        <v>0.0</v>
       </c>
       <c r="P10" s="3">
-        <v>30.0</v>
+        <v>0.0</v>
       </c>
       <c r="Q10" s="3">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="R10" s="1"/>
       <c r="S10" s="3">
-        <v>140.0</v>
+        <v>110.0</v>
       </c>
       <c r="T10" s="3">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="U10" s="1"/>
-      <c r="V10" s="3"/>
-      <c r="W10" s="3"/>
+      <c r="V10" s="3">
+        <v>96.0</v>
+      </c>
+      <c r="W10" s="3">
+        <v>8.0</v>
+      </c>
       <c r="X10" s="1"/>
       <c r="Y10" s="3"/>
       <c r="Z10" s="3"/>
@@ -16752,51 +17049,55 @@
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
-        <v>30.8</v>
+        <v>26.4</v>
       </c>
       <c r="B11" s="3">
-        <v>14.5</v>
+        <v>14.0</v>
       </c>
       <c r="D11" s="3">
-        <v>26.0</v>
+        <v>20.0</v>
       </c>
       <c r="E11" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="G11" s="3">
+        <v>32.0</v>
+      </c>
+      <c r="H11" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="J11" s="3">
+        <v>38.0</v>
+      </c>
+      <c r="K11" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="M11" s="3">
+        <v>110.0</v>
+      </c>
+      <c r="N11" s="3">
         <v>0.0</v>
       </c>
-      <c r="G11" s="3">
-        <v>26.0</v>
-      </c>
-      <c r="H11" s="3">
+      <c r="P11" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="Q11" s="3">
         <v>0.0</v>
-      </c>
-      <c r="J11" s="3">
-        <v>58.0</v>
-      </c>
-      <c r="K11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="M11" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="N11" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="P11" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="Q11" s="3">
-        <v>12.0</v>
       </c>
       <c r="R11" s="1"/>
       <c r="S11" s="3">
-        <v>110.0</v>
+        <v>140.0</v>
       </c>
       <c r="T11" s="3">
-        <v>12.0</v>
+        <v>0.0</v>
       </c>
       <c r="U11" s="1"/>
-      <c r="V11" s="3"/>
-      <c r="W11" s="3"/>
+      <c r="V11" s="3">
+        <v>120.0</v>
+      </c>
+      <c r="W11" s="3">
+        <v>8.0</v>
+      </c>
       <c r="X11" s="1"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
@@ -16820,35 +17121,55 @@
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
-        <v>38.0</v>
+        <v>27.2</v>
       </c>
       <c r="B12" s="3">
+        <v>14.5</v>
+      </c>
+      <c r="D12" s="3">
+        <v>26.0</v>
+      </c>
+      <c r="E12" s="3">
         <v>10.0</v>
       </c>
-      <c r="D12" s="3">
+      <c r="G12" s="3">
+        <v>32.0</v>
+      </c>
+      <c r="H12" s="3">
         <v>0.0</v>
       </c>
-      <c r="E12" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
       <c r="J12" s="3">
-        <v>32.0</v>
+        <v>58.0</v>
       </c>
       <c r="K12" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="M12" s="3"/>
-      <c r="N12" s="3"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="M12" s="3">
+        <v>110.0</v>
+      </c>
+      <c r="N12" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="P12" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>12.0</v>
+      </c>
       <c r="R12" s="1"/>
-      <c r="S12" s="3"/>
-      <c r="T12" s="3"/>
+      <c r="S12" s="3">
+        <v>140.0</v>
+      </c>
+      <c r="T12" s="3">
+        <v>12.0</v>
+      </c>
       <c r="U12" s="1"/>
-      <c r="V12" s="3"/>
-      <c r="W12" s="3"/>
+      <c r="V12" s="3">
+        <v>120.0</v>
+      </c>
+      <c r="W12" s="3">
+        <v>20.0</v>
+      </c>
       <c r="X12" s="1"/>
       <c r="Y12" s="3"/>
       <c r="Z12" s="3"/>
@@ -16872,27 +17193,55 @@
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
-        <v>32.0</v>
+        <v>30.8</v>
       </c>
       <c r="B13" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
+        <v>14.5</v>
+      </c>
+      <c r="D13" s="3">
+        <v>26.0</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G13" s="3">
+        <v>26.0</v>
+      </c>
+      <c r="H13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="J13" s="3">
+        <v>58.0</v>
+      </c>
+      <c r="K13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="M13" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="N13" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>12.0</v>
+      </c>
       <c r="R13" s="1"/>
-      <c r="S13" s="3"/>
-      <c r="T13" s="3"/>
+      <c r="S13" s="3">
+        <v>110.0</v>
+      </c>
+      <c r="T13" s="3">
+        <v>12.0</v>
+      </c>
       <c r="U13" s="1"/>
-      <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
+      <c r="V13" s="3">
+        <v>96.0</v>
+      </c>
+      <c r="W13" s="3">
+        <v>20.0</v>
+      </c>
       <c r="X13" s="1"/>
       <c r="Y13" s="3"/>
       <c r="Z13" s="3"/>
@@ -16916,17 +17265,25 @@
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
-        <v>26.0</v>
+        <v>38.0</v>
       </c>
       <c r="B14" s="3">
         <v>10.0</v>
       </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
+      <c r="D14" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0.0</v>
+      </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
+      <c r="J14" s="3">
+        <v>32.0</v>
+      </c>
+      <c r="K14" s="3">
+        <v>0.0</v>
+      </c>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="P14" s="3"/>
@@ -16959,8 +17316,12 @@
       <c r="AR14" s="3"/>
     </row>
     <row r="15" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
+      <c r="A15" s="3">
+        <v>32.0</v>
+      </c>
+      <c r="B15" s="3">
+        <v>10.0</v>
+      </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="G15" s="3"/>
@@ -16999,8 +17360,12 @@
       <c r="AR15" s="3"/>
     </row>
     <row r="16" spans="1:44" x14ac:dyDescent="0.2">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
+      <c r="A16" s="3">
+        <v>26.0</v>
+      </c>
+      <c r="B16" s="3">
+        <v>10.0</v>
+      </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="G16" s="3"/>
@@ -17478,39 +17843,199 @@
       <c r="AQ27" s="3"/>
       <c r="AR27" s="3"/>
     </row>
+    <row r="28" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A28" s="3"/>
+      <c r="B28" s="3"/>
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3"/>
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="3"/>
+      <c r="T28" s="3"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="3"/>
+      <c r="W28" s="3"/>
+      <c r="X28" s="1"/>
+      <c r="Y28" s="3"/>
+      <c r="Z28" s="3"/>
+      <c r="AA28" s="1"/>
+      <c r="AB28" s="3"/>
+      <c r="AC28" s="3"/>
+      <c r="AE28" s="3"/>
+      <c r="AF28" s="3"/>
+      <c r="AG28" s="1"/>
+      <c r="AH28" s="3"/>
+      <c r="AI28" s="3"/>
+      <c r="AJ28" s="1"/>
+      <c r="AK28" s="3"/>
+      <c r="AL28" s="3"/>
+      <c r="AM28" s="1"/>
+      <c r="AN28" s="3"/>
+      <c r="AO28" s="3"/>
+      <c r="AP28" s="1"/>
+      <c r="AQ28" s="3"/>
+      <c r="AR28" s="3"/>
+    </row>
+    <row r="29" spans="1:44" x14ac:dyDescent="0.2">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="1"/>
+      <c r="S29" s="3"/>
+      <c r="T29" s="3"/>
+      <c r="U29" s="1"/>
+      <c r="V29" s="3"/>
+      <c r="W29" s="3"/>
+      <c r="X29" s="1"/>
+      <c r="Y29" s="3"/>
+      <c r="Z29" s="3"/>
+      <c r="AA29" s="1"/>
+      <c r="AB29" s="3"/>
+      <c r="AC29" s="3"/>
+      <c r="AE29" s="3"/>
+      <c r="AF29" s="3"/>
+      <c r="AG29" s="1"/>
+      <c r="AH29" s="3"/>
+      <c r="AI29" s="3"/>
+      <c r="AJ29" s="1"/>
+      <c r="AK29" s="3"/>
+      <c r="AL29" s="3"/>
+      <c r="AM29" s="1"/>
+      <c r="AN29" s="3"/>
+      <c r="AO29" s="3"/>
+      <c r="AP29" s="1"/>
+      <c r="AQ29" s="3"/>
+      <c r="AR29" s="3"/>
+    </row>
   </sheetData>
   <mergeCells count="30">
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AN6:AO6"/>
+    <mergeCell ref="AB7:AC7"/>
+    <mergeCell ref="AN7:AO7"/>
     <mergeCell ref="AB4:AC4"/>
     <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="G7:H7"/>
     <mergeCell ref="J4:K4"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="Y6:Z6"/>
+    <mergeCell ref="V7:W7"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="AH7:AI7"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="Y7:Z7"/>
     <mergeCell ref="AQ4:AR4"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
-    <mergeCell ref="AK6:AL6"/>
-    <mergeCell ref="AE6:AF6"/>
-    <mergeCell ref="AQ6:AR6"/>
+    <mergeCell ref="AK7:AL7"/>
+    <mergeCell ref="AE7:AF7"/>
+    <mergeCell ref="AQ7:AR7"/>
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="S4:T4"/>
     <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A7:B7"/>
     <mergeCell ref="AK4:AL4"/>
-    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="D7:E7"/>
     <mergeCell ref="V4:W4"/>
     <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="J6:K6"/>
-    <mergeCell ref="P6:Q6"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="P7:Q7"/>
   </mergeCells>
+  <conditionalFormatting sqref="B6 A7:B7">
+    <cfRule type="expression" dxfId="17" priority="1">
+      <formula>AND($B$5&lt;&gt;"",$B$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6 D7:E7">
+    <cfRule type="expression" dxfId="16" priority="2">
+      <formula>AND($E$5&lt;&gt;"",$E$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H6 G7:H7">
+    <cfRule type="expression" dxfId="15" priority="3">
+      <formula>AND($H$5&lt;&gt;"",$H$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K6 J7:K7">
+    <cfRule type="expression" dxfId="14" priority="4">
+      <formula>AND($K$5&lt;&gt;"",$K$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N6 M7:N7">
+    <cfRule type="expression" dxfId="13" priority="5">
+      <formula>AND($N$5&lt;&gt;"",$N$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Q6 P7:Q7">
+    <cfRule type="expression" dxfId="12" priority="6">
+      <formula>AND($Q$5&lt;&gt;"",$Q$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T6 S7:T7">
+    <cfRule type="expression" dxfId="11" priority="7">
+      <formula>AND($T$5&lt;&gt;"",$T$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W6 V7:W7">
+    <cfRule type="expression" dxfId="10" priority="8">
+      <formula>AND($W$5&lt;&gt;"",$W$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z6 Y7:Z7">
+    <cfRule type="expression" dxfId="9" priority="9">
+      <formula>AND($Z$5&lt;&gt;"",$Z$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AC6 AB7:AC7">
+    <cfRule type="expression" dxfId="8" priority="10">
+      <formula>AND($AC$5&lt;&gt;"",$AC$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF6 AE7:AF7">
+    <cfRule type="expression" dxfId="7" priority="11">
+      <formula>AND($AF$5&lt;&gt;"",$AF$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AI6 AH7:AI7">
+    <cfRule type="expression" dxfId="6" priority="12">
+      <formula>AND($AI$5&lt;&gt;"",$AI$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL6 AK7:AL7">
+    <cfRule type="expression" dxfId="5" priority="13">
+      <formula>AND($AL$5&lt;&gt;"",$AL$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AO6 AN7:AO7">
+    <cfRule type="expression" dxfId="4" priority="14">
+      <formula>AND($AO$5&lt;&gt;"",$AO$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AR6 AQ7:AR7">
+    <cfRule type="expression" dxfId="3" priority="15">
+      <formula>AND($AR$5&lt;&gt;"",$AR$5&lt;&gt;"material")</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5 E5 H5 K5 N5 Q5 T5 W5 Z5 AC5 AF5 AI5 AL5 AO5 AR5" xr:uid="{00000000-0002-0000-0400-000000000000}">
+      <formula1>"material,ssr reduce,ssr hold,ssr elastic,refine"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -17958,17 +18483,17 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="E3:E42">
-    <cfRule type="expression" dxfId="4" priority="3">
+    <cfRule type="expression" dxfId="2" priority="3">
       <formula>OR($D3="Intercept", $D3="Radius")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:G42">
-    <cfRule type="expression" dxfId="3" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>OR($D3="Depth",$D3="Radius")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H3:H42">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="0" priority="1">
       <formula>OR($D3="Depth",$D3="Intercept")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -18143,7 +18668,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="B2:X22"/>
+  <dimension ref="B2:X23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -18193,80 +18718,92 @@
       <c r="X2" s="62"/>
     </row>
     <row r="3" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="C3" s="58"/>
+      <c r="D3" s="39"/>
+      <c r="F3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="G3" s="58"/>
+      <c r="H3" s="39"/>
+      <c r="J3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="K3" s="58"/>
+      <c r="L3" s="39"/>
+      <c r="N3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="O3" s="58"/>
+      <c r="P3" s="39"/>
+      <c r="R3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="S3" s="58"/>
+      <c r="T3" s="39"/>
+      <c r="V3" s="58" t="s">
+        <v>304</v>
+      </c>
+      <c r="W3" s="58"/>
+      <c r="X3" s="39"/>
+    </row>
+    <row r="4" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="N4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="O4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="P4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="R4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="T4" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="V3" s="2" t="s">
+      <c r="V4" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="W3" s="2" t="s">
+      <c r="W4" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="X3" s="2" t="s">
+      <c r="X4" s="2" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="4" spans="2:24" x14ac:dyDescent="0.2">
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="R4" s="3"/>
-      <c r="S4" s="3"/>
-      <c r="T4" s="3"/>
-      <c r="V4" s="3"/>
-      <c r="W4" s="3"/>
-      <c r="X4" s="3"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B5" s="3"/>
@@ -18628,15 +19165,46 @@
       <c r="W22" s="3"/>
       <c r="X22" s="3"/>
     </row>
+    <row r="23" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="N23" s="3"/>
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="R23" s="3"/>
+      <c r="S23" s="3"/>
+      <c r="T23" s="3"/>
+      <c r="V23" s="3"/>
+      <c r="W23" s="3"/>
+      <c r="X23" s="3"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="12">
     <mergeCell ref="B2:D2"/>
     <mergeCell ref="V2:X2"/>
     <mergeCell ref="J2:L2"/>
     <mergeCell ref="N2:P2"/>
     <mergeCell ref="R2:T2"/>
     <mergeCell ref="F2:H2"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="R3:S3"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D3 H3 L3 P3 T3 X3" xr:uid="{00000000-0002-0000-0800-000000000000}">
+      <formula1>"normal,vertical"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/docs/usage/sample_sheets/sheets_polygon.xlsx
+++ b/docs/usage/sample_sheets/sheets_polygon.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD1DA693-1E25-A64A-9652-172751DD72EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B93A9E-8BB4-7F49-AFDD-09E330D60C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="660" yWindow="600" windowWidth="44060" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="660" yWindow="600" windowWidth="44060" windowHeight="18400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -403,9 +403,6 @@
     <t>g</t>
   </si>
   <si>
-    <t>gsat</t>
-  </si>
-  <si>
     <t>option</t>
   </si>
   <si>
@@ -1118,6 +1115,25 @@
         <charset val="2"/>
       </rPr>
       <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Symbol"/>
+        <charset val="2"/>
+      </rPr>
+      <t>g</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="0"/>
+        <rFont val="Aptos Narrow"/>
+      </rPr>
+      <t>sat</t>
     </r>
   </si>
 </sst>
@@ -3219,67 +3235,67 @@
   <sheetData>
     <row r="2" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="40" t="s">
         <v>247</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="H2" s="40" t="s">
         <v>248</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="I2" s="40" t="s">
         <v>249</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="J2" s="27" t="s">
         <v>250</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="K2" s="27" t="s">
         <v>251</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="L2" s="27" t="s">
         <v>252</v>
       </c>
-      <c r="L2" s="27" t="s">
+      <c r="M2" s="27" t="s">
         <v>253</v>
       </c>
-      <c r="M2" s="27" t="s">
+      <c r="N2" s="27" t="s">
         <v>254</v>
       </c>
-      <c r="N2" s="27" t="s">
+      <c r="O2" s="27" t="s">
         <v>255</v>
       </c>
-      <c r="O2" s="27" t="s">
+      <c r="P2" s="28" t="s">
         <v>256</v>
       </c>
-      <c r="P2" s="28" t="s">
+      <c r="Q2" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="R2" s="28" t="s">
         <v>257</v>
       </c>
-      <c r="Q2" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="R2" s="28" t="s">
+      <c r="Z2" t="s">
         <v>258</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" t="s">
         <v>259</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AB2" t="s">
         <v>260</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="3" spans="1:28" x14ac:dyDescent="0.2">
@@ -3310,13 +3326,13 @@
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
       <c r="Z3" t="s">
+        <v>261</v>
+      </c>
+      <c r="AA3" t="s">
         <v>262</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AB3" t="s">
         <v>263</v>
-      </c>
-      <c r="AB3" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.2">
@@ -3347,7 +3363,7 @@
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
       <c r="Z4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.2">
@@ -3378,7 +3394,7 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="Z5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.2">
@@ -3465,13 +3481,13 @@
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
       <c r="Z8" t="s">
+        <v>258</v>
+      </c>
+      <c r="AA8" t="s">
         <v>259</v>
       </c>
-      <c r="AA8" t="s">
+      <c r="AB8" t="s">
         <v>260</v>
-      </c>
-      <c r="AB8" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.2">
@@ -3502,13 +3518,13 @@
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
       <c r="Z9" t="s">
+        <v>261</v>
+      </c>
+      <c r="AA9" t="s">
         <v>262</v>
       </c>
-      <c r="AA9" t="s">
+      <c r="AB9" t="s">
         <v>263</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.2">
@@ -3539,13 +3555,13 @@
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
       <c r="Z10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AA10" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AB10" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.2">
@@ -3576,13 +3592,13 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="Z11" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AA11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AB11" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.2">
@@ -3947,61 +3963,61 @@
   <sheetData>
     <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>246</v>
       </c>
-      <c r="F2" s="12" t="s">
-        <v>247</v>
-      </c>
       <c r="G2" s="40" t="s">
+        <v>266</v>
+      </c>
+      <c r="H2" s="40" t="s">
+        <v>305</v>
+      </c>
+      <c r="I2" s="40" t="s">
+        <v>249</v>
+      </c>
+      <c r="J2" s="27" t="s">
         <v>267</v>
       </c>
-      <c r="H2" s="40" t="s">
-        <v>306</v>
-      </c>
-      <c r="I2" s="40" t="s">
-        <v>250</v>
-      </c>
-      <c r="J2" s="27" t="s">
+      <c r="K2" s="27" t="s">
         <v>268</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="L2" s="41" t="s">
         <v>269</v>
       </c>
-      <c r="L2" s="41" t="s">
+      <c r="M2" s="41" t="s">
         <v>270</v>
       </c>
-      <c r="M2" s="41" t="s">
+      <c r="N2" s="28" t="s">
+        <v>122</v>
+      </c>
+      <c r="O2" s="28" t="s">
         <v>271</v>
       </c>
-      <c r="N2" s="28" t="s">
-        <v>123</v>
-      </c>
-      <c r="O2" s="28" t="s">
+      <c r="P2" s="28" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q2" s="28" t="s">
         <v>272</v>
       </c>
-      <c r="P2" s="28" t="s">
-        <v>258</v>
-      </c>
-      <c r="Q2" s="28" t="s">
-        <v>273</v>
-      </c>
       <c r="Z2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AA2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
@@ -4025,10 +4041,10 @@
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
       <c r="Z3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AA3" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
@@ -4272,22 +4288,22 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C2" s="12" t="s">
+        <v>166</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>167</v>
       </c>
-      <c r="D2" s="12" t="s">
-        <v>168</v>
-      </c>
       <c r="E2" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="F2" s="12" t="s">
         <v>274</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -4510,27 +4526,27 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="64" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="59" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="F2" s="54"/>
       <c r="H2" s="59" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I2" s="54"/>
       <c r="K2" s="59" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="L2" s="54"/>
       <c r="N2" s="59" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="O2" s="54"/>
       <c r="Q2" s="59" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="R2" s="54"/>
     </row>
@@ -4554,63 +4570,63 @@
         <v>10.0</v>
       </c>
       <c r="K3" s="32" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L3" s="33"/>
       <c r="N3" s="32" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="O3" s="33"/>
       <c r="Q3" s="32" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="R3" s="33"/>
       <c r="T3" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B4" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="C4" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="C4" s="25" t="s">
-        <v>168</v>
-      </c>
       <c r="E4" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="F4" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="F4" s="25" t="s">
-        <v>168</v>
-      </c>
       <c r="H4" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="I4" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="I4" s="25" t="s">
-        <v>168</v>
-      </c>
       <c r="K4" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="L4" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="L4" s="25" t="s">
-        <v>168</v>
-      </c>
       <c r="N4" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="O4" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="O4" s="25" t="s">
-        <v>168</v>
-      </c>
       <c r="Q4" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="R4" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="R4" s="25" t="s">
-        <v>168</v>
-      </c>
       <c r="T4" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="U4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -4639,10 +4655,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="U5" t="s">
         <v>285</v>
-      </c>
-      <c r="U5" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -4671,7 +4687,7 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="T6" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="U6" s="9"/>
     </row>
@@ -4964,27 +4980,27 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="68" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="60" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F2" s="54"/>
       <c r="H2" s="60" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="I2" s="54"/>
       <c r="K2" s="60" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="L2" s="54"/>
       <c r="N2" s="60" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="O2" s="54"/>
       <c r="Q2" s="60" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="R2" s="54"/>
     </row>
@@ -4992,71 +5008,71 @@
       <c r="B3" s="66"/>
       <c r="C3" s="67"/>
       <c r="E3" s="34" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F3" s="35"/>
       <c r="H3" s="34" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="I3" s="35"/>
       <c r="K3" s="34" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="L3" s="35"/>
       <c r="N3" s="34" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="O3" s="35"/>
       <c r="Q3" s="34" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="R3" s="35"/>
       <c r="T3" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B4" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="C4" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="C4" s="25" t="s">
-        <v>168</v>
-      </c>
       <c r="E4" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="F4" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="F4" s="25" t="s">
-        <v>168</v>
-      </c>
       <c r="H4" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="I4" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="I4" s="25" t="s">
-        <v>168</v>
-      </c>
       <c r="K4" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="L4" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="L4" s="25" t="s">
-        <v>168</v>
-      </c>
       <c r="N4" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="O4" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="O4" s="25" t="s">
-        <v>168</v>
-      </c>
       <c r="Q4" s="25" t="s">
+        <v>166</v>
+      </c>
+      <c r="R4" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="R4" s="25" t="s">
-        <v>168</v>
-      </c>
       <c r="T4" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="U4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -5073,10 +5089,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="U5" t="s">
         <v>285</v>
-      </c>
-      <c r="U5" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -5375,22 +5391,22 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B2" s="50" t="s">
+        <v>293</v>
+      </c>
+      <c r="C2" s="50" t="s">
         <v>294</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="D2" s="50" t="s">
         <v>295</v>
       </c>
-      <c r="D2" s="50" t="s">
+      <c r="E2" s="50" t="s">
         <v>296</v>
       </c>
-      <c r="E2" s="50" t="s">
+      <c r="F2" s="50" t="s">
         <v>297</v>
       </c>
-      <c r="F2" s="50" t="s">
+      <c r="G2" s="50" t="s">
         <v>298</v>
-      </c>
-      <c r="G2" s="50" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
@@ -5401,7 +5417,7 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="I3" s="14" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="J3" s="3"/>
     </row>
@@ -5423,7 +5439,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="I5" s="14" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J5" s="3"/>
     </row>
@@ -5445,7 +5461,7 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="I7" s="14" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -5457,7 +5473,7 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="I8" s="14" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="J8" s="3"/>
     </row>
@@ -5469,7 +5485,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="I9" s="14" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J9" s="3"/>
     </row>
@@ -5489,7 +5505,7 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="J11" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.2">
@@ -6484,121 +6500,121 @@
         <v>113</v>
       </c>
       <c r="D10" s="48" t="s">
+        <v>311</v>
+      </c>
+      <c r="E10" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="E10" s="44" t="s">
+      <c r="F10" s="44" t="s">
         <v>115</v>
       </c>
-      <c r="F10" s="44" t="s">
+      <c r="G10" s="45" t="s">
         <v>116</v>
       </c>
-      <c r="G10" s="45" t="s">
+      <c r="H10" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="H10" s="44" t="s">
+      <c r="I10" s="44" t="s">
         <v>118</v>
       </c>
-      <c r="I10" s="44" t="s">
+      <c r="J10" s="49" t="s">
         <v>119</v>
       </c>
-      <c r="J10" s="49" t="s">
+      <c r="K10" s="49" t="s">
         <v>120</v>
       </c>
-      <c r="K10" s="49" t="s">
+      <c r="L10" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="L10" s="21" t="s">
+      <c r="M10" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="M10" s="21" t="s">
+      <c r="N10" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="N10" s="43" t="s">
+      <c r="O10" s="44" t="s">
         <v>124</v>
-      </c>
-      <c r="O10" s="44" t="s">
-        <v>125</v>
       </c>
       <c r="P10" s="44" t="s">
         <v>105</v>
       </c>
       <c r="Q10" s="44" t="s">
+        <v>125</v>
+      </c>
+      <c r="R10" s="44" t="s">
         <v>126</v>
       </c>
-      <c r="R10" s="44" t="s">
+      <c r="S10" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="S10" s="44" t="s">
+      <c r="T10" s="44" t="s">
         <v>128</v>
       </c>
-      <c r="T10" s="44" t="s">
+      <c r="U10" s="44" t="s">
         <v>129</v>
       </c>
-      <c r="U10" s="44" t="s">
+      <c r="V10" s="44" t="s">
         <v>130</v>
       </c>
-      <c r="V10" s="44" t="s">
+      <c r="W10" s="44" t="s">
         <v>131</v>
       </c>
-      <c r="W10" s="44" t="s">
+      <c r="X10" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="X10" s="44" t="s">
+      <c r="Y10" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="Y10" s="44" t="s">
+      <c r="Z10" s="44" t="s">
         <v>134</v>
       </c>
-      <c r="Z10" s="44" t="s">
+      <c r="AA10" s="46" t="s">
+        <v>307</v>
+      </c>
+      <c r="AB10" s="46" t="s">
+        <v>306</v>
+      </c>
+      <c r="AC10" s="47" t="s">
         <v>135</v>
       </c>
-      <c r="AA10" s="46" t="s">
+      <c r="AD10" s="46" t="s">
         <v>308</v>
       </c>
-      <c r="AB10" s="46" t="s">
-        <v>307</v>
-      </c>
-      <c r="AC10" s="47" t="s">
+      <c r="AE10" s="46" t="s">
+        <v>309</v>
+      </c>
+      <c r="AF10" s="47" t="s">
+        <v>310</v>
+      </c>
+      <c r="AG10" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="AD10" s="46" t="s">
-        <v>309</v>
-      </c>
-      <c r="AE10" s="46" t="s">
-        <v>310</v>
-      </c>
-      <c r="AF10" s="47" t="s">
-        <v>311</v>
-      </c>
-      <c r="AG10" s="23" t="s">
+      <c r="AH10" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="AH10" s="23" t="s">
+      <c r="AI10" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="AI10" s="23" t="s">
+      <c r="AJ10" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="AJ10" s="23" t="s">
+      <c r="AK10" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="AK10" s="23" t="s">
+      <c r="AL10" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="AL10" s="23" t="s">
+      <c r="AM10" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="AM10" s="23" t="s">
+      <c r="AN10" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="AN10" s="23" t="s">
+      <c r="AO10" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="AO10" s="23" t="s">
+      <c r="AP10" s="23" t="s">
         <v>145</v>
-      </c>
-      <c r="AP10" s="23" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:42" x14ac:dyDescent="0.2">
@@ -8301,183 +8317,183 @@
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="D2" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="N2" s="24" t="s">
         <v>148</v>
-      </c>
-      <c r="N2" s="24" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A4" s="55" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B4" s="52"/>
       <c r="D4" s="55" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E4" s="52"/>
       <c r="G4" s="55" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H4" s="52"/>
       <c r="J4" s="55" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K4" s="52"/>
       <c r="M4" s="55" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="N4" s="52"/>
       <c r="P4" s="55" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="Q4" s="54"/>
       <c r="R4" s="1"/>
       <c r="S4" s="55" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="T4" s="54"/>
       <c r="U4" s="1"/>
       <c r="V4" s="55" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="W4" s="54"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="55" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="Z4" s="54"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="55" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AC4" s="54"/>
       <c r="AE4" s="55" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AF4" s="54"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="55" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AI4" s="54"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="55" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AL4" s="54"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="55" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AO4" s="54"/>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="55" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AR4" s="54"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B5" s="37">
         <v>1</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E5" s="37">
         <v>2</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H5" s="37">
         <v>3</v>
       </c>
       <c r="J5" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K5" s="37">
         <v>4</v>
       </c>
       <c r="M5" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N5" s="37">
         <v>5</v>
       </c>
       <c r="P5" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q5" s="37">
         <v>6</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T5" s="37">
         <v>7</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="W5" s="37">
         <v>8</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Z5" s="37">
         <v>9</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AC5" s="37">
         <v>10</v>
       </c>
       <c r="AE5" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AF5" s="37">
         <v>11</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AI5" s="37">
         <v>12</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AL5" s="37">
         <v>13</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AO5" s="37">
         <v>14</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AR5" s="37">
         <v>15</v>
@@ -8570,172 +8586,172 @@
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B7" s="37"/>
       <c r="D7" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E7" s="37"/>
       <c r="G7" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H7" s="37"/>
       <c r="J7" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K7" s="37"/>
       <c r="M7" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="N7" s="37"/>
       <c r="P7" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q7" s="37"/>
       <c r="R7" s="1"/>
       <c r="S7" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="T7" s="37"/>
       <c r="U7" s="1"/>
       <c r="V7" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="W7" s="37"/>
       <c r="X7" s="1"/>
       <c r="Y7" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Z7" s="37"/>
       <c r="AA7" s="1"/>
       <c r="AB7" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AC7" s="37"/>
       <c r="AE7" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AF7" s="37"/>
       <c r="AG7" s="1"/>
       <c r="AH7" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AI7" s="37"/>
       <c r="AJ7" s="1"/>
       <c r="AK7" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AL7" s="37"/>
       <c r="AM7" s="1"/>
       <c r="AN7" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AO7" s="37"/>
       <c r="AP7" s="1"/>
       <c r="AQ7" s="36" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AR7" s="37"/>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="D8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="G8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="J8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="M8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="N8" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="N8" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="P8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q8" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="R8" s="1"/>
       <c r="S8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="T8" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="U8" s="1"/>
       <c r="V8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="W8" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="W8" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="X8" s="1"/>
       <c r="Y8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="Z8" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="Z8" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="AA8" s="1"/>
       <c r="AB8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="AC8" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="AC8" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="AE8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="AF8" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="AF8" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="AG8" s="1"/>
       <c r="AH8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="AI8" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="AI8" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="AL8" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="AL8" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="AM8" s="1"/>
       <c r="AN8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="AO8" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="AO8" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="AR8" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="AR8" s="2" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.2">
@@ -9540,6 +9556,20 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AB6:AC6"/>
+    <mergeCell ref="AN6:AO6"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="AH6:AI6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="Y6:Z6"/>
     <mergeCell ref="AQ4:AR4"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
@@ -9556,20 +9586,6 @@
     <mergeCell ref="AH4:AI4"/>
     <mergeCell ref="J6:K6"/>
     <mergeCell ref="P6:Q6"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AB6:AC6"/>
-    <mergeCell ref="AN6:AO6"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="V6:W6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="AH6:AI6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="Y6:Z6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -9603,10 +9619,10 @@
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
+        <v>168</v>
+      </c>
+      <c r="G2" s="9" t="s">
         <v>169</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
@@ -9662,42 +9678,42 @@
       <c r="W4" s="54"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="55" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Z4" s="54"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="55" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AC4" s="54"/>
       <c r="AE4" s="55" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AF4" s="54"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="55" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AI4" s="54"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="55" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AL4" s="54"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="55" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AO4" s="54"/>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="55" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AR4" s="54"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="38" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
@@ -9705,7 +9721,7 @@
         </is>
       </c>
       <c r="D5" s="38" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E5" s="39" t="inlineStr">
         <is>
@@ -9713,7 +9729,7 @@
         </is>
       </c>
       <c r="G5" s="38" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H5" s="39" t="inlineStr">
         <is>
@@ -9721,7 +9737,7 @@
         </is>
       </c>
       <c r="J5" s="38" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="K5" s="39" t="inlineStr">
         <is>
@@ -9729,7 +9745,7 @@
         </is>
       </c>
       <c r="M5" s="38" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="N5" s="39" t="inlineStr">
         <is>
@@ -9737,7 +9753,7 @@
         </is>
       </c>
       <c r="P5" s="38" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="Q5" s="39" t="inlineStr">
         <is>
@@ -9746,7 +9762,7 @@
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="38" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="T5" s="39" t="inlineStr">
         <is>
@@ -9755,7 +9771,7 @@
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="38" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="W5" s="39" t="inlineStr">
         <is>
@@ -9764,140 +9780,140 @@
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="Z5" s="39" t="s">
         <v>186</v>
-      </c>
-      <c r="Z5" s="39" t="s">
-        <v>187</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="AC5" s="39" t="s">
         <v>186</v>
       </c>
-      <c r="AC5" s="39" t="s">
-        <v>187</v>
-      </c>
       <c r="AE5" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="AF5" s="39" t="s">
         <v>186</v>
-      </c>
-      <c r="AF5" s="39" t="s">
-        <v>187</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="AI5" s="39" t="s">
         <v>186</v>
-      </c>
-      <c r="AI5" s="39" t="s">
-        <v>187</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="AL5" s="39" t="s">
         <v>186</v>
-      </c>
-      <c r="AL5" s="39" t="s">
-        <v>187</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="AO5" s="39" t="s">
         <v>186</v>
-      </c>
-      <c r="AO5" s="39" t="s">
-        <v>187</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="AR5" s="39" t="s">
         <v>186</v>
-      </c>
-      <c r="AR5" s="39" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A6" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B6" s="39">
         <v>1</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E6" s="39">
         <v>3</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H6" s="39">
         <v>2</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K6" s="39">
         <v>3</v>
       </c>
       <c r="M6" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N6" s="39"/>
       <c r="P6" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q6" s="39"/>
       <c r="R6" s="1"/>
       <c r="S6" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T6" s="39"/>
       <c r="U6" s="1"/>
       <c r="V6" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="W6" s="39"/>
       <c r="X6" s="1"/>
       <c r="Y6" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Z6" s="39">
         <v>9</v>
       </c>
       <c r="AA6" s="1"/>
       <c r="AB6" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AC6" s="39">
         <v>10</v>
       </c>
       <c r="AE6" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AF6" s="39">
         <v>11</v>
       </c>
       <c r="AG6" s="1"/>
       <c r="AH6" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AI6" s="39">
         <v>12</v>
       </c>
       <c r="AJ6" s="1"/>
       <c r="AK6" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AL6" s="39">
         <v>13</v>
       </c>
       <c r="AM6" s="1"/>
       <c r="AN6" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AO6" s="39">
         <v>14</v>
       </c>
       <c r="AP6" s="1"/>
       <c r="AQ6" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AR6" s="39">
         <v>15</v>
@@ -9994,178 +10010,178 @@
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A8" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B8" s="39">
         <v>1.5</v>
       </c>
       <c r="D8" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E8" s="39"/>
       <c r="G8" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H8" s="39"/>
       <c r="J8" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="K8" s="39"/>
       <c r="M8" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="N8" s="39">
         <v>0.75</v>
       </c>
       <c r="P8" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q8" s="39"/>
       <c r="R8" s="1"/>
       <c r="S8" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="T8" s="39"/>
       <c r="U8" s="1"/>
       <c r="V8" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="W8" s="39">
         <v>0.5</v>
       </c>
       <c r="X8" s="1"/>
       <c r="Y8" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Z8" s="39"/>
       <c r="AA8" s="1"/>
       <c r="AB8" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AC8" s="39"/>
       <c r="AE8" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AF8" s="39"/>
       <c r="AG8" s="1"/>
       <c r="AH8" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AI8" s="39"/>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AL8" s="39"/>
       <c r="AM8" s="1"/>
       <c r="AN8" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AO8" s="39"/>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="38" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AR8" s="39"/>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="D9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="G9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="J9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="M9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="N9" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="N9" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="P9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q9" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="R9" s="1"/>
       <c r="S9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="T9" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="U9" s="1"/>
       <c r="V9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="W9" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="W9" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="X9" s="1"/>
       <c r="Y9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="Z9" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="Z9" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="AA9" s="1"/>
       <c r="AB9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="AC9" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="AC9" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="AE9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="AF9" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="AF9" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="AG9" s="1"/>
       <c r="AH9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="AI9" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="AI9" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="AJ9" s="1"/>
       <c r="AK9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="AL9" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="AL9" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="AM9" s="1"/>
       <c r="AN9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="AO9" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="AO9" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="AP9" s="1"/>
       <c r="AQ9" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="AR9" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="AR9" s="2" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.2">
@@ -11118,16 +11134,10 @@
     </row>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="AQ7:AR7"/>
-    <mergeCell ref="AN4:AO4"/>
-    <mergeCell ref="AH4:AI4"/>
-    <mergeCell ref="Y7:Z7"/>
-    <mergeCell ref="AQ4:AR4"/>
-    <mergeCell ref="Y4:Z4"/>
-    <mergeCell ref="AE7:AF7"/>
-    <mergeCell ref="AK7:AL7"/>
-    <mergeCell ref="AB4:AC4"/>
-    <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="S7:T7"/>
+    <mergeCell ref="M7:N7"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="P4:Q4"/>
@@ -11144,10 +11154,16 @@
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="AB7:AC7"/>
     <mergeCell ref="AH7:AI7"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="S7:T7"/>
-    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="AQ7:AR7"/>
+    <mergeCell ref="AN4:AO4"/>
+    <mergeCell ref="AH4:AI4"/>
+    <mergeCell ref="Y7:Z7"/>
+    <mergeCell ref="AQ4:AR4"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AE7:AF7"/>
+    <mergeCell ref="AK7:AL7"/>
+    <mergeCell ref="AB4:AC4"/>
+    <mergeCell ref="AK4:AL4"/>
   </mergeCells>
   <conditionalFormatting sqref="B6 A7:B7">
     <cfRule type="expression" dxfId="17" priority="1">
@@ -11244,20 +11260,20 @@
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="59" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B2" s="54"/>
       <c r="D2" s="60" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E2" s="54"/>
       <c r="G2" s="22" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="32" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B3" s="33" t="inlineStr">
         <is>
@@ -11265,7 +11281,7 @@
         </is>
       </c>
       <c r="D3" s="34" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E3" s="35" t="inlineStr">
         <is>
@@ -11276,19 +11292,19 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="D4" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>168</v>
-      </c>
       <c r="G4" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H4" s="1"/>
     </row>
@@ -11301,7 +11317,7 @@
         <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -11310,10 +11326,10 @@
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="G6" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="H6" t="s">
         <v>193</v>
-      </c>
-      <c r="H6" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -11450,31 +11466,31 @@
   <sheetData>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="C2" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="D2" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="E2" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="F2" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="G2" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="H2" s="13" t="s">
         <v>201</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="J2" s="5" t="s">
         <v>202</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>203</v>
       </c>
       <c r="K2" s="10" t="s">
         <v>5</v>
@@ -11492,10 +11508,10 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="J3" s="1" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -11510,10 +11526,10 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="J4" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="K4" s="9" t="s">
         <v>205</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -11528,10 +11544,10 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="J5" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="K5" t="s">
         <v>207</v>
-      </c>
-      <c r="K5" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -11558,7 +11574,7 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="J7" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -11573,7 +11589,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="J8" s="14" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K8"/>
     </row>
@@ -11589,7 +11605,7 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="J9" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K9"/>
     </row>
@@ -11605,7 +11621,7 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="J10" s="14" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K10"/>
     </row>
@@ -11621,7 +11637,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="J11" s="14" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K11"/>
     </row>
@@ -11637,31 +11653,31 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="J12" s="14" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K12"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J13" s="14" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K13"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J14" s="14" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K14"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J15" s="14" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K15"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J16" s="14" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -11670,7 +11686,7 @@
     </row>
     <row r="17" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J17" s="14" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="K17"/>
     </row>
@@ -11711,16 +11727,16 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
+        <v>219</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="C2" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>222</v>
-      </c>
       <c r="E2" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>5</v>
@@ -11731,10 +11747,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" t="s">
+        <v>222</v>
+      </c>
+      <c r="F3" t="s">
         <v>223</v>
-      </c>
-      <c r="F3" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -11742,10 +11758,10 @@
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="E4" t="s">
+        <v>224</v>
+      </c>
+      <c r="F4" t="s">
         <v>225</v>
-      </c>
-      <c r="F4" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -11753,10 +11769,10 @@
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="E5" t="s">
+        <v>226</v>
+      </c>
+      <c r="F5" t="s">
         <v>227</v>
-      </c>
-      <c r="F5" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -11886,122 +11902,122 @@
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B4" s="61" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
       <c r="F4" s="61" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G4" s="62"/>
       <c r="H4" s="62"/>
       <c r="J4" s="61" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K4" s="62"/>
       <c r="L4" s="62"/>
       <c r="N4" s="61" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="O4" s="62"/>
       <c r="P4" s="62"/>
       <c r="R4" s="61" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="S4" s="62"/>
       <c r="T4" s="62"/>
       <c r="V4" s="61" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="W4" s="62"/>
       <c r="X4" s="62"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B5" s="58" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C5" s="57"/>
       <c r="D5" s="39"/>
       <c r="F5" s="58" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G5" s="57"/>
       <c r="H5" s="39"/>
       <c r="J5" s="58" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K5" s="57"/>
       <c r="L5" s="39"/>
       <c r="N5" s="58" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O5" s="57"/>
       <c r="P5" s="39"/>
       <c r="R5" s="58" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="S5" s="57"/>
       <c r="T5" s="39"/>
       <c r="V5" s="58" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="W5" s="57"/>
       <c r="X5" s="39"/>
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="L6" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="N6" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="O6" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="P6" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="R6" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="S6" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="S6" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="T6" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="V6" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="W6" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="W6" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="X6" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.2">
@@ -12435,122 +12451,122 @@
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B4" s="63" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
       <c r="F4" s="63" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G4" s="62"/>
       <c r="H4" s="62"/>
       <c r="J4" s="63" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K4" s="62"/>
       <c r="L4" s="62"/>
       <c r="N4" s="63" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="O4" s="62"/>
       <c r="P4" s="62"/>
       <c r="R4" s="63" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="S4" s="62"/>
       <c r="T4" s="62"/>
       <c r="V4" s="63" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="W4" s="62"/>
       <c r="X4" s="62"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B5" s="58" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C5" s="57"/>
       <c r="D5" s="39"/>
       <c r="F5" s="58" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G5" s="57"/>
       <c r="H5" s="39"/>
       <c r="J5" s="58" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="K5" s="57"/>
       <c r="L5" s="39"/>
       <c r="N5" s="58" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="O5" s="57"/>
       <c r="P5" s="39"/>
       <c r="R5" s="58" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="S5" s="57"/>
       <c r="T5" s="39"/>
       <c r="V5" s="58" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="W5" s="57"/>
       <c r="X5" s="39"/>
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="L6" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="N6" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="O6" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="P6" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="R6" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="S6" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="S6" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="T6" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="V6" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="W6" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="W6" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="X6" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.2">

--- a/docs/usage/sample_sheets/sheets_polygon.xlsx
+++ b/docs/usage/sample_sheets/sheets_polygon.xlsx
@@ -8502,17 +8502,17 @@
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A6" s="56" t="str">
         <f>_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
-        <v/>
+        <v>levee</v>
       </c>
       <c r="B6" s="57"/>
       <c r="D6" s="56" t="str">
         <f>_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
-        <v/>
+        <v>grout</v>
       </c>
       <c r="E6" s="57"/>
       <c r="G6" s="56" t="str">
         <f>_xlfn.XLOOKUP(H5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
-        <v/>
+        <v>foundation</v>
       </c>
       <c r="H6" s="57"/>
       <c r="J6" s="56" t="str">

--- a/docs/usage/sample_sheets/sheets_polygon.xlsx
+++ b/docs/usage/sample_sheets/sheets_polygon.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/njones/python_projects/xslope/docs/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0B93A9E-8BB4-7F49-AFDD-09E330D60C52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E12967D2-A998-D342-B5ED-43CABE326A3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="660" yWindow="600" windowWidth="44060" windowHeight="18400" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15680" yWindow="4780" windowWidth="46940" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -59,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="319">
   <si>
     <t>XSLOPE Input Template</t>
   </si>
@@ -343,9 +343,6 @@
     <t>vg</t>
   </si>
   <si>
-    <t>van Genuchten model (a, n)</t>
-  </si>
-  <si>
     <t>pow</t>
   </si>
   <si>
@@ -877,9 +874,6 @@
     <t>I</t>
   </si>
   <si>
-    <t>Fixity</t>
-  </si>
-  <si>
     <t>P</t>
   </si>
   <si>
@@ -974,28 +968,6 @@
   </si>
   <si>
     <t>save_times</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <rFont val="Symbol"/>
-        <charset val="2"/>
-      </rPr>
-      <t>q</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <rFont val="Aptos Narrow"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>p</t>
-    </r>
   </si>
   <si>
     <r>
@@ -1136,12 +1108,42 @@
       <t>sat</t>
     </r>
   </si>
+  <si>
+    <t>yr</t>
+  </si>
+  <si>
+    <t>Adhesion</t>
+  </si>
+  <si>
+    <t>Delta</t>
+  </si>
+  <si>
+    <t>1D element size:</t>
+  </si>
+  <si>
+    <t>Head</t>
+  </si>
+  <si>
+    <t>Tip</t>
+  </si>
+  <si>
+    <t>Pinned</t>
+  </si>
+  <si>
+    <t>Unrotated</t>
+  </si>
+  <si>
+    <t>van Genuchten model (a, n, l)</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1257,13 +1259,6 @@
       <sz val="12"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Symbol"/>
-      <charset val="2"/>
     </font>
   </fonts>
   <fills count="18">
@@ -1912,16 +1907,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>18</xdr:col>
+      <xdr:col>20</xdr:col>
       <xdr:colOff>217714</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>54430</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>199571</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>9071</xdr:rowOff>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>444500</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>90714</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1936,8 +1931,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14804571" y="254001"/>
-          <a:ext cx="3610429" cy="3746499"/>
+          <a:off x="16455571" y="254001"/>
+          <a:ext cx="3855358" cy="4027713"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2061,6 +2056,31 @@
         <a:p>
           <a:r>
             <a:rPr lang="en-US" sz="1100" b="1"/>
+            <a:t>Adhesion</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+            <a:t> = soii-reinforcement interface adhesion (blank</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" baseline="0"/>
+            <a:t> = use Lp)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
+            <a:t>Delta</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" baseline="0"/>
+            <a:t> = soil-reinforcement interface friction angle (blank = use Lp)</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1"/>
             <a:t>Tend1, Tend2 </a:t>
           </a:r>
           <a:r>
@@ -2107,6 +2127,10 @@
             <a:rPr lang="en-US" sz="1100" b="0"/>
             <a:t> = cross-sectional area of reinforcement (FEM only)</a:t>
           </a:r>
+          <a:br>
+            <a:rPr lang="en-US" sz="1100" b="0"/>
+          </a:br>
+          <a:endParaRPr lang="en-US" sz="1100" b="0"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -2120,15 +2144,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>308429</xdr:colOff>
+      <xdr:colOff>290286</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>190499</xdr:rowOff>
+      <xdr:rowOff>126999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>571501</xdr:colOff>
+      <xdr:colOff>553358</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>117925</xdr:rowOff>
+      <xdr:rowOff>54428</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -2143,8 +2167,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14224000" y="190499"/>
-          <a:ext cx="3156858" cy="2521855"/>
+          <a:off x="14205857" y="126999"/>
+          <a:ext cx="3156858" cy="2521858"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2200,34 +2224,15 @@
             <a:rPr lang="en-US" sz="1100" baseline="0"/>
             <a:t> = Pile force magnitude (kN/m or lb/ft). </a:t>
           </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1" baseline="0">
-              <a:latin typeface="Symbol" pitchFamily="2" charset="2"/>
-            </a:rPr>
-            <a:t>q</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="1" baseline="0"/>
-            <a:t>p</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" baseline="0"/>
-            <a:t> = </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" b="0" i="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>Force angle from horizontal in degrees (degrees)</a:t>
-          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100" b="0" i="0">
+            <a:solidFill>
+              <a:schemeClr val="dk1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
         </a:p>
         <a:p>
           <a:r>
@@ -2468,7 +2473,7 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>Fixity</a:t>
+            <a:t>Head</a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
@@ -2480,8 +2485,54 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t> = Pile head status (fixed or free)</a:t>
+            <a:t> = Pile head fixity status</a:t>
           </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="1" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Tip</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> = Pile tip fixity status</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+        <a:p>
           <a:endParaRPr lang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
@@ -2808,7 +2859,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.6640625" customWidth="1"/>
@@ -2833,7 +2884,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="30">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
@@ -3009,7 +3060,7 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C20" s="14" t="s">
-        <v>45</v>
+        <v>312</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>46</v>
@@ -3021,7 +3072,7 @@
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C21" s="14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>49</v>
@@ -3033,28 +3084,34 @@
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.2">
       <c r="C22" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="1"/>
+        <v>48</v>
+      </c>
       <c r="F22" s="1"/>
+      <c r="D22"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B23" s="1"/>
       <c r="C23" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="1"/>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="B24" s="1"/>
+      <c r="C24" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D23" s="1" t="inlineStr">
+      <c r="D24" s="1" t="inlineStr">
         <is>
           <t>auto</t>
         </is>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B24" s="1"/>
-      <c r="C24" s="14" t="s">
+    <row r="25" spans="2:7" x14ac:dyDescent="0.2">
+      <c r="C25" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="D24"/>
+      <c r="D25"/>
     </row>
     <row r="49" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D49" s="1" t="s">
@@ -3096,93 +3153,98 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D59" s="1" t="s">
-        <v>62</v>
+    <row r="58" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D58" s="1" t="s">
+        <v>309</v>
       </c>
     </row>
     <row r="60" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D60" s="1" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
     </row>
     <row r="61" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D61" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="62" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D62" s="1" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="63" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D63" s="1" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="64" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D64" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="65" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D65" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="66" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D66" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="67" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D67" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="68" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D68" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="69" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D69" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="70" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D70" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="71" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D71" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="72" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D72" s="1" t="s">
         <v>72</v>
-      </c>
-    </row>
-    <row r="73" spans="4:4" x14ac:dyDescent="0.2">
-      <c r="D73" s="1" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="74" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D74" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="75" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D75" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="76" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D76" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="77" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D77" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="78" spans="4:4" x14ac:dyDescent="0.2">
       <c r="D78" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="4:4" x14ac:dyDescent="0.2">
+      <c r="D79" s="1" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3191,28 +3253,28 @@
     <mergeCell ref="B7:D7"/>
   </mergeCells>
   <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D22" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D23" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"rollers,fixed"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D8" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>$D$50:$D$51</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D9" xr:uid="{00000000-0002-0000-0000-000002000000}">
-      <formula1>$D$54:$D$57</formula1>
+      <formula1>$D$54:$D$58</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D17" xr:uid="{00000000-0002-0000-0000-000003000000}">
-      <formula1>$D$60:$D$61</formula1>
+      <formula1>$D$61:$D$62</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D14" xr:uid="{00000000-0002-0000-0000-000004000000}">
-      <formula1>$D$64:$D$71</formula1>
+      <formula1>$D$65:$D$72</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="D18" xr:uid="{00000000-0002-0000-0000-000005000000}">
-      <formula1>$D$74:$D$78</formula1>
+      <formula1>$D$75:$D$79</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D23" xr:uid="{00000000-0002-0000-0000-000006000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D24" xr:uid="{00000000-0002-0000-0000-000006000000}">
       <formula1>"auto,manual"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D24" xr:uid="{00000000-0002-0000-0000-000007000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D25" xr:uid="{00000000-0002-0000-0000-000007000000}">
       <formula1>"circular,non-circular"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3222,83 +3284,89 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A2:AB25"/>
+  <dimension ref="A2:AD25"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="1" customWidth="1"/>
     <col min="2" max="6" width="10.83203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="13.1640625" customWidth="1"/>
-    <col min="10" max="12" width="10.83203125" style="1" customWidth="1"/>
-    <col min="16" max="18" width="10.83203125" style="1" customWidth="1"/>
-    <col min="19" max="19" width="4.33203125" customWidth="1"/>
+    <col min="10" max="14" width="10.83203125" style="1" customWidth="1"/>
+    <col min="18" max="20" width="10.83203125" style="1" customWidth="1"/>
+    <col min="21" max="21" width="4.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="F2" s="12" t="s">
+      <c r="G2" s="40" t="s">
         <v>246</v>
       </c>
-      <c r="G2" s="40" t="s">
+      <c r="H2" s="40" t="s">
         <v>247</v>
       </c>
-      <c r="H2" s="40" t="s">
+      <c r="I2" s="40" t="s">
         <v>248</v>
       </c>
-      <c r="I2" s="40" t="s">
+      <c r="J2" s="27" t="s">
         <v>249</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="K2" s="27" t="s">
         <v>250</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="L2" s="27" t="s">
         <v>251</v>
       </c>
-      <c r="L2" s="27" t="s">
+      <c r="M2" s="27" t="s">
+        <v>310</v>
+      </c>
+      <c r="N2" s="27" t="s">
+        <v>311</v>
+      </c>
+      <c r="O2" s="27" t="s">
         <v>252</v>
       </c>
-      <c r="M2" s="27" t="s">
+      <c r="P2" s="27" t="s">
         <v>253</v>
       </c>
-      <c r="N2" s="27" t="s">
+      <c r="Q2" s="27" t="s">
         <v>254</v>
       </c>
-      <c r="O2" s="27" t="s">
+      <c r="R2" s="28" t="s">
         <v>255</v>
       </c>
-      <c r="P2" s="28" t="s">
+      <c r="S2" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="T2" s="28" t="s">
         <v>256</v>
       </c>
-      <c r="Q2" s="28" t="s">
-        <v>122</v>
-      </c>
-      <c r="R2" s="28" t="s">
+      <c r="AB2" t="s">
         <v>257</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AC2" t="s">
         <v>258</v>
       </c>
-      <c r="AA2" t="s">
+      <c r="AD2" t="s">
         <v>259</v>
       </c>
-      <c r="AB2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>1</v>
       </c>
@@ -3309,11 +3377,11 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3" t="str">
-        <f t="shared" ref="H3:H22" si="0">IF($G3="","",IFERROR(VLOOKUP($G3,$Z$8:$AB$11,2,0),""))</f>
+        <f t="shared" ref="H3:H22" si="0">IF($G3="","",IFERROR(VLOOKUP($G3,$AB$8:$AD$11,2,0),""))</f>
         <v/>
       </c>
       <c r="I3" s="3" t="str">
-        <f t="shared" ref="I3:I22" si="1">IF($G3="","",IFERROR(VLOOKUP($G3,$Z$8:$AB$11,3,0),""))</f>
+        <f t="shared" ref="I3:I22" si="1">IF($G3="","",IFERROR(VLOOKUP($G3,$AB$8:$AD$11,3,0),""))</f>
         <v/>
       </c>
       <c r="J3" s="3"/>
@@ -3325,17 +3393,19 @@
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
       <c r="R3" s="3"/>
-      <c r="Z3" t="s">
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="AB3" t="s">
+        <v>260</v>
+      </c>
+      <c r="AC3" t="s">
         <v>261</v>
       </c>
-      <c r="AA3" t="s">
+      <c r="AD3" t="s">
         <v>262</v>
       </c>
-      <c r="AB3" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2</v>
       </c>
@@ -3362,11 +3432,13 @@
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
       <c r="R4" s="3"/>
-      <c r="Z4" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S4" s="3"/>
+      <c r="T4" s="3"/>
+      <c r="AB4" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>3</v>
       </c>
@@ -3393,11 +3465,13 @@
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
-      <c r="Z5" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S5" s="3"/>
+      <c r="T5" s="3"/>
+      <c r="AB5" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>4</v>
       </c>
@@ -3424,8 +3498,10 @@
       <c r="P6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
-    </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S6" s="3"/>
+      <c r="T6" s="3"/>
+    </row>
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>5</v>
       </c>
@@ -3452,8 +3528,10 @@
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
       <c r="R7" s="3"/>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S7" s="3"/>
+      <c r="T7" s="3"/>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>6</v>
       </c>
@@ -3480,17 +3558,19 @@
       <c r="P8" s="3"/>
       <c r="Q8" s="3"/>
       <c r="R8" s="3"/>
-      <c r="Z8" t="s">
+      <c r="S8" s="3"/>
+      <c r="T8" s="3"/>
+      <c r="AB8" t="s">
+        <v>257</v>
+      </c>
+      <c r="AC8" t="s">
         <v>258</v>
       </c>
-      <c r="AA8" t="s">
+      <c r="AD8" t="s">
         <v>259</v>
       </c>
-      <c r="AB8" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>7</v>
       </c>
@@ -3517,17 +3597,19 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
       <c r="R9" s="3"/>
-      <c r="Z9" t="s">
+      <c r="S9" s="3"/>
+      <c r="T9" s="3"/>
+      <c r="AB9" t="s">
+        <v>260</v>
+      </c>
+      <c r="AC9" t="s">
         <v>261</v>
       </c>
-      <c r="AA9" t="s">
+      <c r="AD9" t="s">
         <v>262</v>
       </c>
-      <c r="AB9" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>8</v>
       </c>
@@ -3554,17 +3636,19 @@
       <c r="P10" s="3"/>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
-      <c r="Z10" t="s">
-        <v>264</v>
-      </c>
-      <c r="AA10" t="s">
-        <v>262</v>
-      </c>
+      <c r="S10" s="3"/>
+      <c r="T10" s="3"/>
       <c r="AB10" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+        <v>263</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>261</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>9</v>
       </c>
@@ -3591,17 +3675,19 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-      <c r="Z11" t="s">
-        <v>265</v>
-      </c>
-      <c r="AA11" t="s">
-        <v>262</v>
-      </c>
+      <c r="S11" s="3"/>
+      <c r="T11" s="3"/>
       <c r="AB11" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+        <v>264</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>261</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>10</v>
       </c>
@@ -3628,8 +3714,10 @@
       <c r="P12" s="3"/>
       <c r="Q12" s="3"/>
       <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+      <c r="T12" s="3"/>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>11</v>
       </c>
@@ -3656,8 +3744,10 @@
       <c r="P13" s="3"/>
       <c r="Q13" s="3"/>
       <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S13" s="3"/>
+      <c r="T13" s="3"/>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>12</v>
       </c>
@@ -3684,8 +3774,10 @@
       <c r="P14" s="3"/>
       <c r="Q14" s="3"/>
       <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+      <c r="T14" s="3"/>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>13</v>
       </c>
@@ -3712,8 +3804,10 @@
       <c r="P15" s="3"/>
       <c r="Q15" s="3"/>
       <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+      <c r="T15" s="3"/>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>14</v>
       </c>
@@ -3740,8 +3834,10 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>15</v>
       </c>
@@ -3768,8 +3864,10 @@
       <c r="P17" s="3"/>
       <c r="Q17" s="3"/>
       <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+      <c r="T17" s="3"/>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>16</v>
       </c>
@@ -3796,8 +3894,10 @@
       <c r="P18" s="3"/>
       <c r="Q18" s="3"/>
       <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+      <c r="T18" s="3"/>
+    </row>
+    <row r="19" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>17</v>
       </c>
@@ -3824,8 +3924,10 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>18</v>
       </c>
@@ -3852,8 +3954,10 @@
       <c r="P20" s="3"/>
       <c r="Q20" s="3"/>
       <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+      <c r="T20" s="3"/>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>19</v>
       </c>
@@ -3880,8 +3984,10 @@
       <c r="P21" s="3"/>
       <c r="Q21" s="3"/>
       <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+      <c r="T21" s="3"/>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>20</v>
       </c>
@@ -3908,39 +4014,41 @@
       <c r="P22" s="3"/>
       <c r="Q22" s="3"/>
       <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
-      <c r="T23" s="42"/>
-      <c r="U23" t="s">
+      <c r="S22" s="3"/>
+      <c r="T22" s="3"/>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="V23" s="42"/>
+      <c r="W23" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.2">
       <c r="K24" s="9"/>
       <c r="L24" s="9"/>
-      <c r="T24" s="26"/>
-      <c r="U24" s="9" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V24" s="26"/>
+      <c r="W24" s="9" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" x14ac:dyDescent="0.2">
       <c r="K25" s="9"/>
       <c r="L25" s="9"/>
-      <c r="T25" s="29"/>
-      <c r="U25" s="9" t="s">
-        <v>104</v>
+      <c r="V25" s="29"/>
+      <c r="W25" s="9" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G3:G22" xr:uid="{00000000-0002-0000-0900-000000000000}">
-      <formula1>$Z$2:$Z$5</formula1>
+      <formula1>$AB$2:$AB$5</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H22" xr:uid="{00000000-0002-0000-0900-000001000000}">
-      <formula1>$AA$2:$AA$3</formula1>
+      <formula1>$AC$2:$AC$3</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I22" xr:uid="{00000000-0002-0000-0900-000002000000}">
-      <formula1>$AB$2:$AB$3</formula1>
+      <formula1>$AD$2:$AD$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3950,74 +4058,74 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
-  <dimension ref="A2:AA18"/>
+  <dimension ref="A2:AA17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.83203125" style="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" style="1" customWidth="1"/>
-    <col min="3" max="8" width="10.83203125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5" customWidth="1"/>
-    <col min="10" max="17" width="10.83203125" style="1" customWidth="1"/>
+    <col min="3" max="7" width="10.83203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5" customWidth="1"/>
+    <col min="9" max="17" width="10.83203125" style="1" customWidth="1"/>
     <col min="18" max="18" width="5.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B2" s="12" t="s">
+        <v>241</v>
+      </c>
+      <c r="C2" s="12" t="s">
         <v>242</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="D2" s="12" t="s">
         <v>243</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="E2" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="F2" s="12" t="s">
         <v>245</v>
       </c>
-      <c r="F2" s="12" t="s">
-        <v>246</v>
-      </c>
       <c r="G2" s="40" t="s">
+        <v>265</v>
+      </c>
+      <c r="H2" s="40" t="s">
+        <v>248</v>
+      </c>
+      <c r="I2" s="27" t="s">
         <v>266</v>
-      </c>
-      <c r="H2" s="40" t="s">
-        <v>305</v>
-      </c>
-      <c r="I2" s="40" t="s">
-        <v>249</v>
       </c>
       <c r="J2" s="27" t="s">
         <v>267</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="K2" s="41" t="s">
         <v>268</v>
       </c>
       <c r="L2" s="41" t="s">
         <v>269</v>
       </c>
-      <c r="M2" s="41" t="s">
+      <c r="M2" s="28" t="s">
+        <v>121</v>
+      </c>
+      <c r="N2" s="28" t="s">
         <v>270</v>
       </c>
-      <c r="N2" s="28" t="s">
-        <v>122</v>
-      </c>
       <c r="O2" s="28" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="P2" s="28" t="s">
-        <v>257</v>
+        <v>313</v>
       </c>
       <c r="Q2" s="28" t="s">
-        <v>272</v>
+        <v>314</v>
       </c>
       <c r="Z2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="AA2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.2">
@@ -4041,10 +4149,10 @@
       <c r="P3" s="3"/>
       <c r="Q3" s="3"/>
       <c r="Z3" t="s">
-        <v>226</v>
+        <v>315</v>
       </c>
       <c r="AA3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
@@ -4067,6 +4175,9 @@
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
       <c r="Q4" s="3"/>
+      <c r="Z4" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
@@ -4088,6 +4199,9 @@
       <c r="O5" s="3"/>
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
+      <c r="Z5" t="s">
+        <v>225</v>
+      </c>
     </row>
     <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
@@ -4237,38 +4351,34 @@
       <c r="Q12" s="3"/>
     </row>
     <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="I14" s="9"/>
       <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
+      <c r="S15" s="42"/>
+      <c r="T15" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.2">
-      <c r="S16" s="42"/>
-      <c r="T16" t="s">
-        <v>91</v>
+      <c r="S16" s="26"/>
+      <c r="T16" s="9" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="19:20" x14ac:dyDescent="0.2">
-      <c r="S17" s="26"/>
+      <c r="S17" s="29"/>
       <c r="T17" s="9" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="18" spans="19:20" x14ac:dyDescent="0.2">
-      <c r="S18" s="29"/>
-      <c r="T18" s="9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q3:Q12" xr:uid="{00000000-0002-0000-0A00-000000000000}">
-      <formula1>$Z$2:$Z$3</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H3:H12" xr:uid="{00000000-0002-0000-0A00-000001000000}">
+      <formula1>$AA$2:$AA$3</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I3:I12" xr:uid="{00000000-0002-0000-0A00-000001000000}">
-      <formula1>$AA$2:$AA$3</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P3:Q12" xr:uid="{00000000-0002-0000-0A00-000000000000}">
+      <formula1>$Z$2:$Z$5</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4288,22 +4398,22 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C2" s="12" t="s">
+        <v>165</v>
+      </c>
+      <c r="D2" s="12" t="s">
         <v>166</v>
       </c>
-      <c r="D2" s="12" t="s">
-        <v>167</v>
-      </c>
       <c r="E2" s="12" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -4526,27 +4636,27 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="64" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="59" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F2" s="54"/>
       <c r="H2" s="59" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="I2" s="54"/>
       <c r="K2" s="59" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="L2" s="54"/>
       <c r="N2" s="59" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="O2" s="54"/>
       <c r="Q2" s="59" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="R2" s="54"/>
     </row>
@@ -4570,63 +4680,63 @@
         <v>10.0</v>
       </c>
       <c r="K3" s="32" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="L3" s="33"/>
       <c r="N3" s="32" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="O3" s="33"/>
       <c r="Q3" s="32" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="R3" s="33"/>
       <c r="T3" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="C4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="E4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="F4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="F4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="H4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="I4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="I4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="K4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="L4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="L4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="N4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="O4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="O4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="Q4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="R4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="R4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="T4" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="U4" t="s">
         <v>281</v>
-      </c>
-      <c r="U4" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -4655,10 +4765,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="U5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -4687,7 +4797,7 @@
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
       <c r="T6" s="1" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="U6" s="9"/>
     </row>
@@ -4980,27 +5090,27 @@
   <sheetData>
     <row r="2" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B2" s="68" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C2" s="65"/>
       <c r="E2" s="60" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="F2" s="54"/>
       <c r="H2" s="60" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="I2" s="54"/>
       <c r="K2" s="60" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="L2" s="54"/>
       <c r="N2" s="60" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="O2" s="54"/>
       <c r="Q2" s="60" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="R2" s="54"/>
     </row>
@@ -5008,71 +5118,71 @@
       <c r="B3" s="66"/>
       <c r="C3" s="67"/>
       <c r="E3" s="34" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F3" s="35"/>
       <c r="H3" s="34" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="I3" s="35"/>
       <c r="K3" s="34" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="L3" s="35"/>
       <c r="N3" s="34" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="O3" s="35"/>
       <c r="Q3" s="34" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="R3" s="35"/>
       <c r="T3" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="C4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="C4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="E4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="F4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="F4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="H4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="I4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="I4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="K4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="L4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="L4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="N4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="O4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="O4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="Q4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="R4" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="R4" s="25" t="s">
-        <v>167</v>
-      </c>
       <c r="T4" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="U4" t="s">
         <v>281</v>
-      </c>
-      <c r="U4" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
@@ -5089,10 +5199,10 @@
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
       <c r="T5" s="1" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="U5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
@@ -5391,22 +5501,22 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B2" s="50" t="s">
+        <v>291</v>
+      </c>
+      <c r="C2" s="50" t="s">
+        <v>292</v>
+      </c>
+      <c r="D2" s="50" t="s">
         <v>293</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="E2" s="50" t="s">
         <v>294</v>
       </c>
-      <c r="D2" s="50" t="s">
+      <c r="F2" s="50" t="s">
         <v>295</v>
       </c>
-      <c r="E2" s="50" t="s">
+      <c r="G2" s="50" t="s">
         <v>296</v>
-      </c>
-      <c r="F2" s="50" t="s">
-        <v>297</v>
-      </c>
-      <c r="G2" s="50" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.2">
@@ -5417,7 +5527,7 @@
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="I3" s="14" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="J3" s="3"/>
     </row>
@@ -5439,7 +5549,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="I5" s="14" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="J5" s="3"/>
     </row>
@@ -5461,7 +5571,7 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="I7" s="14" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -5473,7 +5583,7 @@
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="I8" s="14" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="J8" s="3"/>
     </row>
@@ -5485,7 +5595,7 @@
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="I9" s="14" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="J9" s="3"/>
     </row>
@@ -5505,7 +5615,7 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="J11" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.2">
@@ -6316,16 +6426,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:AP52"/>
+  <dimension ref="A2:AQ52"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" style="1" customWidth="1"/>
     <col min="2" max="2" width="17.33203125" style="1" customWidth="1"/>
     <col min="3" max="10" width="8.5" style="1" customWidth="1"/>
-    <col min="11" max="41" width="8.5" customWidth="1"/>
+    <col min="11" max="42" width="8.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C2" s="6" t="s">
         <v>79</v>
       </c>
@@ -6340,7 +6450,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C3" s="1" t="s">
         <v>83</v>
       </c>
@@ -6361,7 +6471,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C4" s="1" t="s">
         <v>89</v>
       </c>
@@ -6383,67 +6493,67 @@
         <v>93</v>
       </c>
       <c r="AK4" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="C5" s="1" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="C5" s="1" t="s">
+      <c r="D5" t="s">
         <v>95</v>
-      </c>
-      <c r="D5" t="s">
-        <v>96</v>
       </c>
       <c r="L5" s="26"/>
       <c r="M5" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="O5" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="P5" s="9" t="s">
         <v>98</v>
-      </c>
-      <c r="P5" s="9" t="s">
-        <v>99</v>
       </c>
       <c r="AD5" s="14"/>
       <c r="AJ5" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AK5" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="AK5" s="9" t="s">
+    </row>
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
+      <c r="C6" s="1" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="9" t="s">
         <v>102</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>103</v>
       </c>
       <c r="L6" s="29"/>
       <c r="M6" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="O6" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="O6" s="1" t="s">
+      <c r="P6" t="s">
         <v>105</v>
-      </c>
-      <c r="P6" t="s">
-        <v>106</v>
       </c>
       <c r="AE6" s="1"/>
       <c r="AF6" s="1"/>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>107</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>108</v>
       </c>
       <c r="AE7" s="1"/>
       <c r="AF7" s="1"/>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="53" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D9" s="52"/>
       <c r="E9" s="52"/>
@@ -6469,7 +6579,7 @@
       <c r="Y9" s="54"/>
       <c r="Z9" s="54"/>
       <c r="AA9" s="53" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AB9" s="54"/>
       <c r="AC9" s="54"/>
@@ -6477,7 +6587,7 @@
       <c r="AE9" s="54"/>
       <c r="AF9" s="54"/>
       <c r="AG9" s="53" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AH9" s="54"/>
       <c r="AI9" s="54"/>
@@ -6488,136 +6598,140 @@
       <c r="AN9" s="54"/>
       <c r="AO9" s="54"/>
       <c r="AP9" s="54"/>
-    </row>
-    <row r="10" spans="1:42" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AQ9" s="54"/>
+    </row>
+    <row r="10" spans="1:43" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="20" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="45" t="s">
         <v>112</v>
       </c>
-      <c r="C10" s="45" t="s">
+      <c r="D10" s="48" t="s">
+        <v>308</v>
+      </c>
+      <c r="E10" s="44" t="s">
         <v>113</v>
       </c>
-      <c r="D10" s="48" t="s">
-        <v>311</v>
-      </c>
-      <c r="E10" s="44" t="s">
+      <c r="F10" s="44" t="s">
         <v>114</v>
       </c>
-      <c r="F10" s="44" t="s">
+      <c r="G10" s="45" t="s">
         <v>115</v>
       </c>
-      <c r="G10" s="45" t="s">
+      <c r="H10" s="44" t="s">
         <v>116</v>
       </c>
-      <c r="H10" s="44" t="s">
+      <c r="I10" s="44" t="s">
         <v>117</v>
       </c>
-      <c r="I10" s="44" t="s">
+      <c r="J10" s="49" t="s">
         <v>118</v>
       </c>
-      <c r="J10" s="49" t="s">
+      <c r="K10" s="49" t="s">
         <v>119</v>
       </c>
-      <c r="K10" s="49" t="s">
+      <c r="L10" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="L10" s="21" t="s">
+      <c r="M10" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="M10" s="21" t="s">
+      <c r="N10" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="N10" s="43" t="s">
+      <c r="O10" s="44" t="s">
         <v>123</v>
       </c>
-      <c r="O10" s="44" t="s">
+      <c r="P10" s="44" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q10" s="44" t="s">
         <v>124</v>
       </c>
-      <c r="P10" s="44" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q10" s="44" t="s">
+      <c r="R10" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="R10" s="44" t="s">
+      <c r="S10" s="44" t="s">
         <v>126</v>
       </c>
-      <c r="S10" s="44" t="s">
+      <c r="T10" s="44" t="s">
         <v>127</v>
       </c>
-      <c r="T10" s="44" t="s">
+      <c r="U10" s="44" t="s">
         <v>128</v>
       </c>
-      <c r="U10" s="44" t="s">
+      <c r="V10" s="44" t="s">
         <v>129</v>
       </c>
-      <c r="V10" s="44" t="s">
+      <c r="W10" s="44" t="s">
         <v>130</v>
       </c>
-      <c r="W10" s="44" t="s">
+      <c r="X10" s="44" t="s">
         <v>131</v>
       </c>
-      <c r="X10" s="44" t="s">
+      <c r="Y10" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="Y10" s="44" t="s">
+      <c r="Z10" s="44" t="s">
         <v>133</v>
       </c>
-      <c r="Z10" s="44" t="s">
+      <c r="AA10" s="46" t="s">
+        <v>304</v>
+      </c>
+      <c r="AB10" s="46" t="s">
+        <v>303</v>
+      </c>
+      <c r="AC10" s="47" t="s">
         <v>134</v>
       </c>
-      <c r="AA10" s="46" t="s">
+      <c r="AD10" s="46" t="s">
+        <v>305</v>
+      </c>
+      <c r="AE10" s="46" t="s">
+        <v>306</v>
+      </c>
+      <c r="AF10" s="47" t="s">
         <v>307</v>
       </c>
-      <c r="AB10" s="46" t="s">
-        <v>306</v>
-      </c>
-      <c r="AC10" s="47" t="s">
+      <c r="AG10" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="AD10" s="46" t="s">
-        <v>308</v>
-      </c>
-      <c r="AE10" s="46" t="s">
-        <v>309</v>
-      </c>
-      <c r="AF10" s="47" t="s">
-        <v>310</v>
-      </c>
-      <c r="AG10" s="23" t="s">
+      <c r="AH10" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="AH10" s="23" t="s">
+      <c r="AI10" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="AI10" s="23" t="s">
+      <c r="AJ10" s="23" t="s">
         <v>138</v>
       </c>
-      <c r="AJ10" s="23" t="s">
+      <c r="AK10" s="23" t="s">
         <v>139</v>
       </c>
-      <c r="AK10" s="23" t="s">
+      <c r="AL10" s="23" t="s">
         <v>140</v>
       </c>
-      <c r="AL10" s="23" t="s">
+      <c r="AM10" s="23" t="s">
         <v>141</v>
       </c>
-      <c r="AM10" s="23" t="s">
+      <c r="AN10" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="AN10" s="23" t="s">
+      <c r="AO10" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="AP10" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="AO10" s="23" t="s">
+      <c r="AQ10" s="23" t="s">
         <v>144</v>
       </c>
-      <c r="AP10" s="23" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>1</v>
       </c>
@@ -6734,10 +6848,13 @@
       <c r="AN11" s="3">
         <v>0.0</v>
       </c>
-      <c r="AO11" s="3"/>
+      <c r="AO11" s="3">
+        <v>0.5</v>
+      </c>
       <c r="AP11" s="3"/>
-    </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ11" s="3"/>
+    </row>
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>2</v>
       </c>
@@ -6854,10 +6971,13 @@
       <c r="AN12" s="19">
         <v>0.0</v>
       </c>
-      <c r="AO12" s="19"/>
+      <c r="AO12" s="19">
+        <v>0.5</v>
+      </c>
       <c r="AP12" s="19"/>
-    </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ12" s="19"/>
+    </row>
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>3</v>
       </c>
@@ -6974,10 +7094,13 @@
       <c r="AN13" s="19">
         <v>0.0</v>
       </c>
-      <c r="AO13" s="19"/>
+      <c r="AO13" s="19">
+        <v>0.5</v>
+      </c>
       <c r="AP13" s="19"/>
-    </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ13" s="19"/>
+    </row>
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>4</v>
       </c>
@@ -7022,8 +7145,9 @@
       <c r="AN14" s="3"/>
       <c r="AO14" s="3"/>
       <c r="AP14" s="3"/>
-    </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ14" s="3"/>
+    </row>
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>5</v>
       </c>
@@ -7068,8 +7192,9 @@
       <c r="AN15" s="3"/>
       <c r="AO15" s="3"/>
       <c r="AP15" s="3"/>
-    </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ15" s="3"/>
+    </row>
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>6</v>
       </c>
@@ -7114,8 +7239,9 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
-    </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ16" s="3"/>
+    </row>
+    <row r="17" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>7</v>
       </c>
@@ -7160,8 +7286,9 @@
       <c r="AN17" s="3"/>
       <c r="AO17" s="3"/>
       <c r="AP17" s="3"/>
-    </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ17" s="3"/>
+    </row>
+    <row r="18" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>8</v>
       </c>
@@ -7206,8 +7333,9 @@
       <c r="AN18" s="3"/>
       <c r="AO18" s="3"/>
       <c r="AP18" s="3"/>
-    </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ18" s="3"/>
+    </row>
+    <row r="19" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>9</v>
       </c>
@@ -7252,8 +7380,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
-    </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ19" s="3"/>
+    </row>
+    <row r="20" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>10</v>
       </c>
@@ -7298,8 +7427,9 @@
       <c r="AN20" s="3"/>
       <c r="AO20" s="3"/>
       <c r="AP20" s="3"/>
-    </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ20" s="3"/>
+    </row>
+    <row r="21" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>11</v>
       </c>
@@ -7344,8 +7474,9 @@
       <c r="AN21" s="3"/>
       <c r="AO21" s="3"/>
       <c r="AP21" s="3"/>
-    </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ21" s="3"/>
+    </row>
+    <row r="22" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>12</v>
       </c>
@@ -7390,8 +7521,9 @@
       <c r="AN22" s="3"/>
       <c r="AO22" s="3"/>
       <c r="AP22" s="3"/>
-    </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ22" s="3"/>
+    </row>
+    <row r="23" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>13</v>
       </c>
@@ -7436,8 +7568,9 @@
       <c r="AN23" s="3"/>
       <c r="AO23" s="3"/>
       <c r="AP23" s="3"/>
-    </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ23" s="3"/>
+    </row>
+    <row r="24" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A24" s="3">
         <v>14</v>
       </c>
@@ -7482,8 +7615,9 @@
       <c r="AN24" s="3"/>
       <c r="AO24" s="3"/>
       <c r="AP24" s="3"/>
-    </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ24" s="3"/>
+    </row>
+    <row r="25" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A25" s="3">
         <v>15</v>
       </c>
@@ -7528,8 +7662,9 @@
       <c r="AN25" s="3"/>
       <c r="AO25" s="3"/>
       <c r="AP25" s="3"/>
-    </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ25" s="3"/>
+    </row>
+    <row r="26" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
@@ -7562,8 +7697,9 @@
       <c r="AN26" s="1"/>
       <c r="AO26" s="1"/>
       <c r="AP26" s="1"/>
-    </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="AQ26" s="1"/>
+    </row>
+    <row r="27" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
@@ -7587,7 +7723,7 @@
       <c r="AE27" s="1"/>
       <c r="AF27" s="1"/>
     </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
@@ -7611,7 +7747,7 @@
       <c r="AE28" s="1"/>
       <c r="AF28" s="1"/>
     </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
@@ -7635,7 +7771,7 @@
       <c r="AE29" s="1"/>
       <c r="AF29" s="1"/>
     </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
@@ -7659,7 +7795,7 @@
       <c r="AE30" s="1"/>
       <c r="AF30" s="1"/>
     </row>
-    <row r="31" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
@@ -7683,7 +7819,7 @@
       <c r="AE31" s="1"/>
       <c r="AF31" s="1"/>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:43" x14ac:dyDescent="0.2">
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
@@ -8189,7 +8325,7 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="AG9:AP9"/>
+    <mergeCell ref="AG9:AQ9"/>
     <mergeCell ref="AA9:AF9"/>
     <mergeCell ref="C9:Z9"/>
   </mergeCells>
@@ -8269,7 +8405,7 @@
       <formula>OR($AJ11="vg",$AJ11="gard")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AM11:AN52">
+  <conditionalFormatting sqref="AM11:AO52">
     <cfRule type="expression" dxfId="18" priority="1">
       <formula>$AJ11="lf"</formula>
     </cfRule>
@@ -8317,183 +8453,181 @@
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="B2" s="3"/>
+      <c r="D2" s="24" t="s">
         <v>146</v>
       </c>
-      <c r="B2" s="3">
-        <v>0</v>
-      </c>
-      <c r="D2" s="24" t="s">
+      <c r="N2" s="24" t="s">
         <v>147</v>
-      </c>
-      <c r="N2" s="24" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A4" s="55" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B4" s="52"/>
       <c r="D4" s="55" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E4" s="52"/>
       <c r="G4" s="55" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H4" s="52"/>
       <c r="J4" s="55" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="K4" s="52"/>
       <c r="M4" s="55" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="N4" s="52"/>
       <c r="P4" s="55" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="Q4" s="54"/>
       <c r="R4" s="1"/>
       <c r="S4" s="55" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="T4" s="54"/>
       <c r="U4" s="1"/>
       <c r="V4" s="55" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="W4" s="54"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="55" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Z4" s="54"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="55" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="AC4" s="54"/>
       <c r="AE4" s="55" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AF4" s="54"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="55" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AI4" s="54"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="55" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AL4" s="54"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="55" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AO4" s="54"/>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="55" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AR4" s="54"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B5" s="37">
         <v>1</v>
       </c>
       <c r="D5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E5" s="37">
         <v>2</v>
       </c>
       <c r="G5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H5" s="37">
         <v>3</v>
       </c>
       <c r="J5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K5" s="37">
         <v>4</v>
       </c>
       <c r="M5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="N5" s="37">
         <v>5</v>
       </c>
       <c r="P5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q5" s="37">
         <v>6</v>
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="T5" s="37">
         <v>7</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="W5" s="37">
         <v>8</v>
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Z5" s="37">
         <v>9</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AC5" s="37">
         <v>10</v>
       </c>
       <c r="AE5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AF5" s="37">
         <v>11</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AI5" s="37">
         <v>12</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AL5" s="37">
         <v>13</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AO5" s="37">
         <v>14</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="36" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AR5" s="37">
         <v>15</v>
@@ -8502,17 +8636,17 @@
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A6" s="56" t="str">
         <f>_xlfn.XLOOKUP(B5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
-        <v>levee</v>
+        <v/>
       </c>
       <c r="B6" s="57"/>
       <c r="D6" s="56" t="str">
         <f>_xlfn.XLOOKUP(E5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
-        <v>grout</v>
+        <v/>
       </c>
       <c r="E6" s="57"/>
       <c r="G6" s="56" t="str">
         <f>_xlfn.XLOOKUP(H5,mat!$A:$A, mat!$B:$B,"") &amp; ""</f>
-        <v>foundation</v>
+        <v/>
       </c>
       <c r="H6" s="57"/>
       <c r="J6" s="56" t="str">
@@ -8586,172 +8720,172 @@
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B7" s="37"/>
       <c r="D7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E7" s="37"/>
       <c r="G7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H7" s="37"/>
       <c r="J7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K7" s="37"/>
       <c r="M7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N7" s="37"/>
       <c r="P7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q7" s="37"/>
       <c r="R7" s="1"/>
       <c r="S7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T7" s="37"/>
       <c r="U7" s="1"/>
       <c r="V7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="W7" s="37"/>
       <c r="X7" s="1"/>
       <c r="Y7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Z7" s="37"/>
       <c r="AA7" s="1"/>
       <c r="AB7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AC7" s="37"/>
       <c r="AE7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AF7" s="37"/>
       <c r="AG7" s="1"/>
       <c r="AH7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AI7" s="37"/>
       <c r="AJ7" s="1"/>
       <c r="AK7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AL7" s="37"/>
       <c r="AM7" s="1"/>
       <c r="AN7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AO7" s="37"/>
       <c r="AP7" s="1"/>
       <c r="AQ7" s="36" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AR7" s="37"/>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="D8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="G8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="J8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="M8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="N8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="N8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="P8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="R8" s="1"/>
       <c r="S8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="T8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="U8" s="1"/>
       <c r="V8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="W8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="W8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="X8" s="1"/>
       <c r="Y8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="Z8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="Z8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AA8" s="1"/>
       <c r="AB8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AC8" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="AC8" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="AE8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AF8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AF8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AG8" s="1"/>
       <c r="AH8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AI8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AI8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AL8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AL8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AM8" s="1"/>
       <c r="AN8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AO8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AO8" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AR8" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AR8" s="2" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.2">
@@ -9619,10 +9753,10 @@
   <sheetData>
     <row r="2" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A2" s="24" t="s">
+        <v>167</v>
+      </c>
+      <c r="G2" s="9" t="s">
         <v>168</v>
-      </c>
-      <c r="G2" s="9" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.2">
@@ -9678,42 +9812,42 @@
       <c r="W4" s="54"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="55" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Z4" s="54"/>
       <c r="AA4" s="1"/>
       <c r="AB4" s="55" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AC4" s="54"/>
       <c r="AE4" s="55" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="AF4" s="54"/>
       <c r="AG4" s="1"/>
       <c r="AH4" s="55" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="AI4" s="54"/>
       <c r="AJ4" s="1"/>
       <c r="AK4" s="55" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="AL4" s="54"/>
       <c r="AM4" s="1"/>
       <c r="AN4" s="55" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="AO4" s="54"/>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="55" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AR4" s="54"/>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A5" s="38" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
@@ -9721,7 +9855,7 @@
         </is>
       </c>
       <c r="D5" s="38" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E5" s="39" t="inlineStr">
         <is>
@@ -9729,7 +9863,7 @@
         </is>
       </c>
       <c r="G5" s="38" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H5" s="39" t="inlineStr">
         <is>
@@ -9737,7 +9871,7 @@
         </is>
       </c>
       <c r="J5" s="38" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K5" s="39" t="inlineStr">
         <is>
@@ -9745,7 +9879,7 @@
         </is>
       </c>
       <c r="M5" s="38" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="N5" s="39" t="inlineStr">
         <is>
@@ -9753,7 +9887,7 @@
         </is>
       </c>
       <c r="P5" s="38" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="Q5" s="39" t="inlineStr">
         <is>
@@ -9762,7 +9896,7 @@
       </c>
       <c r="R5" s="1"/>
       <c r="S5" s="38" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="T5" s="39" t="inlineStr">
         <is>
@@ -9771,7 +9905,7 @@
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="38" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="W5" s="39" t="inlineStr">
         <is>
@@ -9780,140 +9914,140 @@
       </c>
       <c r="X5" s="1"/>
       <c r="Y5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="Z5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="Z5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="AA5" s="1"/>
       <c r="AB5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AC5" s="39" t="s">
         <v>185</v>
       </c>
-      <c r="AC5" s="39" t="s">
-        <v>186</v>
-      </c>
       <c r="AE5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AF5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="AF5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="AG5" s="1"/>
       <c r="AH5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AI5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="AI5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AL5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="AL5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="AM5" s="1"/>
       <c r="AN5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AO5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="AO5" s="39" t="s">
-        <v>186</v>
       </c>
       <c r="AP5" s="1"/>
       <c r="AQ5" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="AR5" s="39" t="s">
         <v>185</v>
-      </c>
-      <c r="AR5" s="39" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B6" s="39">
         <v>1</v>
       </c>
       <c r="D6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E6" s="39">
         <v>3</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H6" s="39">
         <v>2</v>
       </c>
       <c r="J6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="K6" s="39">
         <v>3</v>
       </c>
       <c r="M6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="N6" s="39"/>
       <c r="P6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Q6" s="39"/>
       <c r="R6" s="1"/>
       <c r="S6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="T6" s="39"/>
       <c r="U6" s="1"/>
       <c r="V6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="W6" s="39"/>
       <c r="X6" s="1"/>
       <c r="Y6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="Z6" s="39">
         <v>9</v>
       </c>
       <c r="AA6" s="1"/>
       <c r="AB6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AC6" s="39">
         <v>10</v>
       </c>
       <c r="AE6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AF6" s="39">
         <v>11</v>
       </c>
       <c r="AG6" s="1"/>
       <c r="AH6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AI6" s="39">
         <v>12</v>
       </c>
       <c r="AJ6" s="1"/>
       <c r="AK6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AL6" s="39">
         <v>13</v>
       </c>
       <c r="AM6" s="1"/>
       <c r="AN6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AO6" s="39">
         <v>14</v>
       </c>
       <c r="AP6" s="1"/>
       <c r="AQ6" s="38" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AR6" s="39">
         <v>15</v>
@@ -10010,178 +10144,178 @@
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B8" s="39">
         <v>1.5</v>
       </c>
       <c r="D8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E8" s="39"/>
       <c r="G8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H8" s="39"/>
       <c r="J8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="K8" s="39"/>
       <c r="M8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="N8" s="39">
         <v>0.75</v>
       </c>
       <c r="P8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Q8" s="39"/>
       <c r="R8" s="1"/>
       <c r="S8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T8" s="39"/>
       <c r="U8" s="1"/>
       <c r="V8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="W8" s="39">
         <v>0.5</v>
       </c>
       <c r="X8" s="1"/>
       <c r="Y8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Z8" s="39"/>
       <c r="AA8" s="1"/>
       <c r="AB8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AC8" s="39"/>
       <c r="AE8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AF8" s="39"/>
       <c r="AG8" s="1"/>
       <c r="AH8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AI8" s="39"/>
       <c r="AJ8" s="1"/>
       <c r="AK8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AL8" s="39"/>
       <c r="AM8" s="1"/>
       <c r="AN8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AO8" s="39"/>
       <c r="AP8" s="1"/>
       <c r="AQ8" s="38" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="AR8" s="39"/>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="D9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="G9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="J9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="M9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="N9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="N9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="P9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="Q9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="R9" s="1"/>
       <c r="S9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="T9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="U9" s="1"/>
       <c r="V9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="W9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="W9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="X9" s="1"/>
       <c r="Y9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="Z9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="Z9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AA9" s="1"/>
       <c r="AB9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AC9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="AC9" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="AE9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AF9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AF9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AG9" s="1"/>
       <c r="AH9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AI9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AI9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AJ9" s="1"/>
       <c r="AK9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AL9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AL9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AM9" s="1"/>
       <c r="AN9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AO9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AO9" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="AP9" s="1"/>
       <c r="AQ9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="AR9" s="2" t="s">
         <v>166</v>
-      </c>
-      <c r="AR9" s="2" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.2">
@@ -11134,26 +11268,21 @@
     </row>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="J4:K4"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="J7:K7"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="P7:Q7"/>
+    <mergeCell ref="AB7:AC7"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="G7:H7"/>
     <mergeCell ref="S7:T7"/>
     <mergeCell ref="M7:N7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="AN7:AO7"/>
-    <mergeCell ref="M4:N4"/>
     <mergeCell ref="S4:T4"/>
-    <mergeCell ref="AE4:AF4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="V7:W7"/>
-    <mergeCell ref="J4:K4"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="P7:Q7"/>
-    <mergeCell ref="J7:K7"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="AB7:AC7"/>
-    <mergeCell ref="AH7:AI7"/>
     <mergeCell ref="AQ7:AR7"/>
     <mergeCell ref="AN4:AO4"/>
     <mergeCell ref="AH4:AI4"/>
@@ -11164,6 +11293,11 @@
     <mergeCell ref="AK7:AL7"/>
     <mergeCell ref="AB4:AC4"/>
     <mergeCell ref="AK4:AL4"/>
+    <mergeCell ref="AN7:AO7"/>
+    <mergeCell ref="AH7:AI7"/>
+    <mergeCell ref="AE4:AF4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="V7:W7"/>
   </mergeCells>
   <conditionalFormatting sqref="B6 A7:B7">
     <cfRule type="expression" dxfId="17" priority="1">
@@ -11260,20 +11394,20 @@
   <sheetData>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="59" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B2" s="54"/>
       <c r="D2" s="60" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E2" s="54"/>
       <c r="G2" s="22" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="32" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B3" s="33" t="inlineStr">
         <is>
@@ -11281,7 +11415,7 @@
         </is>
       </c>
       <c r="D3" s="34" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E3" s="35" t="inlineStr">
         <is>
@@ -11292,19 +11426,19 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="D4" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="G4" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H4" s="1"/>
     </row>
@@ -11317,7 +11451,7 @@
         <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
@@ -11326,10 +11460,10 @@
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="G6" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="H6" t="s">
         <v>192</v>
-      </c>
-      <c r="H6" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
@@ -11466,31 +11600,31 @@
   <sheetData>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="B2" s="13" t="s">
         <v>194</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="C2" s="13" t="s">
         <v>195</v>
       </c>
-      <c r="C2" s="13" t="s">
+      <c r="D2" s="13" t="s">
         <v>196</v>
       </c>
-      <c r="D2" s="13" t="s">
+      <c r="E2" s="13" t="s">
         <v>197</v>
       </c>
-      <c r="E2" s="13" t="s">
+      <c r="F2" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="F2" s="13" t="s">
+      <c r="G2" s="13" t="s">
         <v>199</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="H2" s="13" t="s">
         <v>200</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="J2" s="5" t="s">
         <v>201</v>
-      </c>
-      <c r="J2" s="5" t="s">
-        <v>202</v>
       </c>
       <c r="K2" s="10" t="s">
         <v>5</v>
@@ -11508,10 +11642,10 @@
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="J3" s="1" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="K3" s="9" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
@@ -11526,10 +11660,10 @@
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="J4" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="K4" s="9" t="s">
         <v>204</v>
-      </c>
-      <c r="K4" s="9" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
@@ -11544,10 +11678,10 @@
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="J5" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="K5" t="s">
         <v>206</v>
-      </c>
-      <c r="K5" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -11574,7 +11708,7 @@
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
       <c r="J7" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -11589,7 +11723,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="J8" s="14" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="K8"/>
     </row>
@@ -11605,7 +11739,7 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="J9" s="14" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="K9"/>
     </row>
@@ -11621,7 +11755,7 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="J10" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="K10"/>
     </row>
@@ -11637,7 +11771,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="J11" s="14" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="K11"/>
     </row>
@@ -11653,31 +11787,31 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="J12" s="14" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="K12"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J13" s="14" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="K13"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J14" s="14" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="K14"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J15" s="14" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K15"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="J16" s="14" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
@@ -11686,7 +11820,7 @@
     </row>
     <row r="17" spans="10:10" x14ac:dyDescent="0.2">
       <c r="J17" s="14" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="K17"/>
     </row>
@@ -11727,16 +11861,16 @@
   <sheetData>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="C2" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>221</v>
-      </c>
       <c r="E2" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F2" s="6" t="s">
         <v>5</v>
@@ -11747,10 +11881,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" t="s">
+        <v>221</v>
+      </c>
+      <c r="F3" t="s">
         <v>222</v>
-      </c>
-      <c r="F3" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -11758,10 +11892,10 @@
       <c r="B4" s="3"/>
       <c r="C4" s="3"/>
       <c r="E4" t="s">
+        <v>223</v>
+      </c>
+      <c r="F4" t="s">
         <v>224</v>
-      </c>
-      <c r="F4" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -11769,10 +11903,10 @@
       <c r="B5" s="3"/>
       <c r="C5" s="3"/>
       <c r="E5" t="s">
+        <v>225</v>
+      </c>
+      <c r="F5" t="s">
         <v>226</v>
-      </c>
-      <c r="F5" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -11896,128 +12030,128 @@
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B2" t="str">
-        <f>IF(main!$D$23="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
+        <f>IF(main!$D$24="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
         <v>Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.</v>
       </c>
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B4" s="61" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
       <c r="F4" s="61" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="G4" s="62"/>
       <c r="H4" s="62"/>
       <c r="J4" s="61" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K4" s="62"/>
       <c r="L4" s="62"/>
       <c r="N4" s="61" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="O4" s="62"/>
       <c r="P4" s="62"/>
       <c r="R4" s="61" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="S4" s="62"/>
       <c r="T4" s="62"/>
       <c r="V4" s="61" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="W4" s="62"/>
       <c r="X4" s="62"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C5" s="57"/>
       <c r="D5" s="39"/>
       <c r="F5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G5" s="57"/>
       <c r="H5" s="39"/>
       <c r="J5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K5" s="57"/>
       <c r="L5" s="39"/>
       <c r="N5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O5" s="57"/>
       <c r="P5" s="39"/>
       <c r="R5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="S5" s="57"/>
       <c r="T5" s="39"/>
       <c r="V5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="W5" s="57"/>
       <c r="X5" s="39"/>
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="L6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="O6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="P6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="R6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="S6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="S6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="T6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="V6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="W6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="W6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="X6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.2">
@@ -12445,128 +12579,128 @@
   <sheetData>
     <row r="2" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B2" t="str">
-        <f>IF(main!$D$23="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
+        <f>IF(main!$D$24="auto","Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.","")</f>
         <v>Enter non-water loads only — water loads derive automatically from the piezometric line / seepage boundary conditions.</v>
       </c>
     </row>
     <row r="4" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B4" s="63" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C4" s="62"/>
       <c r="D4" s="62"/>
       <c r="F4" s="63" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G4" s="62"/>
       <c r="H4" s="62"/>
       <c r="J4" s="63" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="K4" s="62"/>
       <c r="L4" s="62"/>
       <c r="N4" s="63" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="O4" s="62"/>
       <c r="P4" s="62"/>
       <c r="R4" s="63" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="S4" s="62"/>
       <c r="T4" s="62"/>
       <c r="V4" s="63" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="W4" s="62"/>
       <c r="X4" s="62"/>
     </row>
     <row r="5" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C5" s="57"/>
       <c r="D5" s="39"/>
       <c r="F5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G5" s="57"/>
       <c r="H5" s="39"/>
       <c r="J5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="K5" s="57"/>
       <c r="L5" s="39"/>
       <c r="N5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="O5" s="57"/>
       <c r="P5" s="39"/>
       <c r="R5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="S5" s="57"/>
       <c r="T5" s="39"/>
       <c r="V5" s="58" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="W5" s="57"/>
       <c r="X5" s="39"/>
     </row>
     <row r="6" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="D6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="L6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="N6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="O6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="P6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="R6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="S6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="S6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="T6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="V6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="W6" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="W6" s="2" t="s">
-        <v>220</v>
-      </c>
       <c r="X6" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="7" spans="2:24" x14ac:dyDescent="0.2">
